--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="112">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">subject_application_vendor: YOO Multimedia SRL</t>
   </si>
   <si>
-    <t xml:space="preserve">subject_application_version: 1.0.0</t>
+    <t xml:space="preserve">subject_application_version: 1.1.0</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -318,6 +318,22 @@
   </si>
   <si>
     <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09T13:42:58Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92a0d9fa1ee781154fd41ff9bc8018a8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">Razionale di Applicabilità</t>
@@ -754,7 +770,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -904,6 +920,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2764,7 +2784,7 @@
       <c r="G11" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="32" t="s">
         <v>58</v>
       </c>
       <c r="I11" s="33" t="s">
@@ -2787,25 +2807,50 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="16"/>
+    <row r="12" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="n">
+        <v>476</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="34" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F13" s="13"/>
@@ -6875,15 +6920,15 @@
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J11 M10:N11 P10:R11" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J12 M10:N12 P10:R12" type="list">
       <formula1>Sheet1!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T11" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T12" type="list">
       <formula1>Sheet1!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K11" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K12" type="list">
       <formula1>'LISTA VALORI'!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6909,43 +6954,43 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
-        <v>60</v>
+      <c r="A1" s="39" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>61</v>
+      <c r="A2" s="39" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
-        <v>62</v>
+      <c r="A3" s="39" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
-        <v>63</v>
+      <c r="A4" s="39" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
-        <v>64</v>
+      <c r="A5" s="39" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
-        <v>65</v>
+      <c r="A6" s="39" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
-        <v>66</v>
+      <c r="A7" s="39" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="s">
-        <v>67</v>
+      <c r="A8" s="39" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -6977,170 +7022,170 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>72</v>
+      <c r="C1" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>76</v>
+      <c r="A2" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="45" t="s">
+      <c r="A3" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>79</v>
       </c>
+      <c r="C3" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>82</v>
+      <c r="A4" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>85</v>
+      <c r="A5" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>88</v>
+      <c r="A6" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>91</v>
+      <c r="A7" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>94</v>
+      <c r="A8" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>96</v>
+      <c r="B9" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>99</v>
+      <c r="A10" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>102</v>
+      <c r="A11" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="48"/>
+      <c r="D12" s="49"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="48"/>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8125,18 +8170,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -283,43 +283,6 @@
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 1" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-20T10:49:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f17cfcdc21dd44a0f6b102d0921ef63b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.3f47aed86b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 2" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-20T11:50:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87202318605b410218263c6a459226ae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
   </si>
   <si>
@@ -336,6 +299,12 @@
     <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Razionale di Applicabilità</t>
   </si>
   <si>
@@ -466,9 +435,6 @@
   </si>
   <si>
     <t xml:space="preserve">PASS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
   </si>
   <si>
     <t xml:space="preserve">FAIL</t>
@@ -486,7 +452,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,12 +548,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -770,7 +730,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -919,14 +879,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -939,7 +891,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2432,7 +2384,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W574"/>
+  <dimension ref="A1:AA574"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.16"/>
@@ -2717,9 +2669,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="n">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>47</v>
@@ -2734,7 +2686,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>46073</v>
+        <v>46090</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>51</v>
@@ -2745,7 +2697,9 @@
       <c r="I10" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="34" t="s">
+        <v>54</v>
+      </c>
       <c r="K10" s="34"/>
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
@@ -2759,98 +2713,60 @@
       <c r="U10" s="35"/>
       <c r="V10" s="36"/>
       <c r="W10" s="34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="n">
-        <v>445</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>46073</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
+      <c r="T11" s="0"/>
+      <c r="U11" s="0"/>
+      <c r="V11" s="0"/>
+      <c r="W11" s="0"/>
+      <c r="AA11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="n">
-        <v>476</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="34" t="s">
-        <v>54</v>
-      </c>
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
+      <c r="S12" s="0"/>
+      <c r="T12" s="0"/>
+      <c r="U12" s="0"/>
+      <c r="V12" s="0"/>
+      <c r="W12" s="0"/>
+      <c r="AA12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F13" s="13"/>
@@ -6920,15 +6836,15 @@
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J12 M10:N12 P10:R12" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10 M10:N10 P10:R10" type="list">
       <formula1>Sheet1!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T12" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10" type="list">
       <formula1>Sheet1!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K12" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10" type="list">
       <formula1>'LISTA VALORI'!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6954,43 +6870,43 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>65</v>
+      <c r="A1" s="37" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
-        <v>66</v>
+      <c r="A2" s="37" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
-        <v>67</v>
+      <c r="A3" s="37" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="s">
-        <v>68</v>
+      <c r="A4" s="37" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
-        <v>69</v>
+      <c r="A5" s="37" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
-        <v>70</v>
+      <c r="A6" s="37" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
-        <v>71</v>
+      <c r="A7" s="37" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="s">
-        <v>72</v>
+      <c r="A8" s="37" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -7022,170 +6938,170 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="41" t="s">
+      <c r="B3" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D3" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="42" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="B4" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="s">
+      <c r="D4" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="44" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="B5" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D5" s="44" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="45" t="s">
+      <c r="B6" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="45" t="s">
+      <c r="B7" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D7" s="45" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="45" t="s">
+      <c r="B8" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="D9" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="47" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+      <c r="B10" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="45" t="s">
+      <c r="D10" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="47" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+      <c r="B11" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="45" t="s">
+      <c r="D11" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="49"/>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="49"/>
+      <c r="D13" s="47"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8170,18 +8086,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Summary!$A$1:$G$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$29</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="112">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -283,6 +283,49 @@
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 1" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-20T10:49:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f17cfcdc21dd44a0f6b102d0921ef63b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.3f47aed86b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 2" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-20T11:50:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87202318605b410218263c6a459226ae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
   </si>
   <si>
@@ -299,12 +342,6 @@
     <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Razionale di Applicabilità</t>
   </si>
   <si>
@@ -438,9 +475,6 @@
   </si>
   <si>
     <t xml:space="preserve">FAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
   </si>
 </sst>
 </file>
@@ -2384,7 +2418,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA574"/>
+  <dimension ref="A1:W595"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.16"/>
@@ -2669,9 +2703,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="n">
-        <v>476</v>
+        <v>30</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>47</v>
@@ -2679,26 +2713,14 @@
       <c r="C10" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="28"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34" t="s">
         <v>49</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>54</v>
       </c>
       <c r="K10" s="34"/>
       <c r="L10" s="34"/>
@@ -2713,480 +2735,849 @@
       <c r="U10" s="35"/>
       <c r="V10" s="36"/>
       <c r="W10" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="n">
+        <v>38</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="n">
+        <v>46</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="n">
+        <v>175</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="n">
+        <v>177</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="n">
+        <v>178</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="n">
+        <v>179</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="36"/>
+      <c r="W16" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="n">
+        <v>180</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="36"/>
+      <c r="W17" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="n">
+        <v>181</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="n">
+        <v>182</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="n">
+        <v>183</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="n">
+        <v>184</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="n">
+        <v>185</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28" t="n">
+        <v>186</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="28"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="n">
+        <v>187</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28" t="n">
+        <v>188</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="n">
+        <v>189</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="n">
+        <v>190</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="n">
+        <v>444</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>46073</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="33" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
-      <c r="N11" s="0"/>
-      <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" s="0"/>
-      <c r="T11" s="0"/>
-      <c r="U11" s="0"/>
-      <c r="V11" s="0"/>
-      <c r="W11" s="0"/>
-      <c r="AA11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0"/>
-      <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
-      <c r="N12" s="0"/>
-      <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
-      <c r="S12" s="0"/>
-      <c r="T12" s="0"/>
-      <c r="U12" s="0"/>
-      <c r="V12" s="0"/>
-      <c r="W12" s="0"/>
-      <c r="AA12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="16"/>
+      <c r="J28" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="n">
+        <v>445</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>46073</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="J29" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="36"/>
+      <c r="W29" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="n">
+        <v>469</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28" t="n">
+        <v>476</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="J31" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="n">
+        <v>477</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="36"/>
+      <c r="W32" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="n">
+        <v>478</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="36"/>
+      <c r="W33" s="34" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F34" s="13"/>
@@ -5569,67 +5960,424 @@
       <c r="W152" s="16"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W153" s="14"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="14"/>
+      <c r="K153" s="14"/>
+      <c r="L153" s="14"/>
+      <c r="M153" s="14"/>
+      <c r="N153" s="14"/>
+      <c r="O153" s="14"/>
+      <c r="P153" s="14"/>
+      <c r="Q153" s="14"/>
+      <c r="R153" s="14"/>
+      <c r="S153" s="14"/>
+      <c r="T153" s="14"/>
+      <c r="U153" s="15"/>
+      <c r="V153" s="3"/>
+      <c r="W153" s="16"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W154" s="14"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+      <c r="J154" s="14"/>
+      <c r="K154" s="14"/>
+      <c r="L154" s="14"/>
+      <c r="M154" s="14"/>
+      <c r="N154" s="14"/>
+      <c r="O154" s="14"/>
+      <c r="P154" s="14"/>
+      <c r="Q154" s="14"/>
+      <c r="R154" s="14"/>
+      <c r="S154" s="14"/>
+      <c r="T154" s="14"/>
+      <c r="U154" s="15"/>
+      <c r="V154" s="3"/>
+      <c r="W154" s="16"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W155" s="14"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="I155" s="13"/>
+      <c r="J155" s="14"/>
+      <c r="K155" s="14"/>
+      <c r="L155" s="14"/>
+      <c r="M155" s="14"/>
+      <c r="N155" s="14"/>
+      <c r="O155" s="14"/>
+      <c r="P155" s="14"/>
+      <c r="Q155" s="14"/>
+      <c r="R155" s="14"/>
+      <c r="S155" s="14"/>
+      <c r="T155" s="14"/>
+      <c r="U155" s="15"/>
+      <c r="V155" s="3"/>
+      <c r="W155" s="16"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W156" s="14"/>
+      <c r="F156" s="13"/>
+      <c r="G156" s="13"/>
+      <c r="H156" s="13"/>
+      <c r="I156" s="13"/>
+      <c r="J156" s="14"/>
+      <c r="K156" s="14"/>
+      <c r="L156" s="14"/>
+      <c r="M156" s="14"/>
+      <c r="N156" s="14"/>
+      <c r="O156" s="14"/>
+      <c r="P156" s="14"/>
+      <c r="Q156" s="14"/>
+      <c r="R156" s="14"/>
+      <c r="S156" s="14"/>
+      <c r="T156" s="14"/>
+      <c r="U156" s="15"/>
+      <c r="V156" s="3"/>
+      <c r="W156" s="16"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W157" s="14"/>
+      <c r="F157" s="13"/>
+      <c r="G157" s="13"/>
+      <c r="H157" s="13"/>
+      <c r="I157" s="13"/>
+      <c r="J157" s="14"/>
+      <c r="K157" s="14"/>
+      <c r="L157" s="14"/>
+      <c r="M157" s="14"/>
+      <c r="N157" s="14"/>
+      <c r="O157" s="14"/>
+      <c r="P157" s="14"/>
+      <c r="Q157" s="14"/>
+      <c r="R157" s="14"/>
+      <c r="S157" s="14"/>
+      <c r="T157" s="14"/>
+      <c r="U157" s="15"/>
+      <c r="V157" s="3"/>
+      <c r="W157" s="16"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W158" s="14"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="13"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="13"/>
+      <c r="J158" s="14"/>
+      <c r="K158" s="14"/>
+      <c r="L158" s="14"/>
+      <c r="M158" s="14"/>
+      <c r="N158" s="14"/>
+      <c r="O158" s="14"/>
+      <c r="P158" s="14"/>
+      <c r="Q158" s="14"/>
+      <c r="R158" s="14"/>
+      <c r="S158" s="14"/>
+      <c r="T158" s="14"/>
+      <c r="U158" s="15"/>
+      <c r="V158" s="3"/>
+      <c r="W158" s="16"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W159" s="14"/>
+      <c r="F159" s="13"/>
+      <c r="G159" s="13"/>
+      <c r="H159" s="13"/>
+      <c r="I159" s="13"/>
+      <c r="J159" s="14"/>
+      <c r="K159" s="14"/>
+      <c r="L159" s="14"/>
+      <c r="M159" s="14"/>
+      <c r="N159" s="14"/>
+      <c r="O159" s="14"/>
+      <c r="P159" s="14"/>
+      <c r="Q159" s="14"/>
+      <c r="R159" s="14"/>
+      <c r="S159" s="14"/>
+      <c r="T159" s="14"/>
+      <c r="U159" s="15"/>
+      <c r="V159" s="3"/>
+      <c r="W159" s="16"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W160" s="14"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="13"/>
+      <c r="J160" s="14"/>
+      <c r="K160" s="14"/>
+      <c r="L160" s="14"/>
+      <c r="M160" s="14"/>
+      <c r="N160" s="14"/>
+      <c r="O160" s="14"/>
+      <c r="P160" s="14"/>
+      <c r="Q160" s="14"/>
+      <c r="R160" s="14"/>
+      <c r="S160" s="14"/>
+      <c r="T160" s="14"/>
+      <c r="U160" s="15"/>
+      <c r="V160" s="3"/>
+      <c r="W160" s="16"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W161" s="14"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="13"/>
+      <c r="H161" s="13"/>
+      <c r="I161" s="13"/>
+      <c r="J161" s="14"/>
+      <c r="K161" s="14"/>
+      <c r="L161" s="14"/>
+      <c r="M161" s="14"/>
+      <c r="N161" s="14"/>
+      <c r="O161" s="14"/>
+      <c r="P161" s="14"/>
+      <c r="Q161" s="14"/>
+      <c r="R161" s="14"/>
+      <c r="S161" s="14"/>
+      <c r="T161" s="14"/>
+      <c r="U161" s="15"/>
+      <c r="V161" s="3"/>
+      <c r="W161" s="16"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W162" s="14"/>
+      <c r="F162" s="13"/>
+      <c r="G162" s="13"/>
+      <c r="H162" s="13"/>
+      <c r="I162" s="13"/>
+      <c r="J162" s="14"/>
+      <c r="K162" s="14"/>
+      <c r="L162" s="14"/>
+      <c r="M162" s="14"/>
+      <c r="N162" s="14"/>
+      <c r="O162" s="14"/>
+      <c r="P162" s="14"/>
+      <c r="Q162" s="14"/>
+      <c r="R162" s="14"/>
+      <c r="S162" s="14"/>
+      <c r="T162" s="14"/>
+      <c r="U162" s="15"/>
+      <c r="V162" s="3"/>
+      <c r="W162" s="16"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W163" s="14"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="13"/>
+      <c r="H163" s="13"/>
+      <c r="I163" s="13"/>
+      <c r="J163" s="14"/>
+      <c r="K163" s="14"/>
+      <c r="L163" s="14"/>
+      <c r="M163" s="14"/>
+      <c r="N163" s="14"/>
+      <c r="O163" s="14"/>
+      <c r="P163" s="14"/>
+      <c r="Q163" s="14"/>
+      <c r="R163" s="14"/>
+      <c r="S163" s="14"/>
+      <c r="T163" s="14"/>
+      <c r="U163" s="15"/>
+      <c r="V163" s="3"/>
+      <c r="W163" s="16"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W164" s="14"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="13"/>
+      <c r="H164" s="13"/>
+      <c r="I164" s="13"/>
+      <c r="J164" s="14"/>
+      <c r="K164" s="14"/>
+      <c r="L164" s="14"/>
+      <c r="M164" s="14"/>
+      <c r="N164" s="14"/>
+      <c r="O164" s="14"/>
+      <c r="P164" s="14"/>
+      <c r="Q164" s="14"/>
+      <c r="R164" s="14"/>
+      <c r="S164" s="14"/>
+      <c r="T164" s="14"/>
+      <c r="U164" s="15"/>
+      <c r="V164" s="3"/>
+      <c r="W164" s="16"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W165" s="14"/>
+      <c r="F165" s="13"/>
+      <c r="G165" s="13"/>
+      <c r="H165" s="13"/>
+      <c r="I165" s="13"/>
+      <c r="J165" s="14"/>
+      <c r="K165" s="14"/>
+      <c r="L165" s="14"/>
+      <c r="M165" s="14"/>
+      <c r="N165" s="14"/>
+      <c r="O165" s="14"/>
+      <c r="P165" s="14"/>
+      <c r="Q165" s="14"/>
+      <c r="R165" s="14"/>
+      <c r="S165" s="14"/>
+      <c r="T165" s="14"/>
+      <c r="U165" s="15"/>
+      <c r="V165" s="3"/>
+      <c r="W165" s="16"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W166" s="14"/>
+      <c r="F166" s="13"/>
+      <c r="G166" s="13"/>
+      <c r="H166" s="13"/>
+      <c r="I166" s="13"/>
+      <c r="J166" s="14"/>
+      <c r="K166" s="14"/>
+      <c r="L166" s="14"/>
+      <c r="M166" s="14"/>
+      <c r="N166" s="14"/>
+      <c r="O166" s="14"/>
+      <c r="P166" s="14"/>
+      <c r="Q166" s="14"/>
+      <c r="R166" s="14"/>
+      <c r="S166" s="14"/>
+      <c r="T166" s="14"/>
+      <c r="U166" s="15"/>
+      <c r="V166" s="3"/>
+      <c r="W166" s="16"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W167" s="14"/>
+      <c r="F167" s="13"/>
+      <c r="G167" s="13"/>
+      <c r="H167" s="13"/>
+      <c r="I167" s="13"/>
+      <c r="J167" s="14"/>
+      <c r="K167" s="14"/>
+      <c r="L167" s="14"/>
+      <c r="M167" s="14"/>
+      <c r="N167" s="14"/>
+      <c r="O167" s="14"/>
+      <c r="P167" s="14"/>
+      <c r="Q167" s="14"/>
+      <c r="R167" s="14"/>
+      <c r="S167" s="14"/>
+      <c r="T167" s="14"/>
+      <c r="U167" s="15"/>
+      <c r="V167" s="3"/>
+      <c r="W167" s="16"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W168" s="14"/>
+      <c r="F168" s="13"/>
+      <c r="G168" s="13"/>
+      <c r="H168" s="13"/>
+      <c r="I168" s="13"/>
+      <c r="J168" s="14"/>
+      <c r="K168" s="14"/>
+      <c r="L168" s="14"/>
+      <c r="M168" s="14"/>
+      <c r="N168" s="14"/>
+      <c r="O168" s="14"/>
+      <c r="P168" s="14"/>
+      <c r="Q168" s="14"/>
+      <c r="R168" s="14"/>
+      <c r="S168" s="14"/>
+      <c r="T168" s="14"/>
+      <c r="U168" s="15"/>
+      <c r="V168" s="3"/>
+      <c r="W168" s="16"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W169" s="14"/>
+      <c r="F169" s="13"/>
+      <c r="G169" s="13"/>
+      <c r="H169" s="13"/>
+      <c r="I169" s="13"/>
+      <c r="J169" s="14"/>
+      <c r="K169" s="14"/>
+      <c r="L169" s="14"/>
+      <c r="M169" s="14"/>
+      <c r="N169" s="14"/>
+      <c r="O169" s="14"/>
+      <c r="P169" s="14"/>
+      <c r="Q169" s="14"/>
+      <c r="R169" s="14"/>
+      <c r="S169" s="14"/>
+      <c r="T169" s="14"/>
+      <c r="U169" s="15"/>
+      <c r="V169" s="3"/>
+      <c r="W169" s="16"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W170" s="14"/>
+      <c r="F170" s="13"/>
+      <c r="G170" s="13"/>
+      <c r="H170" s="13"/>
+      <c r="I170" s="13"/>
+      <c r="J170" s="14"/>
+      <c r="K170" s="14"/>
+      <c r="L170" s="14"/>
+      <c r="M170" s="14"/>
+      <c r="N170" s="14"/>
+      <c r="O170" s="14"/>
+      <c r="P170" s="14"/>
+      <c r="Q170" s="14"/>
+      <c r="R170" s="14"/>
+      <c r="S170" s="14"/>
+      <c r="T170" s="14"/>
+      <c r="U170" s="15"/>
+      <c r="V170" s="3"/>
+      <c r="W170" s="16"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W171" s="14"/>
+      <c r="F171" s="13"/>
+      <c r="G171" s="13"/>
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="14"/>
+      <c r="K171" s="14"/>
+      <c r="L171" s="14"/>
+      <c r="M171" s="14"/>
+      <c r="N171" s="14"/>
+      <c r="O171" s="14"/>
+      <c r="P171" s="14"/>
+      <c r="Q171" s="14"/>
+      <c r="R171" s="14"/>
+      <c r="S171" s="14"/>
+      <c r="T171" s="14"/>
+      <c r="U171" s="15"/>
+      <c r="V171" s="3"/>
+      <c r="W171" s="16"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W172" s="14"/>
+      <c r="F172" s="13"/>
+      <c r="G172" s="13"/>
+      <c r="H172" s="13"/>
+      <c r="I172" s="13"/>
+      <c r="J172" s="14"/>
+      <c r="K172" s="14"/>
+      <c r="L172" s="14"/>
+      <c r="M172" s="14"/>
+      <c r="N172" s="14"/>
+      <c r="O172" s="14"/>
+      <c r="P172" s="14"/>
+      <c r="Q172" s="14"/>
+      <c r="R172" s="14"/>
+      <c r="S172" s="14"/>
+      <c r="T172" s="14"/>
+      <c r="U172" s="15"/>
+      <c r="V172" s="3"/>
+      <c r="W172" s="16"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W173" s="14"/>
+      <c r="F173" s="13"/>
+      <c r="G173" s="13"/>
+      <c r="H173" s="13"/>
+      <c r="I173" s="13"/>
+      <c r="J173" s="14"/>
+      <c r="K173" s="14"/>
+      <c r="L173" s="14"/>
+      <c r="M173" s="14"/>
+      <c r="N173" s="14"/>
+      <c r="O173" s="14"/>
+      <c r="P173" s="14"/>
+      <c r="Q173" s="14"/>
+      <c r="R173" s="14"/>
+      <c r="S173" s="14"/>
+      <c r="T173" s="14"/>
+      <c r="U173" s="15"/>
+      <c r="V173" s="3"/>
+      <c r="W173" s="16"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W174" s="14"/>
@@ -6819,13 +7567,76 @@
     <row r="569" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W569" s="14"/>
     </row>
-    <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W570" s="14"/>
+    </row>
+    <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W571" s="14"/>
+    </row>
+    <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W572" s="14"/>
+    </row>
+    <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W573" s="14"/>
+    </row>
+    <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W574" s="14"/>
+    </row>
+    <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W575" s="14"/>
+    </row>
+    <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W576" s="14"/>
+    </row>
+    <row r="577" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W577" s="14"/>
+    </row>
+    <row r="578" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W578" s="14"/>
+    </row>
+    <row r="579" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W579" s="14"/>
+    </row>
+    <row r="580" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W580" s="14"/>
+    </row>
+    <row r="581" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W581" s="14"/>
+    </row>
+    <row r="582" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W582" s="14"/>
+    </row>
+    <row r="583" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W583" s="14"/>
+    </row>
+    <row r="584" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W584" s="14"/>
+    </row>
+    <row r="585" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W585" s="14"/>
+    </row>
+    <row r="586" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W586" s="14"/>
+    </row>
+    <row r="587" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W587" s="14"/>
+    </row>
+    <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W588" s="14"/>
+    </row>
+    <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W589" s="14"/>
+    </row>
+    <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W590" s="14"/>
+    </row>
+    <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A9:W11"/>
+  <autoFilter ref="A9:W29"/>
   <mergeCells count="7">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -6836,15 +7647,15 @@
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10 M10:N10 P10:R10" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J33 M10:N33 P10:R33" type="list">
       <formula1>Sheet1!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T33" type="list">
       <formula1>Sheet1!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K33" type="list">
       <formula1>'LISTA VALORI'!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6871,42 +7682,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="37" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -6939,120 +7750,120 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="42" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="42" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="42" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7060,41 +7871,41 @@
         <v>48</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="42" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8086,18 +8897,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="133">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -283,10 +283,64 @@
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT4</t>
+  </si>
+  <si>
     <t xml:space="preserve">NO</t>
   </si>
   <si>
     <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT1</t>
@@ -326,6 +380,9 @@
     <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22</t>
+  </si>
+  <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
   </si>
   <si>
@@ -340,6 +397,12 @@
   </si>
   <si>
     <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT24</t>
   </si>
   <si>
     <t xml:space="preserve">Razionale di Applicabilità</t>
@@ -486,7 +549,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,6 +638,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -764,7 +833,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -885,6 +954,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -893,11 +966,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -925,7 +998,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2713,29 +2786,31 @@
       <c r="C10" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="34" t="s">
+      <c r="D10" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="34" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2748,29 +2823,31 @@
       <c r="C11" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="34" t="s">
+      <c r="D11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2783,29 +2860,31 @@
       <c r="C12" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="34" t="s">
+      <c r="D12" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2818,29 +2897,31 @@
       <c r="C13" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="34" t="s">
+      <c r="D13" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2853,29 +2934,31 @@
       <c r="C14" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="34" t="s">
+      <c r="D14" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2888,29 +2971,31 @@
       <c r="C15" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="36"/>
-      <c r="W15" s="34" t="s">
+      <c r="D15" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="37"/>
+      <c r="W15" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2923,29 +3008,31 @@
       <c r="C16" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="34" t="s">
+      <c r="D16" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2958,29 +3045,31 @@
       <c r="C17" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="34" t="s">
+      <c r="D17" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2993,29 +3082,31 @@
       <c r="C18" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="34" t="s">
+      <c r="D18" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="37"/>
+      <c r="W18" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3028,29 +3119,31 @@
       <c r="C19" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="34" t="s">
+      <c r="D19" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3063,29 +3156,31 @@
       <c r="C20" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="34" t="s">
+      <c r="D20" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3098,29 +3193,31 @@
       <c r="C21" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="36"/>
-      <c r="W21" s="34" t="s">
+      <c r="D21" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3133,29 +3230,31 @@
       <c r="C22" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="36"/>
-      <c r="W22" s="34" t="s">
+      <c r="D22" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3168,29 +3267,31 @@
       <c r="C23" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="36"/>
-      <c r="W23" s="34" t="s">
+      <c r="D23" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3203,29 +3304,31 @@
       <c r="C24" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="36"/>
-      <c r="W24" s="34" t="s">
+      <c r="D24" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3238,29 +3341,31 @@
       <c r="C25" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="36"/>
-      <c r="W25" s="34" t="s">
+      <c r="D25" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,29 +3378,31 @@
       <c r="C26" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="36"/>
-      <c r="W26" s="34" t="s">
+      <c r="D26" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3308,29 +3415,31 @@
       <c r="C27" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="28"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="36"/>
-      <c r="W27" s="34" t="s">
+      <c r="D27" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3344,40 +3453,40 @@
         <v>48</v>
       </c>
       <c r="D28" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="32" t="n">
+        <v>46073</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="35" t="s">
         <v>51</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="F28" s="31" t="n">
-        <v>46073</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="36"/>
-      <c r="W28" s="34" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3391,40 +3500,40 @@
         <v>48</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="31" t="n">
+        <v>75</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="32" t="n">
         <v>46073</v>
       </c>
-      <c r="G29" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="J29" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="36"/>
-      <c r="W29" s="34" t="s">
-        <v>50</v>
+      <c r="G29" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3437,29 +3546,31 @@
       <c r="C30" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="28"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="34" t="s">
+      <c r="D30" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3473,40 +3584,40 @@
         <v>48</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="F31" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="E31" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" s="32" t="n">
         <v>46090</v>
       </c>
-      <c r="G31" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="J31" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="36"/>
-      <c r="W31" s="34" t="s">
-        <v>50</v>
+      <c r="G31" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="J31" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3519,29 +3630,31 @@
       <c r="C32" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="35"/>
-      <c r="V32" s="36"/>
-      <c r="W32" s="34" t="s">
+      <c r="D32" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="31"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="36"/>
+      <c r="V32" s="37"/>
+      <c r="W32" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3554,29 +3667,31 @@
       <c r="C33" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="35"/>
-      <c r="V33" s="36"/>
-      <c r="W33" s="34" t="s">
+      <c r="D33" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="31"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7681,43 +7796,43 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
-        <v>67</v>
+      <c r="A1" s="38" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
-        <v>68</v>
+      <c r="A2" s="38" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
-        <v>69</v>
+      <c r="A3" s="38" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
-        <v>70</v>
+      <c r="A4" s="38" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
-        <v>71</v>
+      <c r="A5" s="38" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
-        <v>72</v>
+      <c r="A6" s="38" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
-        <v>73</v>
+      <c r="A7" s="38" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>74</v>
+      <c r="A8" s="38" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -7749,170 +7864,170 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="39" t="s">
+      <c r="A1" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>79</v>
+      <c r="C1" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>83</v>
+      <c r="A2" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>86</v>
+      <c r="A3" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>89</v>
+      <c r="A4" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>92</v>
+      <c r="A5" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>95</v>
+      <c r="A6" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>98</v>
+      <c r="A7" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>101</v>
+      <c r="A8" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="43" t="s">
+      <c r="B9" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="45" t="s">
-        <v>103</v>
+      <c r="C9" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>106</v>
+      <c r="A10" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>109</v>
+      <c r="A11" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="47"/>
+      <c r="D12" s="48"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="47"/>
+      <c r="D13" s="48"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8897,18 +9012,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Summary!$A$1:$G$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$29</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$31</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="156">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -70,7 +70,8 @@
     <t xml:space="preserve">2) Per tutti i casi di test coerenti con la/e tipologia/e di documento utilizzata/e dal software è necessario compilare SEMPRE la colonna APPLICABILITA' con SI o NO</t>
   </si>
   <si>
-    <t xml:space="preserve">3) Nel caso in cui tra le tipologie documentali oggetto di accreditamento per l'applicativo figurino PSS, RAP, RAD, RSA, LDO, LAB, VPS, SING_VACC, CERT_VACC i relativi casi di test con id 444, 417, 418, 460, 448, 450, 452,454, 456, 457, 458, 471 che recepiscono quanto previsto dal Decreto 07 settembre 2023, devono essere obbligatoriamente eseguiti e compilati (la colonna APPLICABILITA' deve essere valorizzata con SI)</t>
+    <t xml:space="preserve">3) Nel caso in cui tra le tipologie documentali oggetto di accreditamento per l'applicativo figurino PSS, RAP, RAD, RSA, LDO, LAB, VPS, SING_VACC, CERT_VACC, TPI, LETT_SCREEN, LETT_VACC, CCE  i relativi casi di test con id 476*, 417, 418, 460, 448, 450, 452,454, 456, 457, 458, 471, 479, 491, 506, 521   che recepiscono quanto previsto dal Decreto 07 settembre 2023, devono essere obbligatoriamente eseguiti e compilati (la colonna APPLICABILITA' deve essere valorizzata con SI). 
+*) Il test in questione è da intendersi obbligatorio per gli applicativi che si stanno accreditando per la prima volta per PSS; nel caso di applicativi già accreditati, sarà sufficiente sottomettere il caso di test 478 (Fast Track)</t>
   </si>
   <si>
     <t xml:space="preserve">4) Se il test è applicabile la colonna APPLICABILITA' deve essere compilata con SI e dovranno essere valorizzate:
@@ -83,7 +84,7 @@
     MESSAGGIO DI ERRORE da compilare con il messaggio di errore visualizzato dall’applicativo, solo per i casi KO (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT visibili all'utente (colonna ERRORE VISIBILE A UTENTE (SI/NO)=SI)
     GESTITO IN BACKOFFICE (SI/NO) da compilare solo per i casi KO (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
     PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO A FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO) da compilare solo per i casi KO (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
-   INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO) da compilare solo per i casi KO  (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
+  INVIO MANUALE DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO) da compilare solo per i casi KO  (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
     GESTIONE ERRORE da compilare con la procedura che viene adottata per la gestione dell'errore, solo per i casi KO (ovvero con CASO OK / KO= KO) e per i casi di test di TIMEOUT,  specificando le modalità di invio del documento clinico al FSE a seguito della correzione dell'errore e chiarendo se è possibile per l'utente (medico) proseguire con il processo e produrre il documento. Esclusivamente per i casi di test di TIMEOUT, qualora non fosse prevista una coda di retry e la gestione dell'errore non fossa gestita da un operatore di backoffice, indicare le modalità attraverso cui è reso esplicito all’utente (medico) di effettuare nuovi tentativi di invio verso il FSE fino al ripristino del servizio di validazione.</t>
   </si>
   <si>
@@ -199,13 +200,73 @@
     <t xml:space="preserve">IDENTIFICATIVI SOFTWARE</t>
   </si>
   <si>
-    <t xml:space="preserve">subject_application_id: YOOMULTIMEDIA-FSE-GATEWAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subject_application_vendor: YOO Multimedia SRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subject_application_version: 1.1.0</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">subject_application_id: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">YOOMULTIMEDIA-FSE-GATEWAY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">subject_application_vendor: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">YOO Multimedia SRL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">subject_application_version: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1.1.0</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -256,10 +317,10 @@
     <t xml:space="preserve">GESTITO IN BACKOFFICE (SI/NO)</t>
   </si>
   <si>
-    <t xml:space="preserve"> PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
+    <t xml:space="preserve">PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVIO MANUALE DEL DOCUMENTO AL SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
   </si>
   <si>
     <t xml:space="preserve">GESTIONE ERRORE</t>
@@ -283,126 +344,273 @@
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT4</t>
+    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_PSS_KO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <u val="single"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Precondizioni:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Il fornitore utilizza un token jwt mancante di campi obbligatori, quindi non valido.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <u val="single"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Descrizione di Business del caso di test: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" con un token jwt non valido a causa della mancanza di uno o più campi obbligatori al fine di testare la gestione dell'errore sul token (status code 403), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Al fine di rendere non valido il token è necessario non valorizzare nel JWT il campo "purpose_of_use".</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">NO</t>
   </si>
   <si>
+    <t xml:space="preserve">KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_CAMPO_PSS_KO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <u val="single"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Precondizioni:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Il fornitore utilizza un token jwt con dei campi valorizzati in maniera errata.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <u val="single"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Descrizione di Business del caso di test: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" con un token jwt avente dei campi valorizzati in maniera errata al fine di testare la gestione dell'errore sul token (status code 403), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Al fine di rendere non valido il token è necessario valorizzare il campo "action_id" con la stringa "TEST" (valore non ammesso).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_PSS_TIMEOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per questo caso di test è richiesta la sola descrizione del comportamento a fronte di un timeout, da inserire nelle colonne relative a:
+"ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 11" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 12" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 23" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09T13:42:58Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92a0d9fa1ee781154fd41ff9bc8018a8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
     <t xml:space="preserve">OK</t>
   </si>
   <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT1</t>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT24</t>
   </si>
   <si>
     <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 1" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-20T10:49:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f17cfcdc21dd44a0f6b102d0921ef63b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.3f47aed86b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT2</t>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT25</t>
   </si>
   <si>
     <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 2" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-20T11:50:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87202318605b410218263c6a459226ae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-09T13:42:58Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92a0d9fa1ee781154fd41ff9bc8018a8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT24</t>
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. Il "CASO DI TEST 25" si riferisce a un esempio di CDA2 semplice, contenente esclusivamente sezioni ed elementi obbligatori previsti dalle specifiche nazionali (IG HL7 Italia)</t>
   </si>
   <si>
     <t xml:space="preserve">Razionale di Applicabilità</t>
@@ -441,7 +649,7 @@
     <t xml:space="preserve">Versione:</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.5</t>
+    <t xml:space="preserve">8.3.0</t>
   </si>
   <si>
     <t xml:space="preserve">LAB</t>
@@ -453,7 +661,7 @@
     <t xml:space="preserve">4, 452</t>
   </si>
   <si>
-    <t xml:space="preserve">28,36,44,53,55,56,57,58,59,60,61,62, 466</t>
+    <t xml:space="preserve">28,36,44,53,55,56,57,59,60,61,62, 466, 473</t>
   </si>
   <si>
     <t xml:space="preserve">LDO</t>
@@ -471,7 +679,7 @@
     <t xml:space="preserve">471, 472</t>
   </si>
   <si>
-    <t xml:space="preserve">31,39,47,76,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93, 462</t>
+    <t xml:space="preserve">31,39,47,76,78,79,80,81,83,84,85,86,87,88,89,90,91,92,93, 462, 474</t>
   </si>
   <si>
     <t xml:space="preserve">CERT_VAC</t>
@@ -507,10 +715,10 @@
     <t xml:space="preserve">448, 449</t>
   </si>
   <si>
-    <t xml:space="preserve">32,40,48,152,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169, 461, 468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">444, 445</t>
+    <t xml:space="preserve">32,40,48,152,154,155,156,157,159,160,161,162,163,164,165,166,167,168,169, 461, 468, 475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">476,477,478</t>
   </si>
   <si>
     <t xml:space="preserve">30,38,46,175,177,178,179,180,181,182,183,184,185,186,187,188,189,190, 469</t>
@@ -532,6 +740,39 @@
   </si>
   <si>
     <t xml:space="preserve">423,424,425,427,428,429,430,431,432,433,434,435,436,437,438,439,440,441,442,443,448,449, 470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">479, 480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481,482,483,484,485,486,487,488,489,490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETT_SCREEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">491, 492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493,494,495,496,497,498,499,500,501,502,503,504,505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETT_VACC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">506, 507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508,509,510,511,512,513,514,515,516,517,518,519,520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">522,523,524,525,526,527,528,529,530</t>
   </si>
   <si>
     <t xml:space="preserve">PASS</t>
@@ -549,7 +790,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,12 +858,25 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -640,17 +894,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -838,196 +1094,196 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1338,34 +1594,34 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="130.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="130.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="0" width="8.82"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="65.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="33.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="55.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="206.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1374,34 +1630,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1420,11 +1676,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B996"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="194.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="194.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1433,12 +1689,12 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2"/>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
@@ -2491,22 +2747,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W595"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="63.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="78.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="33.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="27.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="11" style="1" width="36.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="27.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="33.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="36.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="1" width="31.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="30.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="63.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="104.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="33.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="27.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="11" style="0" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="27.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="33.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="0" width="31.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="30.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2527,7 +2783,7 @@
       <c r="S1" s="14"/>
       <c r="T1" s="14"/>
       <c r="U1" s="15"/>
-      <c r="V1" s="3"/>
+      <c r="V1" s="2"/>
       <c r="W1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2555,7 +2811,7 @@
       <c r="S2" s="14"/>
       <c r="T2" s="14"/>
       <c r="U2" s="15"/>
-      <c r="V2" s="3"/>
+      <c r="V2" s="2"/>
       <c r="W2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2583,7 +2839,7 @@
       <c r="S3" s="14"/>
       <c r="T3" s="14"/>
       <c r="U3" s="15"/>
-      <c r="V3" s="3"/>
+      <c r="V3" s="2"/>
       <c r="W3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2610,7 +2866,7 @@
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
       <c r="U4" s="15"/>
-      <c r="V4" s="3"/>
+      <c r="V4" s="2"/>
       <c r="W4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2636,7 +2892,7 @@
       <c r="S5" s="14"/>
       <c r="T5" s="14"/>
       <c r="U5" s="15"/>
-      <c r="V5" s="3"/>
+      <c r="V5" s="2"/>
       <c r="W5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2659,7 +2915,7 @@
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="15"/>
-      <c r="V6" s="3"/>
+      <c r="V6" s="2"/>
       <c r="W6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2682,7 +2938,7 @@
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="15"/>
-      <c r="V7" s="3"/>
+      <c r="V7" s="2"/>
       <c r="W7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2702,7 +2958,7 @@
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="15"/>
-      <c r="V8" s="3"/>
+      <c r="V8" s="2"/>
       <c r="W8" s="16"/>
     </row>
     <row r="9" s="27" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2776,7 +3032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="n">
         <v>30</v>
       </c>
@@ -2786,34 +3042,36 @@
       <c r="C10" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35" t="s">
+      <c r="E10" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="35" t="s">
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="n">
         <v>38</v>
       </c>
@@ -2823,34 +3081,36 @@
       <c r="C11" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="12" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="n">
         <v>46</v>
       </c>
@@ -2860,34 +3120,38 @@
       <c r="C12" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="35" t="s">
+      <c r="D12" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="35"/>
+      <c r="W12" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="n">
         <v>175</v>
       </c>
@@ -2897,34 +3161,36 @@
       <c r="C13" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="35" t="s">
+      <c r="D13" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="n">
         <v>177</v>
       </c>
@@ -2934,34 +3200,36 @@
       <c r="C14" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="35" t="s">
+      <c r="D14" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="34"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="n">
         <v>178</v>
       </c>
@@ -2971,34 +3239,36 @@
       <c r="C15" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="37"/>
-      <c r="W15" s="35" t="s">
+      <c r="D15" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="n">
         <v>179</v>
       </c>
@@ -3008,34 +3278,36 @@
       <c r="C16" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="35" t="s">
+      <c r="D16" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="n">
         <v>180</v>
       </c>
@@ -3045,34 +3317,36 @@
       <c r="C17" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="36"/>
-      <c r="V17" s="37"/>
-      <c r="W17" s="35" t="s">
+      <c r="D17" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="n">
         <v>181</v>
       </c>
@@ -3082,34 +3356,36 @@
       <c r="C18" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="35" t="s">
+      <c r="D18" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="n">
         <v>182</v>
       </c>
@@ -3119,34 +3395,36 @@
       <c r="C19" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="37"/>
-      <c r="W19" s="35" t="s">
+      <c r="D19" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="n">
         <v>183</v>
       </c>
@@ -3156,34 +3434,36 @@
       <c r="C20" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="35" t="s">
+      <c r="D20" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="n">
         <v>184</v>
       </c>
@@ -3193,34 +3473,36 @@
       <c r="C21" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="35" t="s">
+      <c r="D21" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="n">
         <v>185</v>
       </c>
@@ -3230,34 +3512,36 @@
       <c r="C22" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="36"/>
-      <c r="V22" s="37"/>
-      <c r="W22" s="35" t="s">
+      <c r="D22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="n">
         <v>186</v>
       </c>
@@ -3267,34 +3551,36 @@
       <c r="C23" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="37"/>
-      <c r="W23" s="35" t="s">
+      <c r="D23" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="n">
         <v>187</v>
       </c>
@@ -3304,34 +3590,36 @@
       <c r="C24" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="37"/>
-      <c r="W24" s="35" t="s">
+      <c r="D24" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="n">
         <v>188</v>
       </c>
@@ -3341,34 +3629,36 @@
       <c r="C25" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="37"/>
-      <c r="W25" s="35" t="s">
+      <c r="D25" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="n">
         <v>189</v>
       </c>
@@ -3378,34 +3668,36 @@
       <c r="C26" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="35" t="s">
+      <c r="D26" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="n">
         <v>190</v>
       </c>
@@ -3415,36 +3707,38 @@
       <c r="C27" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="37"/>
-      <c r="W27" s="35" t="s">
+      <c r="D27" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="n">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>47</v>
@@ -3453,45 +3747,37 @@
         <v>48</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="32" t="n">
-        <v>46073</v>
-      </c>
-      <c r="G28" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="36"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K28" s="33"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="37.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="n">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>47</v>
@@ -3500,45 +3786,45 @@
         <v>48</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="32" t="n">
-        <v>46073</v>
-      </c>
-      <c r="G29" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="J29" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="36"/>
-      <c r="V29" s="37"/>
-      <c r="W29" s="35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>47</v>
@@ -3546,36 +3832,38 @@
       <c r="C30" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="37"/>
-      <c r="W30" s="35" t="s">
+      <c r="D30" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B31" s="28" t="s">
         <v>47</v>
@@ -3584,115 +3872,73 @@
         <v>48</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="32" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G31" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="I31" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="J31" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="36"/>
-      <c r="V31" s="37"/>
-      <c r="W31" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="n">
-        <v>477</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
-      <c r="U32" s="36"/>
-      <c r="V32" s="37"/>
-      <c r="W32" s="35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="n">
-        <v>478</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="37"/>
-      <c r="W33" s="35" t="s">
-        <v>51</v>
-      </c>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="16"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F34" s="13"/>
@@ -3711,7 +3957,7 @@
       <c r="S34" s="14"/>
       <c r="T34" s="14"/>
       <c r="U34" s="15"/>
-      <c r="V34" s="3"/>
+      <c r="V34" s="2"/>
       <c r="W34" s="16"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3731,7 +3977,7 @@
       <c r="S35" s="14"/>
       <c r="T35" s="14"/>
       <c r="U35" s="15"/>
-      <c r="V35" s="3"/>
+      <c r="V35" s="2"/>
       <c r="W35" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3751,7 +3997,7 @@
       <c r="S36" s="14"/>
       <c r="T36" s="14"/>
       <c r="U36" s="15"/>
-      <c r="V36" s="3"/>
+      <c r="V36" s="2"/>
       <c r="W36" s="16"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3771,7 +4017,7 @@
       <c r="S37" s="14"/>
       <c r="T37" s="14"/>
       <c r="U37" s="15"/>
-      <c r="V37" s="3"/>
+      <c r="V37" s="2"/>
       <c r="W37" s="16"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3791,7 +4037,7 @@
       <c r="S38" s="14"/>
       <c r="T38" s="14"/>
       <c r="U38" s="15"/>
-      <c r="V38" s="3"/>
+      <c r="V38" s="2"/>
       <c r="W38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3811,7 +4057,7 @@
       <c r="S39" s="14"/>
       <c r="T39" s="14"/>
       <c r="U39" s="15"/>
-      <c r="V39" s="3"/>
+      <c r="V39" s="2"/>
       <c r="W39" s="16"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3831,7 +4077,7 @@
       <c r="S40" s="14"/>
       <c r="T40" s="14"/>
       <c r="U40" s="15"/>
-      <c r="V40" s="3"/>
+      <c r="V40" s="2"/>
       <c r="W40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3851,7 +4097,7 @@
       <c r="S41" s="14"/>
       <c r="T41" s="14"/>
       <c r="U41" s="15"/>
-      <c r="V41" s="3"/>
+      <c r="V41" s="2"/>
       <c r="W41" s="16"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3871,7 +4117,7 @@
       <c r="S42" s="14"/>
       <c r="T42" s="14"/>
       <c r="U42" s="15"/>
-      <c r="V42" s="3"/>
+      <c r="V42" s="2"/>
       <c r="W42" s="16"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3891,7 +4137,7 @@
       <c r="S43" s="14"/>
       <c r="T43" s="14"/>
       <c r="U43" s="15"/>
-      <c r="V43" s="3"/>
+      <c r="V43" s="2"/>
       <c r="W43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3911,7 +4157,7 @@
       <c r="S44" s="14"/>
       <c r="T44" s="14"/>
       <c r="U44" s="15"/>
-      <c r="V44" s="3"/>
+      <c r="V44" s="2"/>
       <c r="W44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3931,7 +4177,7 @@
       <c r="S45" s="14"/>
       <c r="T45" s="14"/>
       <c r="U45" s="15"/>
-      <c r="V45" s="3"/>
+      <c r="V45" s="2"/>
       <c r="W45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3951,7 +4197,7 @@
       <c r="S46" s="14"/>
       <c r="T46" s="14"/>
       <c r="U46" s="15"/>
-      <c r="V46" s="3"/>
+      <c r="V46" s="2"/>
       <c r="W46" s="16"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3971,7 +4217,7 @@
       <c r="S47" s="14"/>
       <c r="T47" s="14"/>
       <c r="U47" s="15"/>
-      <c r="V47" s="3"/>
+      <c r="V47" s="2"/>
       <c r="W47" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3991,7 +4237,7 @@
       <c r="S48" s="14"/>
       <c r="T48" s="14"/>
       <c r="U48" s="15"/>
-      <c r="V48" s="3"/>
+      <c r="V48" s="2"/>
       <c r="W48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4011,7 +4257,7 @@
       <c r="S49" s="14"/>
       <c r="T49" s="14"/>
       <c r="U49" s="15"/>
-      <c r="V49" s="3"/>
+      <c r="V49" s="2"/>
       <c r="W49" s="16"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4031,7 +4277,7 @@
       <c r="S50" s="14"/>
       <c r="T50" s="14"/>
       <c r="U50" s="15"/>
-      <c r="V50" s="3"/>
+      <c r="V50" s="2"/>
       <c r="W50" s="16"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4051,7 +4297,7 @@
       <c r="S51" s="14"/>
       <c r="T51" s="14"/>
       <c r="U51" s="15"/>
-      <c r="V51" s="3"/>
+      <c r="V51" s="2"/>
       <c r="W51" s="16"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4071,7 +4317,7 @@
       <c r="S52" s="14"/>
       <c r="T52" s="14"/>
       <c r="U52" s="15"/>
-      <c r="V52" s="3"/>
+      <c r="V52" s="2"/>
       <c r="W52" s="16"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4091,7 +4337,7 @@
       <c r="S53" s="14"/>
       <c r="T53" s="14"/>
       <c r="U53" s="15"/>
-      <c r="V53" s="3"/>
+      <c r="V53" s="2"/>
       <c r="W53" s="16"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4111,7 +4357,7 @@
       <c r="S54" s="14"/>
       <c r="T54" s="14"/>
       <c r="U54" s="15"/>
-      <c r="V54" s="3"/>
+      <c r="V54" s="2"/>
       <c r="W54" s="16"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4131,7 +4377,7 @@
       <c r="S55" s="14"/>
       <c r="T55" s="14"/>
       <c r="U55" s="15"/>
-      <c r="V55" s="3"/>
+      <c r="V55" s="2"/>
       <c r="W55" s="16"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4151,7 +4397,7 @@
       <c r="S56" s="14"/>
       <c r="T56" s="14"/>
       <c r="U56" s="15"/>
-      <c r="V56" s="3"/>
+      <c r="V56" s="2"/>
       <c r="W56" s="16"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4171,7 +4417,7 @@
       <c r="S57" s="14"/>
       <c r="T57" s="14"/>
       <c r="U57" s="15"/>
-      <c r="V57" s="3"/>
+      <c r="V57" s="2"/>
       <c r="W57" s="16"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4191,7 +4437,7 @@
       <c r="S58" s="14"/>
       <c r="T58" s="14"/>
       <c r="U58" s="15"/>
-      <c r="V58" s="3"/>
+      <c r="V58" s="2"/>
       <c r="W58" s="16"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4211,7 +4457,7 @@
       <c r="S59" s="14"/>
       <c r="T59" s="14"/>
       <c r="U59" s="15"/>
-      <c r="V59" s="3"/>
+      <c r="V59" s="2"/>
       <c r="W59" s="16"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4231,7 +4477,7 @@
       <c r="S60" s="14"/>
       <c r="T60" s="14"/>
       <c r="U60" s="15"/>
-      <c r="V60" s="3"/>
+      <c r="V60" s="2"/>
       <c r="W60" s="16"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4251,7 +4497,7 @@
       <c r="S61" s="14"/>
       <c r="T61" s="14"/>
       <c r="U61" s="15"/>
-      <c r="V61" s="3"/>
+      <c r="V61" s="2"/>
       <c r="W61" s="16"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4271,7 +4517,7 @@
       <c r="S62" s="14"/>
       <c r="T62" s="14"/>
       <c r="U62" s="15"/>
-      <c r="V62" s="3"/>
+      <c r="V62" s="2"/>
       <c r="W62" s="16"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4291,7 +4537,7 @@
       <c r="S63" s="14"/>
       <c r="T63" s="14"/>
       <c r="U63" s="15"/>
-      <c r="V63" s="3"/>
+      <c r="V63" s="2"/>
       <c r="W63" s="16"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4311,7 +4557,7 @@
       <c r="S64" s="14"/>
       <c r="T64" s="14"/>
       <c r="U64" s="15"/>
-      <c r="V64" s="3"/>
+      <c r="V64" s="2"/>
       <c r="W64" s="16"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4331,7 +4577,7 @@
       <c r="S65" s="14"/>
       <c r="T65" s="14"/>
       <c r="U65" s="15"/>
-      <c r="V65" s="3"/>
+      <c r="V65" s="2"/>
       <c r="W65" s="16"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4351,7 +4597,7 @@
       <c r="S66" s="14"/>
       <c r="T66" s="14"/>
       <c r="U66" s="15"/>
-      <c r="V66" s="3"/>
+      <c r="V66" s="2"/>
       <c r="W66" s="16"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4371,7 +4617,7 @@
       <c r="S67" s="14"/>
       <c r="T67" s="14"/>
       <c r="U67" s="15"/>
-      <c r="V67" s="3"/>
+      <c r="V67" s="2"/>
       <c r="W67" s="16"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4391,7 +4637,7 @@
       <c r="S68" s="14"/>
       <c r="T68" s="14"/>
       <c r="U68" s="15"/>
-      <c r="V68" s="3"/>
+      <c r="V68" s="2"/>
       <c r="W68" s="16"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4411,7 +4657,7 @@
       <c r="S69" s="14"/>
       <c r="T69" s="14"/>
       <c r="U69" s="15"/>
-      <c r="V69" s="3"/>
+      <c r="V69" s="2"/>
       <c r="W69" s="16"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4431,7 +4677,7 @@
       <c r="S70" s="14"/>
       <c r="T70" s="14"/>
       <c r="U70" s="15"/>
-      <c r="V70" s="3"/>
+      <c r="V70" s="2"/>
       <c r="W70" s="16"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4451,7 +4697,7 @@
       <c r="S71" s="14"/>
       <c r="T71" s="14"/>
       <c r="U71" s="15"/>
-      <c r="V71" s="3"/>
+      <c r="V71" s="2"/>
       <c r="W71" s="16"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4471,7 +4717,7 @@
       <c r="S72" s="14"/>
       <c r="T72" s="14"/>
       <c r="U72" s="15"/>
-      <c r="V72" s="3"/>
+      <c r="V72" s="2"/>
       <c r="W72" s="16"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4491,7 +4737,7 @@
       <c r="S73" s="14"/>
       <c r="T73" s="14"/>
       <c r="U73" s="15"/>
-      <c r="V73" s="3"/>
+      <c r="V73" s="2"/>
       <c r="W73" s="16"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4511,7 +4757,7 @@
       <c r="S74" s="14"/>
       <c r="T74" s="14"/>
       <c r="U74" s="15"/>
-      <c r="V74" s="3"/>
+      <c r="V74" s="2"/>
       <c r="W74" s="16"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4531,7 +4777,7 @@
       <c r="S75" s="14"/>
       <c r="T75" s="14"/>
       <c r="U75" s="15"/>
-      <c r="V75" s="3"/>
+      <c r="V75" s="2"/>
       <c r="W75" s="16"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4551,7 +4797,7 @@
       <c r="S76" s="14"/>
       <c r="T76" s="14"/>
       <c r="U76" s="15"/>
-      <c r="V76" s="3"/>
+      <c r="V76" s="2"/>
       <c r="W76" s="16"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4571,7 +4817,7 @@
       <c r="S77" s="14"/>
       <c r="T77" s="14"/>
       <c r="U77" s="15"/>
-      <c r="V77" s="3"/>
+      <c r="V77" s="2"/>
       <c r="W77" s="16"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4591,7 +4837,7 @@
       <c r="S78" s="14"/>
       <c r="T78" s="14"/>
       <c r="U78" s="15"/>
-      <c r="V78" s="3"/>
+      <c r="V78" s="2"/>
       <c r="W78" s="16"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4611,7 +4857,7 @@
       <c r="S79" s="14"/>
       <c r="T79" s="14"/>
       <c r="U79" s="15"/>
-      <c r="V79" s="3"/>
+      <c r="V79" s="2"/>
       <c r="W79" s="16"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4631,7 +4877,7 @@
       <c r="S80" s="14"/>
       <c r="T80" s="14"/>
       <c r="U80" s="15"/>
-      <c r="V80" s="3"/>
+      <c r="V80" s="2"/>
       <c r="W80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4651,7 +4897,7 @@
       <c r="S81" s="14"/>
       <c r="T81" s="14"/>
       <c r="U81" s="15"/>
-      <c r="V81" s="3"/>
+      <c r="V81" s="2"/>
       <c r="W81" s="16"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4671,7 +4917,7 @@
       <c r="S82" s="14"/>
       <c r="T82" s="14"/>
       <c r="U82" s="15"/>
-      <c r="V82" s="3"/>
+      <c r="V82" s="2"/>
       <c r="W82" s="16"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4691,7 +4937,7 @@
       <c r="S83" s="14"/>
       <c r="T83" s="14"/>
       <c r="U83" s="15"/>
-      <c r="V83" s="3"/>
+      <c r="V83" s="2"/>
       <c r="W83" s="16"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4711,7 +4957,7 @@
       <c r="S84" s="14"/>
       <c r="T84" s="14"/>
       <c r="U84" s="15"/>
-      <c r="V84" s="3"/>
+      <c r="V84" s="2"/>
       <c r="W84" s="16"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4731,7 +4977,7 @@
       <c r="S85" s="14"/>
       <c r="T85" s="14"/>
       <c r="U85" s="15"/>
-      <c r="V85" s="3"/>
+      <c r="V85" s="2"/>
       <c r="W85" s="16"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4751,7 +4997,7 @@
       <c r="S86" s="14"/>
       <c r="T86" s="14"/>
       <c r="U86" s="15"/>
-      <c r="V86" s="3"/>
+      <c r="V86" s="2"/>
       <c r="W86" s="16"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4771,7 +5017,7 @@
       <c r="S87" s="14"/>
       <c r="T87" s="14"/>
       <c r="U87" s="15"/>
-      <c r="V87" s="3"/>
+      <c r="V87" s="2"/>
       <c r="W87" s="16"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4791,7 +5037,7 @@
       <c r="S88" s="14"/>
       <c r="T88" s="14"/>
       <c r="U88" s="15"/>
-      <c r="V88" s="3"/>
+      <c r="V88" s="2"/>
       <c r="W88" s="16"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4811,7 +5057,7 @@
       <c r="S89" s="14"/>
       <c r="T89" s="14"/>
       <c r="U89" s="15"/>
-      <c r="V89" s="3"/>
+      <c r="V89" s="2"/>
       <c r="W89" s="16"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4831,7 +5077,7 @@
       <c r="S90" s="14"/>
       <c r="T90" s="14"/>
       <c r="U90" s="15"/>
-      <c r="V90" s="3"/>
+      <c r="V90" s="2"/>
       <c r="W90" s="16"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4851,7 +5097,7 @@
       <c r="S91" s="14"/>
       <c r="T91" s="14"/>
       <c r="U91" s="15"/>
-      <c r="V91" s="3"/>
+      <c r="V91" s="2"/>
       <c r="W91" s="16"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4871,7 +5117,7 @@
       <c r="S92" s="14"/>
       <c r="T92" s="14"/>
       <c r="U92" s="15"/>
-      <c r="V92" s="3"/>
+      <c r="V92" s="2"/>
       <c r="W92" s="16"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4891,7 +5137,7 @@
       <c r="S93" s="14"/>
       <c r="T93" s="14"/>
       <c r="U93" s="15"/>
-      <c r="V93" s="3"/>
+      <c r="V93" s="2"/>
       <c r="W93" s="16"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4911,7 +5157,7 @@
       <c r="S94" s="14"/>
       <c r="T94" s="14"/>
       <c r="U94" s="15"/>
-      <c r="V94" s="3"/>
+      <c r="V94" s="2"/>
       <c r="W94" s="16"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4931,7 +5177,7 @@
       <c r="S95" s="14"/>
       <c r="T95" s="14"/>
       <c r="U95" s="15"/>
-      <c r="V95" s="3"/>
+      <c r="V95" s="2"/>
       <c r="W95" s="16"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4951,7 +5197,7 @@
       <c r="S96" s="14"/>
       <c r="T96" s="14"/>
       <c r="U96" s="15"/>
-      <c r="V96" s="3"/>
+      <c r="V96" s="2"/>
       <c r="W96" s="16"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4971,7 +5217,7 @@
       <c r="S97" s="14"/>
       <c r="T97" s="14"/>
       <c r="U97" s="15"/>
-      <c r="V97" s="3"/>
+      <c r="V97" s="2"/>
       <c r="W97" s="16"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4991,7 +5237,7 @@
       <c r="S98" s="14"/>
       <c r="T98" s="14"/>
       <c r="U98" s="15"/>
-      <c r="V98" s="3"/>
+      <c r="V98" s="2"/>
       <c r="W98" s="16"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5011,7 +5257,7 @@
       <c r="S99" s="14"/>
       <c r="T99" s="14"/>
       <c r="U99" s="15"/>
-      <c r="V99" s="3"/>
+      <c r="V99" s="2"/>
       <c r="W99" s="16"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5031,7 +5277,7 @@
       <c r="S100" s="14"/>
       <c r="T100" s="14"/>
       <c r="U100" s="15"/>
-      <c r="V100" s="3"/>
+      <c r="V100" s="2"/>
       <c r="W100" s="16"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5051,7 +5297,7 @@
       <c r="S101" s="14"/>
       <c r="T101" s="14"/>
       <c r="U101" s="15"/>
-      <c r="V101" s="3"/>
+      <c r="V101" s="2"/>
       <c r="W101" s="16"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5071,7 +5317,7 @@
       <c r="S102" s="14"/>
       <c r="T102" s="14"/>
       <c r="U102" s="15"/>
-      <c r="V102" s="3"/>
+      <c r="V102" s="2"/>
       <c r="W102" s="16"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5091,7 +5337,7 @@
       <c r="S103" s="14"/>
       <c r="T103" s="14"/>
       <c r="U103" s="15"/>
-      <c r="V103" s="3"/>
+      <c r="V103" s="2"/>
       <c r="W103" s="16"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5111,7 +5357,7 @@
       <c r="S104" s="14"/>
       <c r="T104" s="14"/>
       <c r="U104" s="15"/>
-      <c r="V104" s="3"/>
+      <c r="V104" s="2"/>
       <c r="W104" s="16"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5131,7 +5377,7 @@
       <c r="S105" s="14"/>
       <c r="T105" s="14"/>
       <c r="U105" s="15"/>
-      <c r="V105" s="3"/>
+      <c r="V105" s="2"/>
       <c r="W105" s="16"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5151,7 +5397,7 @@
       <c r="S106" s="14"/>
       <c r="T106" s="14"/>
       <c r="U106" s="15"/>
-      <c r="V106" s="3"/>
+      <c r="V106" s="2"/>
       <c r="W106" s="16"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5171,7 +5417,7 @@
       <c r="S107" s="14"/>
       <c r="T107" s="14"/>
       <c r="U107" s="15"/>
-      <c r="V107" s="3"/>
+      <c r="V107" s="2"/>
       <c r="W107" s="16"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5191,7 +5437,7 @@
       <c r="S108" s="14"/>
       <c r="T108" s="14"/>
       <c r="U108" s="15"/>
-      <c r="V108" s="3"/>
+      <c r="V108" s="2"/>
       <c r="W108" s="16"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5211,7 +5457,7 @@
       <c r="S109" s="14"/>
       <c r="T109" s="14"/>
       <c r="U109" s="15"/>
-      <c r="V109" s="3"/>
+      <c r="V109" s="2"/>
       <c r="W109" s="16"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5231,7 +5477,7 @@
       <c r="S110" s="14"/>
       <c r="T110" s="14"/>
       <c r="U110" s="15"/>
-      <c r="V110" s="3"/>
+      <c r="V110" s="2"/>
       <c r="W110" s="16"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5251,7 +5497,7 @@
       <c r="S111" s="14"/>
       <c r="T111" s="14"/>
       <c r="U111" s="15"/>
-      <c r="V111" s="3"/>
+      <c r="V111" s="2"/>
       <c r="W111" s="16"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5271,7 +5517,7 @@
       <c r="S112" s="14"/>
       <c r="T112" s="14"/>
       <c r="U112" s="15"/>
-      <c r="V112" s="3"/>
+      <c r="V112" s="2"/>
       <c r="W112" s="16"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5291,7 +5537,7 @@
       <c r="S113" s="14"/>
       <c r="T113" s="14"/>
       <c r="U113" s="15"/>
-      <c r="V113" s="3"/>
+      <c r="V113" s="2"/>
       <c r="W113" s="16"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5311,7 +5557,7 @@
       <c r="S114" s="14"/>
       <c r="T114" s="14"/>
       <c r="U114" s="15"/>
-      <c r="V114" s="3"/>
+      <c r="V114" s="2"/>
       <c r="W114" s="16"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5331,7 +5577,7 @@
       <c r="S115" s="14"/>
       <c r="T115" s="14"/>
       <c r="U115" s="15"/>
-      <c r="V115" s="3"/>
+      <c r="V115" s="2"/>
       <c r="W115" s="16"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5351,7 +5597,7 @@
       <c r="S116" s="14"/>
       <c r="T116" s="14"/>
       <c r="U116" s="15"/>
-      <c r="V116" s="3"/>
+      <c r="V116" s="2"/>
       <c r="W116" s="16"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5371,1128 +5617,176 @@
       <c r="S117" s="14"/>
       <c r="T117" s="14"/>
       <c r="U117" s="15"/>
-      <c r="V117" s="3"/>
+      <c r="V117" s="2"/>
       <c r="W117" s="16"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="13"/>
-      <c r="J118" s="14"/>
-      <c r="K118" s="14"/>
-      <c r="L118" s="14"/>
-      <c r="M118" s="14"/>
-      <c r="N118" s="14"/>
-      <c r="O118" s="14"/>
-      <c r="P118" s="14"/>
-      <c r="Q118" s="14"/>
-      <c r="R118" s="14"/>
-      <c r="S118" s="14"/>
-      <c r="T118" s="14"/>
-      <c r="U118" s="15"/>
-      <c r="V118" s="3"/>
-      <c r="W118" s="16"/>
+      <c r="W118" s="14"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
-      <c r="J119" s="14"/>
-      <c r="K119" s="14"/>
-      <c r="L119" s="14"/>
-      <c r="M119" s="14"/>
-      <c r="N119" s="14"/>
-      <c r="O119" s="14"/>
-      <c r="P119" s="14"/>
-      <c r="Q119" s="14"/>
-      <c r="R119" s="14"/>
-      <c r="S119" s="14"/>
-      <c r="T119" s="14"/>
-      <c r="U119" s="15"/>
-      <c r="V119" s="3"/>
-      <c r="W119" s="16"/>
+      <c r="W119" s="14"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
-      <c r="J120" s="14"/>
-      <c r="K120" s="14"/>
-      <c r="L120" s="14"/>
-      <c r="M120" s="14"/>
-      <c r="N120" s="14"/>
-      <c r="O120" s="14"/>
-      <c r="P120" s="14"/>
-      <c r="Q120" s="14"/>
-      <c r="R120" s="14"/>
-      <c r="S120" s="14"/>
-      <c r="T120" s="14"/>
-      <c r="U120" s="15"/>
-      <c r="V120" s="3"/>
-      <c r="W120" s="16"/>
+      <c r="W120" s="14"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F121" s="13"/>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
-      <c r="J121" s="14"/>
-      <c r="K121" s="14"/>
-      <c r="L121" s="14"/>
-      <c r="M121" s="14"/>
-      <c r="N121" s="14"/>
-      <c r="O121" s="14"/>
-      <c r="P121" s="14"/>
-      <c r="Q121" s="14"/>
-      <c r="R121" s="14"/>
-      <c r="S121" s="14"/>
-      <c r="T121" s="14"/>
-      <c r="U121" s="15"/>
-      <c r="V121" s="3"/>
-      <c r="W121" s="16"/>
+      <c r="W121" s="14"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
-      <c r="J122" s="14"/>
-      <c r="K122" s="14"/>
-      <c r="L122" s="14"/>
-      <c r="M122" s="14"/>
-      <c r="N122" s="14"/>
-      <c r="O122" s="14"/>
-      <c r="P122" s="14"/>
-      <c r="Q122" s="14"/>
-      <c r="R122" s="14"/>
-      <c r="S122" s="14"/>
-      <c r="T122" s="14"/>
-      <c r="U122" s="15"/>
-      <c r="V122" s="3"/>
-      <c r="W122" s="16"/>
+      <c r="W122" s="14"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F123" s="13"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="13"/>
-      <c r="J123" s="14"/>
-      <c r="K123" s="14"/>
-      <c r="L123" s="14"/>
-      <c r="M123" s="14"/>
-      <c r="N123" s="14"/>
-      <c r="O123" s="14"/>
-      <c r="P123" s="14"/>
-      <c r="Q123" s="14"/>
-      <c r="R123" s="14"/>
-      <c r="S123" s="14"/>
-      <c r="T123" s="14"/>
-      <c r="U123" s="15"/>
-      <c r="V123" s="3"/>
-      <c r="W123" s="16"/>
+      <c r="W123" s="14"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F124" s="13"/>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="13"/>
-      <c r="J124" s="14"/>
-      <c r="K124" s="14"/>
-      <c r="L124" s="14"/>
-      <c r="M124" s="14"/>
-      <c r="N124" s="14"/>
-      <c r="O124" s="14"/>
-      <c r="P124" s="14"/>
-      <c r="Q124" s="14"/>
-      <c r="R124" s="14"/>
-      <c r="S124" s="14"/>
-      <c r="T124" s="14"/>
-      <c r="U124" s="15"/>
-      <c r="V124" s="3"/>
-      <c r="W124" s="16"/>
+      <c r="W124" s="14"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F125" s="13"/>
-      <c r="G125" s="13"/>
-      <c r="H125" s="13"/>
-      <c r="I125" s="13"/>
-      <c r="J125" s="14"/>
-      <c r="K125" s="14"/>
-      <c r="L125" s="14"/>
-      <c r="M125" s="14"/>
-      <c r="N125" s="14"/>
-      <c r="O125" s="14"/>
-      <c r="P125" s="14"/>
-      <c r="Q125" s="14"/>
-      <c r="R125" s="14"/>
-      <c r="S125" s="14"/>
-      <c r="T125" s="14"/>
-      <c r="U125" s="15"/>
-      <c r="V125" s="3"/>
-      <c r="W125" s="16"/>
+      <c r="W125" s="14"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F126" s="13"/>
-      <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
-      <c r="I126" s="13"/>
-      <c r="J126" s="14"/>
-      <c r="K126" s="14"/>
-      <c r="L126" s="14"/>
-      <c r="M126" s="14"/>
-      <c r="N126" s="14"/>
-      <c r="O126" s="14"/>
-      <c r="P126" s="14"/>
-      <c r="Q126" s="14"/>
-      <c r="R126" s="14"/>
-      <c r="S126" s="14"/>
-      <c r="T126" s="14"/>
-      <c r="U126" s="15"/>
-      <c r="V126" s="3"/>
-      <c r="W126" s="16"/>
+      <c r="W126" s="14"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F127" s="13"/>
-      <c r="G127" s="13"/>
-      <c r="H127" s="13"/>
-      <c r="I127" s="13"/>
-      <c r="J127" s="14"/>
-      <c r="K127" s="14"/>
-      <c r="L127" s="14"/>
-      <c r="M127" s="14"/>
-      <c r="N127" s="14"/>
-      <c r="O127" s="14"/>
-      <c r="P127" s="14"/>
-      <c r="Q127" s="14"/>
-      <c r="R127" s="14"/>
-      <c r="S127" s="14"/>
-      <c r="T127" s="14"/>
-      <c r="U127" s="15"/>
-      <c r="V127" s="3"/>
-      <c r="W127" s="16"/>
+      <c r="W127" s="14"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F128" s="13"/>
-      <c r="G128" s="13"/>
-      <c r="H128" s="13"/>
-      <c r="I128" s="13"/>
-      <c r="J128" s="14"/>
-      <c r="K128" s="14"/>
-      <c r="L128" s="14"/>
-      <c r="M128" s="14"/>
-      <c r="N128" s="14"/>
-      <c r="O128" s="14"/>
-      <c r="P128" s="14"/>
-      <c r="Q128" s="14"/>
-      <c r="R128" s="14"/>
-      <c r="S128" s="14"/>
-      <c r="T128" s="14"/>
-      <c r="U128" s="15"/>
-      <c r="V128" s="3"/>
-      <c r="W128" s="16"/>
+      <c r="W128" s="14"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F129" s="13"/>
-      <c r="G129" s="13"/>
-      <c r="H129" s="13"/>
-      <c r="I129" s="13"/>
-      <c r="J129" s="14"/>
-      <c r="K129" s="14"/>
-      <c r="L129" s="14"/>
-      <c r="M129" s="14"/>
-      <c r="N129" s="14"/>
-      <c r="O129" s="14"/>
-      <c r="P129" s="14"/>
-      <c r="Q129" s="14"/>
-      <c r="R129" s="14"/>
-      <c r="S129" s="14"/>
-      <c r="T129" s="14"/>
-      <c r="U129" s="15"/>
-      <c r="V129" s="3"/>
-      <c r="W129" s="16"/>
+      <c r="W129" s="14"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F130" s="13"/>
-      <c r="G130" s="13"/>
-      <c r="H130" s="13"/>
-      <c r="I130" s="13"/>
-      <c r="J130" s="14"/>
-      <c r="K130" s="14"/>
-      <c r="L130" s="14"/>
-      <c r="M130" s="14"/>
-      <c r="N130" s="14"/>
-      <c r="O130" s="14"/>
-      <c r="P130" s="14"/>
-      <c r="Q130" s="14"/>
-      <c r="R130" s="14"/>
-      <c r="S130" s="14"/>
-      <c r="T130" s="14"/>
-      <c r="U130" s="15"/>
-      <c r="V130" s="3"/>
-      <c r="W130" s="16"/>
+      <c r="W130" s="14"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F131" s="13"/>
-      <c r="G131" s="13"/>
-      <c r="H131" s="13"/>
-      <c r="I131" s="13"/>
-      <c r="J131" s="14"/>
-      <c r="K131" s="14"/>
-      <c r="L131" s="14"/>
-      <c r="M131" s="14"/>
-      <c r="N131" s="14"/>
-      <c r="O131" s="14"/>
-      <c r="P131" s="14"/>
-      <c r="Q131" s="14"/>
-      <c r="R131" s="14"/>
-      <c r="S131" s="14"/>
-      <c r="T131" s="14"/>
-      <c r="U131" s="15"/>
-      <c r="V131" s="3"/>
-      <c r="W131" s="16"/>
+      <c r="W131" s="14"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F132" s="13"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="13"/>
-      <c r="J132" s="14"/>
-      <c r="K132" s="14"/>
-      <c r="L132" s="14"/>
-      <c r="M132" s="14"/>
-      <c r="N132" s="14"/>
-      <c r="O132" s="14"/>
-      <c r="P132" s="14"/>
-      <c r="Q132" s="14"/>
-      <c r="R132" s="14"/>
-      <c r="S132" s="14"/>
-      <c r="T132" s="14"/>
-      <c r="U132" s="15"/>
-      <c r="V132" s="3"/>
-      <c r="W132" s="16"/>
+      <c r="W132" s="14"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F133" s="13"/>
-      <c r="G133" s="13"/>
-      <c r="H133" s="13"/>
-      <c r="I133" s="13"/>
-      <c r="J133" s="14"/>
-      <c r="K133" s="14"/>
-      <c r="L133" s="14"/>
-      <c r="M133" s="14"/>
-      <c r="N133" s="14"/>
-      <c r="O133" s="14"/>
-      <c r="P133" s="14"/>
-      <c r="Q133" s="14"/>
-      <c r="R133" s="14"/>
-      <c r="S133" s="14"/>
-      <c r="T133" s="14"/>
-      <c r="U133" s="15"/>
-      <c r="V133" s="3"/>
-      <c r="W133" s="16"/>
+      <c r="W133" s="14"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F134" s="13"/>
-      <c r="G134" s="13"/>
-      <c r="H134" s="13"/>
-      <c r="I134" s="13"/>
-      <c r="J134" s="14"/>
-      <c r="K134" s="14"/>
-      <c r="L134" s="14"/>
-      <c r="M134" s="14"/>
-      <c r="N134" s="14"/>
-      <c r="O134" s="14"/>
-      <c r="P134" s="14"/>
-      <c r="Q134" s="14"/>
-      <c r="R134" s="14"/>
-      <c r="S134" s="14"/>
-      <c r="T134" s="14"/>
-      <c r="U134" s="15"/>
-      <c r="V134" s="3"/>
-      <c r="W134" s="16"/>
+      <c r="W134" s="14"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F135" s="13"/>
-      <c r="G135" s="13"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="13"/>
-      <c r="J135" s="14"/>
-      <c r="K135" s="14"/>
-      <c r="L135" s="14"/>
-      <c r="M135" s="14"/>
-      <c r="N135" s="14"/>
-      <c r="O135" s="14"/>
-      <c r="P135" s="14"/>
-      <c r="Q135" s="14"/>
-      <c r="R135" s="14"/>
-      <c r="S135" s="14"/>
-      <c r="T135" s="14"/>
-      <c r="U135" s="15"/>
-      <c r="V135" s="3"/>
-      <c r="W135" s="16"/>
+      <c r="W135" s="14"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F136" s="13"/>
-      <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
-      <c r="I136" s="13"/>
-      <c r="J136" s="14"/>
-      <c r="K136" s="14"/>
-      <c r="L136" s="14"/>
-      <c r="M136" s="14"/>
-      <c r="N136" s="14"/>
-      <c r="O136" s="14"/>
-      <c r="P136" s="14"/>
-      <c r="Q136" s="14"/>
-      <c r="R136" s="14"/>
-      <c r="S136" s="14"/>
-      <c r="T136" s="14"/>
-      <c r="U136" s="15"/>
-      <c r="V136" s="3"/>
-      <c r="W136" s="16"/>
+      <c r="W136" s="14"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F137" s="13"/>
-      <c r="G137" s="13"/>
-      <c r="H137" s="13"/>
-      <c r="I137" s="13"/>
-      <c r="J137" s="14"/>
-      <c r="K137" s="14"/>
-      <c r="L137" s="14"/>
-      <c r="M137" s="14"/>
-      <c r="N137" s="14"/>
-      <c r="O137" s="14"/>
-      <c r="P137" s="14"/>
-      <c r="Q137" s="14"/>
-      <c r="R137" s="14"/>
-      <c r="S137" s="14"/>
-      <c r="T137" s="14"/>
-      <c r="U137" s="15"/>
-      <c r="V137" s="3"/>
-      <c r="W137" s="16"/>
+      <c r="W137" s="14"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F138" s="13"/>
-      <c r="G138" s="13"/>
-      <c r="H138" s="13"/>
-      <c r="I138" s="13"/>
-      <c r="J138" s="14"/>
-      <c r="K138" s="14"/>
-      <c r="L138" s="14"/>
-      <c r="M138" s="14"/>
-      <c r="N138" s="14"/>
-      <c r="O138" s="14"/>
-      <c r="P138" s="14"/>
-      <c r="Q138" s="14"/>
-      <c r="R138" s="14"/>
-      <c r="S138" s="14"/>
-      <c r="T138" s="14"/>
-      <c r="U138" s="15"/>
-      <c r="V138" s="3"/>
-      <c r="W138" s="16"/>
+      <c r="W138" s="14"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F139" s="13"/>
-      <c r="G139" s="13"/>
-      <c r="H139" s="13"/>
-      <c r="I139" s="13"/>
-      <c r="J139" s="14"/>
-      <c r="K139" s="14"/>
-      <c r="L139" s="14"/>
-      <c r="M139" s="14"/>
-      <c r="N139" s="14"/>
-      <c r="O139" s="14"/>
-      <c r="P139" s="14"/>
-      <c r="Q139" s="14"/>
-      <c r="R139" s="14"/>
-      <c r="S139" s="14"/>
-      <c r="T139" s="14"/>
-      <c r="U139" s="15"/>
-      <c r="V139" s="3"/>
-      <c r="W139" s="16"/>
+      <c r="W139" s="14"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F140" s="13"/>
-      <c r="G140" s="13"/>
-      <c r="H140" s="13"/>
-      <c r="I140" s="13"/>
-      <c r="J140" s="14"/>
-      <c r="K140" s="14"/>
-      <c r="L140" s="14"/>
-      <c r="M140" s="14"/>
-      <c r="N140" s="14"/>
-      <c r="O140" s="14"/>
-      <c r="P140" s="14"/>
-      <c r="Q140" s="14"/>
-      <c r="R140" s="14"/>
-      <c r="S140" s="14"/>
-      <c r="T140" s="14"/>
-      <c r="U140" s="15"/>
-      <c r="V140" s="3"/>
-      <c r="W140" s="16"/>
+      <c r="W140" s="14"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F141" s="13"/>
-      <c r="G141" s="13"/>
-      <c r="H141" s="13"/>
-      <c r="I141" s="13"/>
-      <c r="J141" s="14"/>
-      <c r="K141" s="14"/>
-      <c r="L141" s="14"/>
-      <c r="M141" s="14"/>
-      <c r="N141" s="14"/>
-      <c r="O141" s="14"/>
-      <c r="P141" s="14"/>
-      <c r="Q141" s="14"/>
-      <c r="R141" s="14"/>
-      <c r="S141" s="14"/>
-      <c r="T141" s="14"/>
-      <c r="U141" s="15"/>
-      <c r="V141" s="3"/>
-      <c r="W141" s="16"/>
+      <c r="W141" s="14"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F142" s="13"/>
-      <c r="G142" s="13"/>
-      <c r="H142" s="13"/>
-      <c r="I142" s="13"/>
-      <c r="J142" s="14"/>
-      <c r="K142" s="14"/>
-      <c r="L142" s="14"/>
-      <c r="M142" s="14"/>
-      <c r="N142" s="14"/>
-      <c r="O142" s="14"/>
-      <c r="P142" s="14"/>
-      <c r="Q142" s="14"/>
-      <c r="R142" s="14"/>
-      <c r="S142" s="14"/>
-      <c r="T142" s="14"/>
-      <c r="U142" s="15"/>
-      <c r="V142" s="3"/>
-      <c r="W142" s="16"/>
+      <c r="W142" s="14"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F143" s="13"/>
-      <c r="G143" s="13"/>
-      <c r="H143" s="13"/>
-      <c r="I143" s="13"/>
-      <c r="J143" s="14"/>
-      <c r="K143" s="14"/>
-      <c r="L143" s="14"/>
-      <c r="M143" s="14"/>
-      <c r="N143" s="14"/>
-      <c r="O143" s="14"/>
-      <c r="P143" s="14"/>
-      <c r="Q143" s="14"/>
-      <c r="R143" s="14"/>
-      <c r="S143" s="14"/>
-      <c r="T143" s="14"/>
-      <c r="U143" s="15"/>
-      <c r="V143" s="3"/>
-      <c r="W143" s="16"/>
+      <c r="W143" s="14"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F144" s="13"/>
-      <c r="G144" s="13"/>
-      <c r="H144" s="13"/>
-      <c r="I144" s="13"/>
-      <c r="J144" s="14"/>
-      <c r="K144" s="14"/>
-      <c r="L144" s="14"/>
-      <c r="M144" s="14"/>
-      <c r="N144" s="14"/>
-      <c r="O144" s="14"/>
-      <c r="P144" s="14"/>
-      <c r="Q144" s="14"/>
-      <c r="R144" s="14"/>
-      <c r="S144" s="14"/>
-      <c r="T144" s="14"/>
-      <c r="U144" s="15"/>
-      <c r="V144" s="3"/>
-      <c r="W144" s="16"/>
+      <c r="W144" s="14"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F145" s="13"/>
-      <c r="G145" s="13"/>
-      <c r="H145" s="13"/>
-      <c r="I145" s="13"/>
-      <c r="J145" s="14"/>
-      <c r="K145" s="14"/>
-      <c r="L145" s="14"/>
-      <c r="M145" s="14"/>
-      <c r="N145" s="14"/>
-      <c r="O145" s="14"/>
-      <c r="P145" s="14"/>
-      <c r="Q145" s="14"/>
-      <c r="R145" s="14"/>
-      <c r="S145" s="14"/>
-      <c r="T145" s="14"/>
-      <c r="U145" s="15"/>
-      <c r="V145" s="3"/>
-      <c r="W145" s="16"/>
+      <c r="W145" s="14"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F146" s="13"/>
-      <c r="G146" s="13"/>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
-      <c r="J146" s="14"/>
-      <c r="K146" s="14"/>
-      <c r="L146" s="14"/>
-      <c r="M146" s="14"/>
-      <c r="N146" s="14"/>
-      <c r="O146" s="14"/>
-      <c r="P146" s="14"/>
-      <c r="Q146" s="14"/>
-      <c r="R146" s="14"/>
-      <c r="S146" s="14"/>
-      <c r="T146" s="14"/>
-      <c r="U146" s="15"/>
-      <c r="V146" s="3"/>
-      <c r="W146" s="16"/>
+      <c r="W146" s="14"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F147" s="13"/>
-      <c r="G147" s="13"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="13"/>
-      <c r="J147" s="14"/>
-      <c r="K147" s="14"/>
-      <c r="L147" s="14"/>
-      <c r="M147" s="14"/>
-      <c r="N147" s="14"/>
-      <c r="O147" s="14"/>
-      <c r="P147" s="14"/>
-      <c r="Q147" s="14"/>
-      <c r="R147" s="14"/>
-      <c r="S147" s="14"/>
-      <c r="T147" s="14"/>
-      <c r="U147" s="15"/>
-      <c r="V147" s="3"/>
-      <c r="W147" s="16"/>
+      <c r="W147" s="14"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F148" s="13"/>
-      <c r="G148" s="13"/>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
-      <c r="J148" s="14"/>
-      <c r="K148" s="14"/>
-      <c r="L148" s="14"/>
-      <c r="M148" s="14"/>
-      <c r="N148" s="14"/>
-      <c r="O148" s="14"/>
-      <c r="P148" s="14"/>
-      <c r="Q148" s="14"/>
-      <c r="R148" s="14"/>
-      <c r="S148" s="14"/>
-      <c r="T148" s="14"/>
-      <c r="U148" s="15"/>
-      <c r="V148" s="3"/>
-      <c r="W148" s="16"/>
+      <c r="W148" s="14"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F149" s="13"/>
-      <c r="G149" s="13"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="14"/>
-      <c r="K149" s="14"/>
-      <c r="L149" s="14"/>
-      <c r="M149" s="14"/>
-      <c r="N149" s="14"/>
-      <c r="O149" s="14"/>
-      <c r="P149" s="14"/>
-      <c r="Q149" s="14"/>
-      <c r="R149" s="14"/>
-      <c r="S149" s="14"/>
-      <c r="T149" s="14"/>
-      <c r="U149" s="15"/>
-      <c r="V149" s="3"/>
-      <c r="W149" s="16"/>
+      <c r="W149" s="14"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F150" s="13"/>
-      <c r="G150" s="13"/>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-      <c r="J150" s="14"/>
-      <c r="K150" s="14"/>
-      <c r="L150" s="14"/>
-      <c r="M150" s="14"/>
-      <c r="N150" s="14"/>
-      <c r="O150" s="14"/>
-      <c r="P150" s="14"/>
-      <c r="Q150" s="14"/>
-      <c r="R150" s="14"/>
-      <c r="S150" s="14"/>
-      <c r="T150" s="14"/>
-      <c r="U150" s="15"/>
-      <c r="V150" s="3"/>
-      <c r="W150" s="16"/>
+      <c r="W150" s="14"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F151" s="13"/>
-      <c r="G151" s="13"/>
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
-      <c r="J151" s="14"/>
-      <c r="K151" s="14"/>
-      <c r="L151" s="14"/>
-      <c r="M151" s="14"/>
-      <c r="N151" s="14"/>
-      <c r="O151" s="14"/>
-      <c r="P151" s="14"/>
-      <c r="Q151" s="14"/>
-      <c r="R151" s="14"/>
-      <c r="S151" s="14"/>
-      <c r="T151" s="14"/>
-      <c r="U151" s="15"/>
-      <c r="V151" s="3"/>
-      <c r="W151" s="16"/>
+      <c r="W151" s="14"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F152" s="13"/>
-      <c r="G152" s="13"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-      <c r="J152" s="14"/>
-      <c r="K152" s="14"/>
-      <c r="L152" s="14"/>
-      <c r="M152" s="14"/>
-      <c r="N152" s="14"/>
-      <c r="O152" s="14"/>
-      <c r="P152" s="14"/>
-      <c r="Q152" s="14"/>
-      <c r="R152" s="14"/>
-      <c r="S152" s="14"/>
-      <c r="T152" s="14"/>
-      <c r="U152" s="15"/>
-      <c r="V152" s="3"/>
-      <c r="W152" s="16"/>
+      <c r="W152" s="14"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F153" s="13"/>
-      <c r="G153" s="13"/>
-      <c r="H153" s="13"/>
-      <c r="I153" s="13"/>
-      <c r="J153" s="14"/>
-      <c r="K153" s="14"/>
-      <c r="L153" s="14"/>
-      <c r="M153" s="14"/>
-      <c r="N153" s="14"/>
-      <c r="O153" s="14"/>
-      <c r="P153" s="14"/>
-      <c r="Q153" s="14"/>
-      <c r="R153" s="14"/>
-      <c r="S153" s="14"/>
-      <c r="T153" s="14"/>
-      <c r="U153" s="15"/>
-      <c r="V153" s="3"/>
-      <c r="W153" s="16"/>
+      <c r="W153" s="14"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F154" s="13"/>
-      <c r="G154" s="13"/>
-      <c r="H154" s="13"/>
-      <c r="I154" s="13"/>
-      <c r="J154" s="14"/>
-      <c r="K154" s="14"/>
-      <c r="L154" s="14"/>
-      <c r="M154" s="14"/>
-      <c r="N154" s="14"/>
-      <c r="O154" s="14"/>
-      <c r="P154" s="14"/>
-      <c r="Q154" s="14"/>
-      <c r="R154" s="14"/>
-      <c r="S154" s="14"/>
-      <c r="T154" s="14"/>
-      <c r="U154" s="15"/>
-      <c r="V154" s="3"/>
-      <c r="W154" s="16"/>
+      <c r="W154" s="14"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F155" s="13"/>
-      <c r="G155" s="13"/>
-      <c r="H155" s="13"/>
-      <c r="I155" s="13"/>
-      <c r="J155" s="14"/>
-      <c r="K155" s="14"/>
-      <c r="L155" s="14"/>
-      <c r="M155" s="14"/>
-      <c r="N155" s="14"/>
-      <c r="O155" s="14"/>
-      <c r="P155" s="14"/>
-      <c r="Q155" s="14"/>
-      <c r="R155" s="14"/>
-      <c r="S155" s="14"/>
-      <c r="T155" s="14"/>
-      <c r="U155" s="15"/>
-      <c r="V155" s="3"/>
-      <c r="W155" s="16"/>
+      <c r="W155" s="14"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F156" s="13"/>
-      <c r="G156" s="13"/>
-      <c r="H156" s="13"/>
-      <c r="I156" s="13"/>
-      <c r="J156" s="14"/>
-      <c r="K156" s="14"/>
-      <c r="L156" s="14"/>
-      <c r="M156" s="14"/>
-      <c r="N156" s="14"/>
-      <c r="O156" s="14"/>
-      <c r="P156" s="14"/>
-      <c r="Q156" s="14"/>
-      <c r="R156" s="14"/>
-      <c r="S156" s="14"/>
-      <c r="T156" s="14"/>
-      <c r="U156" s="15"/>
-      <c r="V156" s="3"/>
-      <c r="W156" s="16"/>
+      <c r="W156" s="14"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F157" s="13"/>
-      <c r="G157" s="13"/>
-      <c r="H157" s="13"/>
-      <c r="I157" s="13"/>
-      <c r="J157" s="14"/>
-      <c r="K157" s="14"/>
-      <c r="L157" s="14"/>
-      <c r="M157" s="14"/>
-      <c r="N157" s="14"/>
-      <c r="O157" s="14"/>
-      <c r="P157" s="14"/>
-      <c r="Q157" s="14"/>
-      <c r="R157" s="14"/>
-      <c r="S157" s="14"/>
-      <c r="T157" s="14"/>
-      <c r="U157" s="15"/>
-      <c r="V157" s="3"/>
-      <c r="W157" s="16"/>
+      <c r="W157" s="14"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F158" s="13"/>
-      <c r="G158" s="13"/>
-      <c r="H158" s="13"/>
-      <c r="I158" s="13"/>
-      <c r="J158" s="14"/>
-      <c r="K158" s="14"/>
-      <c r="L158" s="14"/>
-      <c r="M158" s="14"/>
-      <c r="N158" s="14"/>
-      <c r="O158" s="14"/>
-      <c r="P158" s="14"/>
-      <c r="Q158" s="14"/>
-      <c r="R158" s="14"/>
-      <c r="S158" s="14"/>
-      <c r="T158" s="14"/>
-      <c r="U158" s="15"/>
-      <c r="V158" s="3"/>
-      <c r="W158" s="16"/>
+      <c r="W158" s="14"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F159" s="13"/>
-      <c r="G159" s="13"/>
-      <c r="H159" s="13"/>
-      <c r="I159" s="13"/>
-      <c r="J159" s="14"/>
-      <c r="K159" s="14"/>
-      <c r="L159" s="14"/>
-      <c r="M159" s="14"/>
-      <c r="N159" s="14"/>
-      <c r="O159" s="14"/>
-      <c r="P159" s="14"/>
-      <c r="Q159" s="14"/>
-      <c r="R159" s="14"/>
-      <c r="S159" s="14"/>
-      <c r="T159" s="14"/>
-      <c r="U159" s="15"/>
-      <c r="V159" s="3"/>
-      <c r="W159" s="16"/>
+      <c r="W159" s="14"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F160" s="13"/>
-      <c r="G160" s="13"/>
-      <c r="H160" s="13"/>
-      <c r="I160" s="13"/>
-      <c r="J160" s="14"/>
-      <c r="K160" s="14"/>
-      <c r="L160" s="14"/>
-      <c r="M160" s="14"/>
-      <c r="N160" s="14"/>
-      <c r="O160" s="14"/>
-      <c r="P160" s="14"/>
-      <c r="Q160" s="14"/>
-      <c r="R160" s="14"/>
-      <c r="S160" s="14"/>
-      <c r="T160" s="14"/>
-      <c r="U160" s="15"/>
-      <c r="V160" s="3"/>
-      <c r="W160" s="16"/>
+      <c r="W160" s="14"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F161" s="13"/>
-      <c r="G161" s="13"/>
-      <c r="H161" s="13"/>
-      <c r="I161" s="13"/>
-      <c r="J161" s="14"/>
-      <c r="K161" s="14"/>
-      <c r="L161" s="14"/>
-      <c r="M161" s="14"/>
-      <c r="N161" s="14"/>
-      <c r="O161" s="14"/>
-      <c r="P161" s="14"/>
-      <c r="Q161" s="14"/>
-      <c r="R161" s="14"/>
-      <c r="S161" s="14"/>
-      <c r="T161" s="14"/>
-      <c r="U161" s="15"/>
-      <c r="V161" s="3"/>
-      <c r="W161" s="16"/>
+      <c r="W161" s="14"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F162" s="13"/>
-      <c r="G162" s="13"/>
-      <c r="H162" s="13"/>
-      <c r="I162" s="13"/>
-      <c r="J162" s="14"/>
-      <c r="K162" s="14"/>
-      <c r="L162" s="14"/>
-      <c r="M162" s="14"/>
-      <c r="N162" s="14"/>
-      <c r="O162" s="14"/>
-      <c r="P162" s="14"/>
-      <c r="Q162" s="14"/>
-      <c r="R162" s="14"/>
-      <c r="S162" s="14"/>
-      <c r="T162" s="14"/>
-      <c r="U162" s="15"/>
-      <c r="V162" s="3"/>
-      <c r="W162" s="16"/>
+      <c r="W162" s="14"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F163" s="13"/>
-      <c r="G163" s="13"/>
-      <c r="H163" s="13"/>
-      <c r="I163" s="13"/>
-      <c r="J163" s="14"/>
-      <c r="K163" s="14"/>
-      <c r="L163" s="14"/>
-      <c r="M163" s="14"/>
-      <c r="N163" s="14"/>
-      <c r="O163" s="14"/>
-      <c r="P163" s="14"/>
-      <c r="Q163" s="14"/>
-      <c r="R163" s="14"/>
-      <c r="S163" s="14"/>
-      <c r="T163" s="14"/>
-      <c r="U163" s="15"/>
-      <c r="V163" s="3"/>
-      <c r="W163" s="16"/>
+      <c r="W163" s="14"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F164" s="13"/>
-      <c r="G164" s="13"/>
-      <c r="H164" s="13"/>
-      <c r="I164" s="13"/>
-      <c r="J164" s="14"/>
-      <c r="K164" s="14"/>
-      <c r="L164" s="14"/>
-      <c r="M164" s="14"/>
-      <c r="N164" s="14"/>
-      <c r="O164" s="14"/>
-      <c r="P164" s="14"/>
-      <c r="Q164" s="14"/>
-      <c r="R164" s="14"/>
-      <c r="S164" s="14"/>
-      <c r="T164" s="14"/>
-      <c r="U164" s="15"/>
-      <c r="V164" s="3"/>
-      <c r="W164" s="16"/>
+      <c r="W164" s="14"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F165" s="13"/>
-      <c r="G165" s="13"/>
-      <c r="H165" s="13"/>
-      <c r="I165" s="13"/>
-      <c r="J165" s="14"/>
-      <c r="K165" s="14"/>
-      <c r="L165" s="14"/>
-      <c r="M165" s="14"/>
-      <c r="N165" s="14"/>
-      <c r="O165" s="14"/>
-      <c r="P165" s="14"/>
-      <c r="Q165" s="14"/>
-      <c r="R165" s="14"/>
-      <c r="S165" s="14"/>
-      <c r="T165" s="14"/>
-      <c r="U165" s="15"/>
-      <c r="V165" s="3"/>
-      <c r="W165" s="16"/>
+      <c r="W165" s="14"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F166" s="13"/>
-      <c r="G166" s="13"/>
-      <c r="H166" s="13"/>
-      <c r="I166" s="13"/>
-      <c r="J166" s="14"/>
-      <c r="K166" s="14"/>
-      <c r="L166" s="14"/>
-      <c r="M166" s="14"/>
-      <c r="N166" s="14"/>
-      <c r="O166" s="14"/>
-      <c r="P166" s="14"/>
-      <c r="Q166" s="14"/>
-      <c r="R166" s="14"/>
-      <c r="S166" s="14"/>
-      <c r="T166" s="14"/>
-      <c r="U166" s="15"/>
-      <c r="V166" s="3"/>
-      <c r="W166" s="16"/>
+      <c r="W166" s="14"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F167" s="13"/>
-      <c r="G167" s="13"/>
-      <c r="H167" s="13"/>
-      <c r="I167" s="13"/>
-      <c r="J167" s="14"/>
-      <c r="K167" s="14"/>
-      <c r="L167" s="14"/>
-      <c r="M167" s="14"/>
-      <c r="N167" s="14"/>
-      <c r="O167" s="14"/>
-      <c r="P167" s="14"/>
-      <c r="Q167" s="14"/>
-      <c r="R167" s="14"/>
-      <c r="S167" s="14"/>
-      <c r="T167" s="14"/>
-      <c r="U167" s="15"/>
-      <c r="V167" s="3"/>
-      <c r="W167" s="16"/>
+      <c r="W167" s="14"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F168" s="13"/>
-      <c r="G168" s="13"/>
-      <c r="H168" s="13"/>
-      <c r="I168" s="13"/>
-      <c r="J168" s="14"/>
-      <c r="K168" s="14"/>
-      <c r="L168" s="14"/>
-      <c r="M168" s="14"/>
-      <c r="N168" s="14"/>
-      <c r="O168" s="14"/>
-      <c r="P168" s="14"/>
-      <c r="Q168" s="14"/>
-      <c r="R168" s="14"/>
-      <c r="S168" s="14"/>
-      <c r="T168" s="14"/>
-      <c r="U168" s="15"/>
-      <c r="V168" s="3"/>
-      <c r="W168" s="16"/>
+      <c r="W168" s="14"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F169" s="13"/>
-      <c r="G169" s="13"/>
-      <c r="H169" s="13"/>
-      <c r="I169" s="13"/>
-      <c r="J169" s="14"/>
-      <c r="K169" s="14"/>
-      <c r="L169" s="14"/>
-      <c r="M169" s="14"/>
-      <c r="N169" s="14"/>
-      <c r="O169" s="14"/>
-      <c r="P169" s="14"/>
-      <c r="Q169" s="14"/>
-      <c r="R169" s="14"/>
-      <c r="S169" s="14"/>
-      <c r="T169" s="14"/>
-      <c r="U169" s="15"/>
-      <c r="V169" s="3"/>
-      <c r="W169" s="16"/>
+      <c r="W169" s="14"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F170" s="13"/>
-      <c r="G170" s="13"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="13"/>
-      <c r="J170" s="14"/>
-      <c r="K170" s="14"/>
-      <c r="L170" s="14"/>
-      <c r="M170" s="14"/>
-      <c r="N170" s="14"/>
-      <c r="O170" s="14"/>
-      <c r="P170" s="14"/>
-      <c r="Q170" s="14"/>
-      <c r="R170" s="14"/>
-      <c r="S170" s="14"/>
-      <c r="T170" s="14"/>
-      <c r="U170" s="15"/>
-      <c r="V170" s="3"/>
-      <c r="W170" s="16"/>
+      <c r="W170" s="14"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F171" s="13"/>
-      <c r="G171" s="13"/>
-      <c r="H171" s="13"/>
-      <c r="I171" s="13"/>
-      <c r="J171" s="14"/>
-      <c r="K171" s="14"/>
-      <c r="L171" s="14"/>
-      <c r="M171" s="14"/>
-      <c r="N171" s="14"/>
-      <c r="O171" s="14"/>
-      <c r="P171" s="14"/>
-      <c r="Q171" s="14"/>
-      <c r="R171" s="14"/>
-      <c r="S171" s="14"/>
-      <c r="T171" s="14"/>
-      <c r="U171" s="15"/>
-      <c r="V171" s="3"/>
-      <c r="W171" s="16"/>
+      <c r="W171" s="14"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F172" s="13"/>
-      <c r="G172" s="13"/>
-      <c r="H172" s="13"/>
-      <c r="I172" s="13"/>
-      <c r="J172" s="14"/>
-      <c r="K172" s="14"/>
-      <c r="L172" s="14"/>
-      <c r="M172" s="14"/>
-      <c r="N172" s="14"/>
-      <c r="O172" s="14"/>
-      <c r="P172" s="14"/>
-      <c r="Q172" s="14"/>
-      <c r="R172" s="14"/>
-      <c r="S172" s="14"/>
-      <c r="T172" s="14"/>
-      <c r="U172" s="15"/>
-      <c r="V172" s="3"/>
-      <c r="W172" s="16"/>
+      <c r="W172" s="14"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F173" s="13"/>
-      <c r="G173" s="13"/>
-      <c r="H173" s="13"/>
-      <c r="I173" s="13"/>
-      <c r="J173" s="14"/>
-      <c r="K173" s="14"/>
-      <c r="L173" s="14"/>
-      <c r="M173" s="14"/>
-      <c r="N173" s="14"/>
-      <c r="O173" s="14"/>
-      <c r="P173" s="14"/>
-      <c r="Q173" s="14"/>
-      <c r="R173" s="14"/>
-      <c r="S173" s="14"/>
-      <c r="T173" s="14"/>
-      <c r="U173" s="15"/>
-      <c r="V173" s="3"/>
-      <c r="W173" s="16"/>
+      <c r="W173" s="14"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W174" s="14"/>
@@ -7577,181 +6871,227 @@
     <row r="534" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W534" s="14"/>
     </row>
-    <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W535" s="14"/>
-    </row>
-    <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W536" s="14"/>
-    </row>
-    <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W537" s="14"/>
-    </row>
-    <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W538" s="14"/>
-    </row>
-    <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W539" s="14"/>
-    </row>
-    <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W540" s="14"/>
-    </row>
-    <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W541" s="14"/>
-    </row>
-    <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W542" s="14"/>
-    </row>
-    <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W543" s="14"/>
-    </row>
-    <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W544" s="14"/>
-    </row>
-    <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W545" s="14"/>
-    </row>
-    <row r="546" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W546" s="14"/>
-    </row>
-    <row r="547" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W547" s="14"/>
-    </row>
-    <row r="548" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W548" s="14"/>
-    </row>
-    <row r="549" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W549" s="14"/>
-    </row>
-    <row r="550" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W550" s="14"/>
-    </row>
-    <row r="551" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W551" s="14"/>
-    </row>
-    <row r="552" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W552" s="14"/>
-    </row>
-    <row r="553" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W553" s="14"/>
-    </row>
-    <row r="554" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W554" s="14"/>
-    </row>
-    <row r="555" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W555" s="14"/>
-    </row>
-    <row r="556" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W556" s="14"/>
-    </row>
-    <row r="557" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W557" s="14"/>
-    </row>
-    <row r="558" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W558" s="14"/>
-    </row>
-    <row r="559" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W559" s="14"/>
-    </row>
-    <row r="560" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W560" s="14"/>
-    </row>
-    <row r="561" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W561" s="14"/>
-    </row>
-    <row r="562" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W562" s="14"/>
-    </row>
-    <row r="563" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W563" s="14"/>
-    </row>
-    <row r="564" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W564" s="14"/>
-    </row>
-    <row r="565" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W565" s="14"/>
-    </row>
-    <row r="566" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W566" s="14"/>
-    </row>
-    <row r="567" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W567" s="14"/>
-    </row>
-    <row r="568" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W568" s="14"/>
-    </row>
-    <row r="569" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W569" s="14"/>
-    </row>
-    <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W570" s="14"/>
-    </row>
-    <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W571" s="14"/>
-    </row>
-    <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W572" s="14"/>
-    </row>
-    <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W573" s="14"/>
-    </row>
-    <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W574" s="14"/>
-    </row>
-    <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W575" s="14"/>
-    </row>
-    <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W576" s="14"/>
-    </row>
-    <row r="577" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W577" s="14"/>
-    </row>
-    <row r="578" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W578" s="14"/>
-    </row>
-    <row r="579" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W579" s="14"/>
-    </row>
-    <row r="580" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W580" s="14"/>
-    </row>
-    <row r="581" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W581" s="14"/>
-    </row>
-    <row r="582" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W582" s="14"/>
-    </row>
-    <row r="583" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W583" s="14"/>
-    </row>
-    <row r="584" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W584" s="14"/>
-    </row>
-    <row r="585" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W585" s="14"/>
-    </row>
-    <row r="586" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W586" s="14"/>
-    </row>
-    <row r="587" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W587" s="14"/>
-    </row>
-    <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W588" s="14"/>
-    </row>
-    <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W589" s="14"/>
-    </row>
-    <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W590" s="14"/>
-    </row>
-    <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048363" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048364" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048365" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048366" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048367" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048368" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048369" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048370" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048371" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048372" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048373" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048374" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048375" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048376" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048378" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048379" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048380" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048381" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048382" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048383" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048384" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048385" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048386" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048387" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048388" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048389" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048392" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048393" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048394" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048395" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048396" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048397" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048398" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048399" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048400" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048401" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048402" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048403" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048404" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048405" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048406" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048407" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048408" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048409" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048410" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048411" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048412" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048413" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048414" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048415" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048416" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048417" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048418" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048419" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048420" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048421" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048422" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048423" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048424" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048425" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048426" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048427" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048428" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048429" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048430" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048431" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048432" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048433" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048434" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048435" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048436" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048437" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048438" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048439" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048440" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048441" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048442" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048443" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048444" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048445" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048446" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048447" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048448" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048449" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048450" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048451" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048452" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048453" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048454" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048455" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048456" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048457" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048458" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048459" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048460" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048461" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048462" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048463" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048464" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048465" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048466" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048467" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048468" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048469" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048470" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048471" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048472" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048473" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048474" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048475" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048476" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048477" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048478" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048479" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048480" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048481" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048482" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048483" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048484" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A9:W29"/>
+  <autoFilter ref="A9:W31"/>
   <mergeCells count="7">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -7762,15 +7102,15 @@
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J33 M10:N33 P10:R33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J31 M10:N31 P10:R31" type="list">
       <formula1>Sheet1!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T31" type="list">
       <formula1>Sheet1!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K31" type="list">
       <formula1>'LISTA VALORI'!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7793,46 +7133,46 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="s">
-        <v>95</v>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -7852,185 +7192,233 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G960"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="102"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="102"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>100</v>
+      <c r="C1" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>104</v>
+      <c r="A2" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>107</v>
+      <c r="A3" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>110</v>
+      <c r="A4" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>113</v>
+      <c r="A5" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>116</v>
+      <c r="C6" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>119</v>
+      <c r="A7" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>122</v>
+      <c r="A8" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>124</v>
+      <c r="B9" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>127</v>
+      <c r="A10" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>130</v>
+      <c r="A11" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="48"/>
+      <c r="A12" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="48"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A13" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>521</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>153</v>
+      </c>
+    </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8995,11 +8383,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9012,18 +8400,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10042,20 +9430,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d4db60622090a1f8a8d506ac1d64a349">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a3a9ed8bb952a3d76dd1e2fa3d624b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
     <xsd:import namespace="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
     <xsd:element name="properties">
@@ -10081,6 +9457,7 @@
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:UserStoryALM" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10168,6 +9545,11 @@
           <xsd:enumeration value="137048 - Stesura checklist RAP"/>
           <xsd:enumeration value="137049 - Sviluppo testcase RAP"/>
         </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -10311,7 +9693,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10320,25 +9702,20 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE213DB-5082-48B0-B2A5-099EBF944035}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10356,10 +9733,33 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Summary!$A$1:$G$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$33</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="133">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -70,8 +70,7 @@
     <t xml:space="preserve">2) Per tutti i casi di test coerenti con la/e tipologia/e di documento utilizzata/e dal software è necessario compilare SEMPRE la colonna APPLICABILITA' con SI o NO</t>
   </si>
   <si>
-    <t xml:space="preserve">3) Nel caso in cui tra le tipologie documentali oggetto di accreditamento per l'applicativo figurino PSS, RAP, RAD, RSA, LDO, LAB, VPS, SING_VACC, CERT_VACC, TPI, LETT_SCREEN, LETT_VACC, CCE  i relativi casi di test con id 476*, 417, 418, 460, 448, 450, 452,454, 456, 457, 458, 471, 479, 491, 506, 521   che recepiscono quanto previsto dal Decreto 07 settembre 2023, devono essere obbligatoriamente eseguiti e compilati (la colonna APPLICABILITA' deve essere valorizzata con SI). 
-*) Il test in questione è da intendersi obbligatorio per gli applicativi che si stanno accreditando per la prima volta per PSS; nel caso di applicativi già accreditati, sarà sufficiente sottomettere il caso di test 478 (Fast Track)</t>
+    <t xml:space="preserve">3) Nel caso in cui tra le tipologie documentali oggetto di accreditamento per l'applicativo figurino PSS, RAP, RAD, RSA, LDO, LAB, VPS, SING_VACC, CERT_VACC i relativi casi di test con id 444, 417, 418, 460, 448, 450, 452,454, 456, 457, 458, 471 che recepiscono quanto previsto dal Decreto 07 settembre 2023, devono essere obbligatoriamente eseguiti e compilati (la colonna APPLICABILITA' deve essere valorizzata con SI)</t>
   </si>
   <si>
     <t xml:space="preserve">4) Se il test è applicabile la colonna APPLICABILITA' deve essere compilata con SI e dovranno essere valorizzate:
@@ -84,7 +83,7 @@
     MESSAGGIO DI ERRORE da compilare con il messaggio di errore visualizzato dall’applicativo, solo per i casi KO (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT visibili all'utente (colonna ERRORE VISIBILE A UTENTE (SI/NO)=SI)
     GESTITO IN BACKOFFICE (SI/NO) da compilare solo per i casi KO (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
     PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO A FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO) da compilare solo per i casi KO (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
-  INVIO MANUALE DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO) da compilare solo per i casi KO  (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
+   INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO) da compilare solo per i casi KO  (ovvero con colonna CASO OK / KO= KO) e per i casi di test di TIMEOUT,
     GESTIONE ERRORE da compilare con la procedura che viene adottata per la gestione dell'errore, solo per i casi KO (ovvero con CASO OK / KO= KO) e per i casi di test di TIMEOUT,  specificando le modalità di invio del documento clinico al FSE a seguito della correzione dell'errore e chiarendo se è possibile per l'utente (medico) proseguire con il processo e produrre il documento. Esclusivamente per i casi di test di TIMEOUT, qualora non fosse prevista una coda di retry e la gestione dell'errore non fossa gestita da un operatore di backoffice, indicare le modalità attraverso cui è reso esplicito all’utente (medico) di effettuare nuovi tentativi di invio verso il FSE fino al ripristino del servizio di validazione.</t>
   </si>
   <si>
@@ -200,73 +199,13 @@
     <t xml:space="preserve">IDENTIFICATIVI SOFTWARE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">subject_application_id: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">YOOMULTIMEDIA-FSE-GATEWAY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">subject_application_vendor: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">YOO Multimedia SRL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">subject_application_version: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1.1.0</t>
-    </r>
+    <t xml:space="preserve">subject_application_id: YOOMULTIMEDIA-FSE-GATEWAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject_application_vendor: YOO Multimedia SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject_application_version: 1.1.0</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -317,10 +256,10 @@
     <t xml:space="preserve">GESTITO IN BACKOFFICE (SI/NO)</t>
   </si>
   <si>
-    <t xml:space="preserve">PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INVIO MANUALE DEL DOCUMENTO AL SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
+    <t xml:space="preserve"> PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)</t>
   </si>
   <si>
     <t xml:space="preserve">GESTIONE ERRORE</t>
@@ -344,275 +283,131 @@
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
-    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_PSS_KO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <u val="single"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Precondizioni:
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’applicativo effettua controlli preventivi sul dato inserito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 1" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Il fornitore utilizza un token jwt mancante di campi obbligatori, quindi non valido.
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-20T10:49:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f17cfcdc21dd44a0f6b102d0921ef63b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.3f47aed86b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
+Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 2" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <u val="single"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Descrizione di Business del caso di test: 
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-20T11:50:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87202318605b410218263c6a459226ae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" con un token jwt non valido a causa della mancanza di uno o più campi obbligatori al fine di testare la gestione dell'errore sul token (status code 403), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Al fine di rendere non valido il token è necessario non valorizzare nel JWT il campo "purpose_of_use".</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_CAMPO_PSS_KO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <u val="single"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Precondizioni:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Il fornitore utilizza un token jwt con dei campi valorizzati in maniera errata.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <u val="single"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Descrizione di Business del caso di test: 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" con un token jwt avente dei campi valorizzati in maniera errata al fine di testare la gestione dell'errore sul token (status code 403), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Al fine di rendere non valido il token è necessario valorizzare il campo "action_id" con la stringa "TEST" (valore non ammesso).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_PSS_TIMEOUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per questo caso di test è richiesta la sola descrizione del comportamento a fronte di un timeout, da inserire nelle colonne relative a:
-"ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 11" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 12" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori terminologici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori sintattici sui Dati (status code 400), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09T13:42:58Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92a0d9fa1ee781154fd41ff9bc8018a8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT23</t>
   </si>
   <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 23" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-09T13:42:58Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92a0d9fa1ee781154fd41ff9bc8018a8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT24</t>
   </si>
   <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. Il "CASO DI TEST 25" si riferisce a un esempio di CDA2 semplice, contenente esclusivamente sezioni ed elementi obbligatori previsti dalle specifiche nazionali (IG HL7 Italia)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Razionale di Applicabilità</t>
   </si>
   <si>
@@ -631,9 +426,6 @@
     <t xml:space="preserve">Campo valorizzabile tramite selezione da un set di valori ammessi</t>
   </si>
   <si>
-    <t xml:space="preserve">L’applicativo effettua controlli preventivi sul dato inserito</t>
-  </si>
-  <si>
     <t xml:space="preserve">Altro (specificare)</t>
   </si>
   <si>
@@ -649,7 +441,7 @@
     <t xml:space="preserve">Versione:</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3.0</t>
+    <t xml:space="preserve">8.2.5</t>
   </si>
   <si>
     <t xml:space="preserve">LAB</t>
@@ -661,7 +453,7 @@
     <t xml:space="preserve">4, 452</t>
   </si>
   <si>
-    <t xml:space="preserve">28,36,44,53,55,56,57,59,60,61,62, 466, 473</t>
+    <t xml:space="preserve">28,36,44,53,55,56,57,58,59,60,61,62, 466</t>
   </si>
   <si>
     <t xml:space="preserve">LDO</t>
@@ -679,7 +471,7 @@
     <t xml:space="preserve">471, 472</t>
   </si>
   <si>
-    <t xml:space="preserve">31,39,47,76,78,79,80,81,83,84,85,86,87,88,89,90,91,92,93, 462, 474</t>
+    <t xml:space="preserve">31,39,47,76,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93, 462</t>
   </si>
   <si>
     <t xml:space="preserve">CERT_VAC</t>
@@ -715,10 +507,10 @@
     <t xml:space="preserve">448, 449</t>
   </si>
   <si>
-    <t xml:space="preserve">32,40,48,152,154,155,156,157,159,160,161,162,163,164,165,166,167,168,169, 461, 468, 475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">476,477,478</t>
+    <t xml:space="preserve">32,40,48,152,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169, 461, 468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">444, 445</t>
   </si>
   <si>
     <t xml:space="preserve">30,38,46,175,177,178,179,180,181,182,183,184,185,186,187,188,189,190, 469</t>
@@ -740,39 +532,6 @@
   </si>
   <si>
     <t xml:space="preserve">423,424,425,427,428,429,430,431,432,433,434,435,436,437,438,439,440,441,442,443,448,449, 470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">479, 480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">481,482,483,484,485,486,487,488,489,490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LETT_SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">491, 492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493,494,495,496,497,498,499,500,501,502,503,504,505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LETT_VACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">506, 507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">508,509,510,511,512,513,514,515,516,517,518,519,520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">522,523,524,525,526,527,528,529,530</t>
   </si>
   <si>
     <t xml:space="preserve">PASS</t>
@@ -790,7 +549,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,25 +617,12 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -894,19 +640,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <u val="single"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1089,201 +827,197 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1594,34 +1328,34 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="130.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="0" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="130.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="1" width="8.86"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="65.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="33.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="206.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1630,34 +1364,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1676,11 +1410,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B996"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="194.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="194.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="8.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1689,12 +1423,12 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1"/>
+      <c r="B3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
@@ -2747,22 +2481,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W1048576"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:W595"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="63.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="104.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="33.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="27.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="11" style="0" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="27.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="33.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="36.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="0" width="31.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="30.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="63.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="78.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="33.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="27.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="11" style="1" width="36.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="27.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="33.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="36.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="1" width="31.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="30.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2783,7 +2517,7 @@
       <c r="S1" s="14"/>
       <c r="T1" s="14"/>
       <c r="U1" s="15"/>
-      <c r="V1" s="2"/>
+      <c r="V1" s="3"/>
       <c r="W1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2811,7 +2545,7 @@
       <c r="S2" s="14"/>
       <c r="T2" s="14"/>
       <c r="U2" s="15"/>
-      <c r="V2" s="2"/>
+      <c r="V2" s="3"/>
       <c r="W2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2839,7 +2573,7 @@
       <c r="S3" s="14"/>
       <c r="T3" s="14"/>
       <c r="U3" s="15"/>
-      <c r="V3" s="2"/>
+      <c r="V3" s="3"/>
       <c r="W3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2866,7 +2600,7 @@
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
       <c r="U4" s="15"/>
-      <c r="V4" s="2"/>
+      <c r="V4" s="3"/>
       <c r="W4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2892,7 +2626,7 @@
       <c r="S5" s="14"/>
       <c r="T5" s="14"/>
       <c r="U5" s="15"/>
-      <c r="V5" s="2"/>
+      <c r="V5" s="3"/>
       <c r="W5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2915,7 +2649,7 @@
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="15"/>
-      <c r="V6" s="2"/>
+      <c r="V6" s="3"/>
       <c r="W6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2938,10 +2672,10 @@
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="15"/>
-      <c r="V7" s="2"/>
+      <c r="V7" s="3"/>
       <c r="W7" s="16"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -2958,10 +2692,10 @@
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="15"/>
-      <c r="V8" s="2"/>
+      <c r="V8" s="3"/>
       <c r="W8" s="16"/>
     </row>
-    <row r="9" s="27" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" s="27" customFormat="true" ht="73.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
         <v>24</v>
       </c>
@@ -3032,7 +2766,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="n">
         <v>30</v>
       </c>
@@ -3045,33 +2779,33 @@
       <c r="D10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="33" t="s">
+      <c r="K10" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="33" t="s">
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="n">
         <v>38</v>
       </c>
@@ -3084,33 +2818,33 @@
       <c r="D11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="30" t="s">
-        <v>54</v>
-      </c>
+      <c r="E11" s="30"/>
       <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="33" t="s">
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="33" t="s">
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="n">
         <v>46</v>
       </c>
@@ -3121,37 +2855,47 @@
         <v>48</v>
       </c>
       <c r="D12" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="30"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="V12" s="35"/>
-      <c r="W12" s="33" t="s">
+      <c r="Q12" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="S12" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="T12" s="34"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="n">
         <v>175</v>
       </c>
@@ -3162,35 +2906,35 @@
         <v>48</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>59</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E13" s="30"/>
       <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="33" t="s">
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="33" t="s">
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="n">
         <v>177</v>
       </c>
@@ -3201,35 +2945,35 @@
         <v>48</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>61</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E14" s="30"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="33" t="s">
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="33" t="s">
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="n">
         <v>178</v>
       </c>
@@ -3240,35 +2984,35 @@
         <v>48</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>63</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E15" s="30"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="33" t="s">
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="33" t="s">
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="n">
         <v>179</v>
       </c>
@@ -3279,35 +3023,35 @@
         <v>48</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>65</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E16" s="30"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="33" t="s">
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="33" t="s">
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="36"/>
+      <c r="W16" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="n">
         <v>180</v>
       </c>
@@ -3318,35 +3062,35 @@
         <v>48</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>67</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E17" s="30"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="33" t="s">
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="33" t="s">
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="36"/>
+      <c r="W17" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="n">
         <v>181</v>
       </c>
@@ -3357,35 +3101,35 @@
         <v>48</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>69</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E18" s="30"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33" t="s">
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="33" t="s">
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="n">
         <v>182</v>
       </c>
@@ -3396,35 +3140,35 @@
         <v>48</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>71</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E19" s="30"/>
       <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33" t="s">
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="33" t="s">
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="n">
         <v>183</v>
       </c>
@@ -3435,35 +3179,35 @@
         <v>48</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>73</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="E20" s="30"/>
       <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33" t="s">
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="33" t="s">
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="n">
         <v>184</v>
       </c>
@@ -3474,35 +3218,35 @@
         <v>48</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>75</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E21" s="30"/>
       <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33" t="s">
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="33" t="s">
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="n">
         <v>185</v>
       </c>
@@ -3513,35 +3257,35 @@
         <v>48</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>77</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="E22" s="30"/>
       <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33" t="s">
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="33" t="s">
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="n">
         <v>186</v>
       </c>
@@ -3552,35 +3296,35 @@
         <v>48</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>79</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E23" s="30"/>
       <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="33" t="s">
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="33" t="s">
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="n">
         <v>187</v>
       </c>
@@ -3591,35 +3335,35 @@
         <v>48</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>81</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="E24" s="30"/>
       <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33" t="s">
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K24" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="33" t="s">
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="n">
         <v>188</v>
       </c>
@@ -3630,35 +3374,35 @@
         <v>48</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>83</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="E25" s="30"/>
       <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33" t="s">
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="33" t="s">
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="n">
         <v>189</v>
       </c>
@@ -3669,35 +3413,35 @@
         <v>48</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>85</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E26" s="30"/>
       <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="33" t="s">
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="33" t="s">
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="n">
         <v>190</v>
       </c>
@@ -3708,37 +3452,37 @@
         <v>48</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>87</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E27" s="30"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="33" t="s">
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="33" t="s">
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="n">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>47</v>
@@ -3747,37 +3491,47 @@
         <v>48</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>46073</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="J28" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="33"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="28" t="s">
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="37.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="n">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>47</v>
@@ -3786,45 +3540,47 @@
         <v>48</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="37" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>46073</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="36"/>
+      <c r="W29" s="34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="n">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>47</v>
@@ -3833,37 +3589,37 @@
         <v>48</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>97</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="E30" s="30"/>
       <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="33" t="s">
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B31" s="28" t="s">
         <v>47</v>
@@ -3872,73 +3628,121 @@
         <v>48</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="16"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="n">
+        <v>477</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="30"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K32" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="36"/>
+      <c r="W32" s="34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="n">
+        <v>478</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="30"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K33" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="36"/>
+      <c r="W33" s="34" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F34" s="13"/>
@@ -3957,7 +3761,7 @@
       <c r="S34" s="14"/>
       <c r="T34" s="14"/>
       <c r="U34" s="15"/>
-      <c r="V34" s="2"/>
+      <c r="V34" s="3"/>
       <c r="W34" s="16"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3977,7 +3781,7 @@
       <c r="S35" s="14"/>
       <c r="T35" s="14"/>
       <c r="U35" s="15"/>
-      <c r="V35" s="2"/>
+      <c r="V35" s="3"/>
       <c r="W35" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3997,7 +3801,7 @@
       <c r="S36" s="14"/>
       <c r="T36" s="14"/>
       <c r="U36" s="15"/>
-      <c r="V36" s="2"/>
+      <c r="V36" s="3"/>
       <c r="W36" s="16"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4017,7 +3821,7 @@
       <c r="S37" s="14"/>
       <c r="T37" s="14"/>
       <c r="U37" s="15"/>
-      <c r="V37" s="2"/>
+      <c r="V37" s="3"/>
       <c r="W37" s="16"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4037,7 +3841,7 @@
       <c r="S38" s="14"/>
       <c r="T38" s="14"/>
       <c r="U38" s="15"/>
-      <c r="V38" s="2"/>
+      <c r="V38" s="3"/>
       <c r="W38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4057,7 +3861,7 @@
       <c r="S39" s="14"/>
       <c r="T39" s="14"/>
       <c r="U39" s="15"/>
-      <c r="V39" s="2"/>
+      <c r="V39" s="3"/>
       <c r="W39" s="16"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4077,7 +3881,7 @@
       <c r="S40" s="14"/>
       <c r="T40" s="14"/>
       <c r="U40" s="15"/>
-      <c r="V40" s="2"/>
+      <c r="V40" s="3"/>
       <c r="W40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4097,7 +3901,7 @@
       <c r="S41" s="14"/>
       <c r="T41" s="14"/>
       <c r="U41" s="15"/>
-      <c r="V41" s="2"/>
+      <c r="V41" s="3"/>
       <c r="W41" s="16"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4117,7 +3921,7 @@
       <c r="S42" s="14"/>
       <c r="T42" s="14"/>
       <c r="U42" s="15"/>
-      <c r="V42" s="2"/>
+      <c r="V42" s="3"/>
       <c r="W42" s="16"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4137,7 +3941,7 @@
       <c r="S43" s="14"/>
       <c r="T43" s="14"/>
       <c r="U43" s="15"/>
-      <c r="V43" s="2"/>
+      <c r="V43" s="3"/>
       <c r="W43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4157,7 +3961,7 @@
       <c r="S44" s="14"/>
       <c r="T44" s="14"/>
       <c r="U44" s="15"/>
-      <c r="V44" s="2"/>
+      <c r="V44" s="3"/>
       <c r="W44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4177,7 +3981,7 @@
       <c r="S45" s="14"/>
       <c r="T45" s="14"/>
       <c r="U45" s="15"/>
-      <c r="V45" s="2"/>
+      <c r="V45" s="3"/>
       <c r="W45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4197,7 +4001,7 @@
       <c r="S46" s="14"/>
       <c r="T46" s="14"/>
       <c r="U46" s="15"/>
-      <c r="V46" s="2"/>
+      <c r="V46" s="3"/>
       <c r="W46" s="16"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4217,7 +4021,7 @@
       <c r="S47" s="14"/>
       <c r="T47" s="14"/>
       <c r="U47" s="15"/>
-      <c r="V47" s="2"/>
+      <c r="V47" s="3"/>
       <c r="W47" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4237,7 +4041,7 @@
       <c r="S48" s="14"/>
       <c r="T48" s="14"/>
       <c r="U48" s="15"/>
-      <c r="V48" s="2"/>
+      <c r="V48" s="3"/>
       <c r="W48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4257,7 +4061,7 @@
       <c r="S49" s="14"/>
       <c r="T49" s="14"/>
       <c r="U49" s="15"/>
-      <c r="V49" s="2"/>
+      <c r="V49" s="3"/>
       <c r="W49" s="16"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4277,7 +4081,7 @@
       <c r="S50" s="14"/>
       <c r="T50" s="14"/>
       <c r="U50" s="15"/>
-      <c r="V50" s="2"/>
+      <c r="V50" s="3"/>
       <c r="W50" s="16"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4297,7 +4101,7 @@
       <c r="S51" s="14"/>
       <c r="T51" s="14"/>
       <c r="U51" s="15"/>
-      <c r="V51" s="2"/>
+      <c r="V51" s="3"/>
       <c r="W51" s="16"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4317,7 +4121,7 @@
       <c r="S52" s="14"/>
       <c r="T52" s="14"/>
       <c r="U52" s="15"/>
-      <c r="V52" s="2"/>
+      <c r="V52" s="3"/>
       <c r="W52" s="16"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4337,7 +4141,7 @@
       <c r="S53" s="14"/>
       <c r="T53" s="14"/>
       <c r="U53" s="15"/>
-      <c r="V53" s="2"/>
+      <c r="V53" s="3"/>
       <c r="W53" s="16"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4357,7 +4161,7 @@
       <c r="S54" s="14"/>
       <c r="T54" s="14"/>
       <c r="U54" s="15"/>
-      <c r="V54" s="2"/>
+      <c r="V54" s="3"/>
       <c r="W54" s="16"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4377,7 +4181,7 @@
       <c r="S55" s="14"/>
       <c r="T55" s="14"/>
       <c r="U55" s="15"/>
-      <c r="V55" s="2"/>
+      <c r="V55" s="3"/>
       <c r="W55" s="16"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4397,7 +4201,7 @@
       <c r="S56" s="14"/>
       <c r="T56" s="14"/>
       <c r="U56" s="15"/>
-      <c r="V56" s="2"/>
+      <c r="V56" s="3"/>
       <c r="W56" s="16"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4417,7 +4221,7 @@
       <c r="S57" s="14"/>
       <c r="T57" s="14"/>
       <c r="U57" s="15"/>
-      <c r="V57" s="2"/>
+      <c r="V57" s="3"/>
       <c r="W57" s="16"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4437,7 +4241,7 @@
       <c r="S58" s="14"/>
       <c r="T58" s="14"/>
       <c r="U58" s="15"/>
-      <c r="V58" s="2"/>
+      <c r="V58" s="3"/>
       <c r="W58" s="16"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4457,7 +4261,7 @@
       <c r="S59" s="14"/>
       <c r="T59" s="14"/>
       <c r="U59" s="15"/>
-      <c r="V59" s="2"/>
+      <c r="V59" s="3"/>
       <c r="W59" s="16"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4477,7 +4281,7 @@
       <c r="S60" s="14"/>
       <c r="T60" s="14"/>
       <c r="U60" s="15"/>
-      <c r="V60" s="2"/>
+      <c r="V60" s="3"/>
       <c r="W60" s="16"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4497,7 +4301,7 @@
       <c r="S61" s="14"/>
       <c r="T61" s="14"/>
       <c r="U61" s="15"/>
-      <c r="V61" s="2"/>
+      <c r="V61" s="3"/>
       <c r="W61" s="16"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4517,7 +4321,7 @@
       <c r="S62" s="14"/>
       <c r="T62" s="14"/>
       <c r="U62" s="15"/>
-      <c r="V62" s="2"/>
+      <c r="V62" s="3"/>
       <c r="W62" s="16"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4537,7 +4341,7 @@
       <c r="S63" s="14"/>
       <c r="T63" s="14"/>
       <c r="U63" s="15"/>
-      <c r="V63" s="2"/>
+      <c r="V63" s="3"/>
       <c r="W63" s="16"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4557,7 +4361,7 @@
       <c r="S64" s="14"/>
       <c r="T64" s="14"/>
       <c r="U64" s="15"/>
-      <c r="V64" s="2"/>
+      <c r="V64" s="3"/>
       <c r="W64" s="16"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4577,7 +4381,7 @@
       <c r="S65" s="14"/>
       <c r="T65" s="14"/>
       <c r="U65" s="15"/>
-      <c r="V65" s="2"/>
+      <c r="V65" s="3"/>
       <c r="W65" s="16"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4597,7 +4401,7 @@
       <c r="S66" s="14"/>
       <c r="T66" s="14"/>
       <c r="U66" s="15"/>
-      <c r="V66" s="2"/>
+      <c r="V66" s="3"/>
       <c r="W66" s="16"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4617,7 +4421,7 @@
       <c r="S67" s="14"/>
       <c r="T67" s="14"/>
       <c r="U67" s="15"/>
-      <c r="V67" s="2"/>
+      <c r="V67" s="3"/>
       <c r="W67" s="16"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4637,7 +4441,7 @@
       <c r="S68" s="14"/>
       <c r="T68" s="14"/>
       <c r="U68" s="15"/>
-      <c r="V68" s="2"/>
+      <c r="V68" s="3"/>
       <c r="W68" s="16"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4657,7 +4461,7 @@
       <c r="S69" s="14"/>
       <c r="T69" s="14"/>
       <c r="U69" s="15"/>
-      <c r="V69" s="2"/>
+      <c r="V69" s="3"/>
       <c r="W69" s="16"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4677,7 +4481,7 @@
       <c r="S70" s="14"/>
       <c r="T70" s="14"/>
       <c r="U70" s="15"/>
-      <c r="V70" s="2"/>
+      <c r="V70" s="3"/>
       <c r="W70" s="16"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4697,7 +4501,7 @@
       <c r="S71" s="14"/>
       <c r="T71" s="14"/>
       <c r="U71" s="15"/>
-      <c r="V71" s="2"/>
+      <c r="V71" s="3"/>
       <c r="W71" s="16"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4717,7 +4521,7 @@
       <c r="S72" s="14"/>
       <c r="T72" s="14"/>
       <c r="U72" s="15"/>
-      <c r="V72" s="2"/>
+      <c r="V72" s="3"/>
       <c r="W72" s="16"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4737,7 +4541,7 @@
       <c r="S73" s="14"/>
       <c r="T73" s="14"/>
       <c r="U73" s="15"/>
-      <c r="V73" s="2"/>
+      <c r="V73" s="3"/>
       <c r="W73" s="16"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4757,7 +4561,7 @@
       <c r="S74" s="14"/>
       <c r="T74" s="14"/>
       <c r="U74" s="15"/>
-      <c r="V74" s="2"/>
+      <c r="V74" s="3"/>
       <c r="W74" s="16"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4777,7 +4581,7 @@
       <c r="S75" s="14"/>
       <c r="T75" s="14"/>
       <c r="U75" s="15"/>
-      <c r="V75" s="2"/>
+      <c r="V75" s="3"/>
       <c r="W75" s="16"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4797,7 +4601,7 @@
       <c r="S76" s="14"/>
       <c r="T76" s="14"/>
       <c r="U76" s="15"/>
-      <c r="V76" s="2"/>
+      <c r="V76" s="3"/>
       <c r="W76" s="16"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4817,7 +4621,7 @@
       <c r="S77" s="14"/>
       <c r="T77" s="14"/>
       <c r="U77" s="15"/>
-      <c r="V77" s="2"/>
+      <c r="V77" s="3"/>
       <c r="W77" s="16"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4837,7 +4641,7 @@
       <c r="S78" s="14"/>
       <c r="T78" s="14"/>
       <c r="U78" s="15"/>
-      <c r="V78" s="2"/>
+      <c r="V78" s="3"/>
       <c r="W78" s="16"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4857,7 +4661,7 @@
       <c r="S79" s="14"/>
       <c r="T79" s="14"/>
       <c r="U79" s="15"/>
-      <c r="V79" s="2"/>
+      <c r="V79" s="3"/>
       <c r="W79" s="16"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4877,7 +4681,7 @@
       <c r="S80" s="14"/>
       <c r="T80" s="14"/>
       <c r="U80" s="15"/>
-      <c r="V80" s="2"/>
+      <c r="V80" s="3"/>
       <c r="W80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4897,7 +4701,7 @@
       <c r="S81" s="14"/>
       <c r="T81" s="14"/>
       <c r="U81" s="15"/>
-      <c r="V81" s="2"/>
+      <c r="V81" s="3"/>
       <c r="W81" s="16"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4917,7 +4721,7 @@
       <c r="S82" s="14"/>
       <c r="T82" s="14"/>
       <c r="U82" s="15"/>
-      <c r="V82" s="2"/>
+      <c r="V82" s="3"/>
       <c r="W82" s="16"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4937,7 +4741,7 @@
       <c r="S83" s="14"/>
       <c r="T83" s="14"/>
       <c r="U83" s="15"/>
-      <c r="V83" s="2"/>
+      <c r="V83" s="3"/>
       <c r="W83" s="16"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4957,7 +4761,7 @@
       <c r="S84" s="14"/>
       <c r="T84" s="14"/>
       <c r="U84" s="15"/>
-      <c r="V84" s="2"/>
+      <c r="V84" s="3"/>
       <c r="W84" s="16"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4977,7 +4781,7 @@
       <c r="S85" s="14"/>
       <c r="T85" s="14"/>
       <c r="U85" s="15"/>
-      <c r="V85" s="2"/>
+      <c r="V85" s="3"/>
       <c r="W85" s="16"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4997,7 +4801,7 @@
       <c r="S86" s="14"/>
       <c r="T86" s="14"/>
       <c r="U86" s="15"/>
-      <c r="V86" s="2"/>
+      <c r="V86" s="3"/>
       <c r="W86" s="16"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5017,7 +4821,7 @@
       <c r="S87" s="14"/>
       <c r="T87" s="14"/>
       <c r="U87" s="15"/>
-      <c r="V87" s="2"/>
+      <c r="V87" s="3"/>
       <c r="W87" s="16"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5037,7 +4841,7 @@
       <c r="S88" s="14"/>
       <c r="T88" s="14"/>
       <c r="U88" s="15"/>
-      <c r="V88" s="2"/>
+      <c r="V88" s="3"/>
       <c r="W88" s="16"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5057,7 +4861,7 @@
       <c r="S89" s="14"/>
       <c r="T89" s="14"/>
       <c r="U89" s="15"/>
-      <c r="V89" s="2"/>
+      <c r="V89" s="3"/>
       <c r="W89" s="16"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5077,7 +4881,7 @@
       <c r="S90" s="14"/>
       <c r="T90" s="14"/>
       <c r="U90" s="15"/>
-      <c r="V90" s="2"/>
+      <c r="V90" s="3"/>
       <c r="W90" s="16"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5097,7 +4901,7 @@
       <c r="S91" s="14"/>
       <c r="T91" s="14"/>
       <c r="U91" s="15"/>
-      <c r="V91" s="2"/>
+      <c r="V91" s="3"/>
       <c r="W91" s="16"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5117,7 +4921,7 @@
       <c r="S92" s="14"/>
       <c r="T92" s="14"/>
       <c r="U92" s="15"/>
-      <c r="V92" s="2"/>
+      <c r="V92" s="3"/>
       <c r="W92" s="16"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5137,7 +4941,7 @@
       <c r="S93" s="14"/>
       <c r="T93" s="14"/>
       <c r="U93" s="15"/>
-      <c r="V93" s="2"/>
+      <c r="V93" s="3"/>
       <c r="W93" s="16"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5157,7 +4961,7 @@
       <c r="S94" s="14"/>
       <c r="T94" s="14"/>
       <c r="U94" s="15"/>
-      <c r="V94" s="2"/>
+      <c r="V94" s="3"/>
       <c r="W94" s="16"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5177,7 +4981,7 @@
       <c r="S95" s="14"/>
       <c r="T95" s="14"/>
       <c r="U95" s="15"/>
-      <c r="V95" s="2"/>
+      <c r="V95" s="3"/>
       <c r="W95" s="16"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5197,7 +5001,7 @@
       <c r="S96" s="14"/>
       <c r="T96" s="14"/>
       <c r="U96" s="15"/>
-      <c r="V96" s="2"/>
+      <c r="V96" s="3"/>
       <c r="W96" s="16"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5217,7 +5021,7 @@
       <c r="S97" s="14"/>
       <c r="T97" s="14"/>
       <c r="U97" s="15"/>
-      <c r="V97" s="2"/>
+      <c r="V97" s="3"/>
       <c r="W97" s="16"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5237,7 +5041,7 @@
       <c r="S98" s="14"/>
       <c r="T98" s="14"/>
       <c r="U98" s="15"/>
-      <c r="V98" s="2"/>
+      <c r="V98" s="3"/>
       <c r="W98" s="16"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5257,7 +5061,7 @@
       <c r="S99" s="14"/>
       <c r="T99" s="14"/>
       <c r="U99" s="15"/>
-      <c r="V99" s="2"/>
+      <c r="V99" s="3"/>
       <c r="W99" s="16"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5277,7 +5081,7 @@
       <c r="S100" s="14"/>
       <c r="T100" s="14"/>
       <c r="U100" s="15"/>
-      <c r="V100" s="2"/>
+      <c r="V100" s="3"/>
       <c r="W100" s="16"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5297,7 +5101,7 @@
       <c r="S101" s="14"/>
       <c r="T101" s="14"/>
       <c r="U101" s="15"/>
-      <c r="V101" s="2"/>
+      <c r="V101" s="3"/>
       <c r="W101" s="16"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5317,7 +5121,7 @@
       <c r="S102" s="14"/>
       <c r="T102" s="14"/>
       <c r="U102" s="15"/>
-      <c r="V102" s="2"/>
+      <c r="V102" s="3"/>
       <c r="W102" s="16"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5337,7 +5141,7 @@
       <c r="S103" s="14"/>
       <c r="T103" s="14"/>
       <c r="U103" s="15"/>
-      <c r="V103" s="2"/>
+      <c r="V103" s="3"/>
       <c r="W103" s="16"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5357,7 +5161,7 @@
       <c r="S104" s="14"/>
       <c r="T104" s="14"/>
       <c r="U104" s="15"/>
-      <c r="V104" s="2"/>
+      <c r="V104" s="3"/>
       <c r="W104" s="16"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5377,7 +5181,7 @@
       <c r="S105" s="14"/>
       <c r="T105" s="14"/>
       <c r="U105" s="15"/>
-      <c r="V105" s="2"/>
+      <c r="V105" s="3"/>
       <c r="W105" s="16"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5397,7 +5201,7 @@
       <c r="S106" s="14"/>
       <c r="T106" s="14"/>
       <c r="U106" s="15"/>
-      <c r="V106" s="2"/>
+      <c r="V106" s="3"/>
       <c r="W106" s="16"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5417,7 +5221,7 @@
       <c r="S107" s="14"/>
       <c r="T107" s="14"/>
       <c r="U107" s="15"/>
-      <c r="V107" s="2"/>
+      <c r="V107" s="3"/>
       <c r="W107" s="16"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5437,7 +5241,7 @@
       <c r="S108" s="14"/>
       <c r="T108" s="14"/>
       <c r="U108" s="15"/>
-      <c r="V108" s="2"/>
+      <c r="V108" s="3"/>
       <c r="W108" s="16"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5457,7 +5261,7 @@
       <c r="S109" s="14"/>
       <c r="T109" s="14"/>
       <c r="U109" s="15"/>
-      <c r="V109" s="2"/>
+      <c r="V109" s="3"/>
       <c r="W109" s="16"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5477,7 +5281,7 @@
       <c r="S110" s="14"/>
       <c r="T110" s="14"/>
       <c r="U110" s="15"/>
-      <c r="V110" s="2"/>
+      <c r="V110" s="3"/>
       <c r="W110" s="16"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5497,7 +5301,7 @@
       <c r="S111" s="14"/>
       <c r="T111" s="14"/>
       <c r="U111" s="15"/>
-      <c r="V111" s="2"/>
+      <c r="V111" s="3"/>
       <c r="W111" s="16"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5517,7 +5321,7 @@
       <c r="S112" s="14"/>
       <c r="T112" s="14"/>
       <c r="U112" s="15"/>
-      <c r="V112" s="2"/>
+      <c r="V112" s="3"/>
       <c r="W112" s="16"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5537,7 +5341,7 @@
       <c r="S113" s="14"/>
       <c r="T113" s="14"/>
       <c r="U113" s="15"/>
-      <c r="V113" s="2"/>
+      <c r="V113" s="3"/>
       <c r="W113" s="16"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5557,7 +5361,7 @@
       <c r="S114" s="14"/>
       <c r="T114" s="14"/>
       <c r="U114" s="15"/>
-      <c r="V114" s="2"/>
+      <c r="V114" s="3"/>
       <c r="W114" s="16"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5577,7 +5381,7 @@
       <c r="S115" s="14"/>
       <c r="T115" s="14"/>
       <c r="U115" s="15"/>
-      <c r="V115" s="2"/>
+      <c r="V115" s="3"/>
       <c r="W115" s="16"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5597,7 +5401,7 @@
       <c r="S116" s="14"/>
       <c r="T116" s="14"/>
       <c r="U116" s="15"/>
-      <c r="V116" s="2"/>
+      <c r="V116" s="3"/>
       <c r="W116" s="16"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5617,176 +5421,1128 @@
       <c r="S117" s="14"/>
       <c r="T117" s="14"/>
       <c r="U117" s="15"/>
-      <c r="V117" s="2"/>
+      <c r="V117" s="3"/>
       <c r="W117" s="16"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W118" s="14"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13"/>
+      <c r="J118" s="14"/>
+      <c r="K118" s="14"/>
+      <c r="L118" s="14"/>
+      <c r="M118" s="14"/>
+      <c r="N118" s="14"/>
+      <c r="O118" s="14"/>
+      <c r="P118" s="14"/>
+      <c r="Q118" s="14"/>
+      <c r="R118" s="14"/>
+      <c r="S118" s="14"/>
+      <c r="T118" s="14"/>
+      <c r="U118" s="15"/>
+      <c r="V118" s="3"/>
+      <c r="W118" s="16"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W119" s="14"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="13"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="14"/>
+      <c r="L119" s="14"/>
+      <c r="M119" s="14"/>
+      <c r="N119" s="14"/>
+      <c r="O119" s="14"/>
+      <c r="P119" s="14"/>
+      <c r="Q119" s="14"/>
+      <c r="R119" s="14"/>
+      <c r="S119" s="14"/>
+      <c r="T119" s="14"/>
+      <c r="U119" s="15"/>
+      <c r="V119" s="3"/>
+      <c r="W119" s="16"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W120" s="14"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="14"/>
+      <c r="L120" s="14"/>
+      <c r="M120" s="14"/>
+      <c r="N120" s="14"/>
+      <c r="O120" s="14"/>
+      <c r="P120" s="14"/>
+      <c r="Q120" s="14"/>
+      <c r="R120" s="14"/>
+      <c r="S120" s="14"/>
+      <c r="T120" s="14"/>
+      <c r="U120" s="15"/>
+      <c r="V120" s="3"/>
+      <c r="W120" s="16"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W121" s="14"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="14"/>
+      <c r="L121" s="14"/>
+      <c r="M121" s="14"/>
+      <c r="N121" s="14"/>
+      <c r="O121" s="14"/>
+      <c r="P121" s="14"/>
+      <c r="Q121" s="14"/>
+      <c r="R121" s="14"/>
+      <c r="S121" s="14"/>
+      <c r="T121" s="14"/>
+      <c r="U121" s="15"/>
+      <c r="V121" s="3"/>
+      <c r="W121" s="16"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W122" s="14"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="14"/>
+      <c r="L122" s="14"/>
+      <c r="M122" s="14"/>
+      <c r="N122" s="14"/>
+      <c r="O122" s="14"/>
+      <c r="P122" s="14"/>
+      <c r="Q122" s="14"/>
+      <c r="R122" s="14"/>
+      <c r="S122" s="14"/>
+      <c r="T122" s="14"/>
+      <c r="U122" s="15"/>
+      <c r="V122" s="3"/>
+      <c r="W122" s="16"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W123" s="14"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
+      <c r="I123" s="13"/>
+      <c r="J123" s="14"/>
+      <c r="K123" s="14"/>
+      <c r="L123" s="14"/>
+      <c r="M123" s="14"/>
+      <c r="N123" s="14"/>
+      <c r="O123" s="14"/>
+      <c r="P123" s="14"/>
+      <c r="Q123" s="14"/>
+      <c r="R123" s="14"/>
+      <c r="S123" s="14"/>
+      <c r="T123" s="14"/>
+      <c r="U123" s="15"/>
+      <c r="V123" s="3"/>
+      <c r="W123" s="16"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W124" s="14"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="13"/>
+      <c r="J124" s="14"/>
+      <c r="K124" s="14"/>
+      <c r="L124" s="14"/>
+      <c r="M124" s="14"/>
+      <c r="N124" s="14"/>
+      <c r="O124" s="14"/>
+      <c r="P124" s="14"/>
+      <c r="Q124" s="14"/>
+      <c r="R124" s="14"/>
+      <c r="S124" s="14"/>
+      <c r="T124" s="14"/>
+      <c r="U124" s="15"/>
+      <c r="V124" s="3"/>
+      <c r="W124" s="16"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W125" s="14"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
+      <c r="I125" s="13"/>
+      <c r="J125" s="14"/>
+      <c r="K125" s="14"/>
+      <c r="L125" s="14"/>
+      <c r="M125" s="14"/>
+      <c r="N125" s="14"/>
+      <c r="O125" s="14"/>
+      <c r="P125" s="14"/>
+      <c r="Q125" s="14"/>
+      <c r="R125" s="14"/>
+      <c r="S125" s="14"/>
+      <c r="T125" s="14"/>
+      <c r="U125" s="15"/>
+      <c r="V125" s="3"/>
+      <c r="W125" s="16"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W126" s="14"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="13"/>
+      <c r="J126" s="14"/>
+      <c r="K126" s="14"/>
+      <c r="L126" s="14"/>
+      <c r="M126" s="14"/>
+      <c r="N126" s="14"/>
+      <c r="O126" s="14"/>
+      <c r="P126" s="14"/>
+      <c r="Q126" s="14"/>
+      <c r="R126" s="14"/>
+      <c r="S126" s="14"/>
+      <c r="T126" s="14"/>
+      <c r="U126" s="15"/>
+      <c r="V126" s="3"/>
+      <c r="W126" s="16"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W127" s="14"/>
+      <c r="F127" s="13"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
+      <c r="I127" s="13"/>
+      <c r="J127" s="14"/>
+      <c r="K127" s="14"/>
+      <c r="L127" s="14"/>
+      <c r="M127" s="14"/>
+      <c r="N127" s="14"/>
+      <c r="O127" s="14"/>
+      <c r="P127" s="14"/>
+      <c r="Q127" s="14"/>
+      <c r="R127" s="14"/>
+      <c r="S127" s="14"/>
+      <c r="T127" s="14"/>
+      <c r="U127" s="15"/>
+      <c r="V127" s="3"/>
+      <c r="W127" s="16"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W128" s="14"/>
+      <c r="F128" s="13"/>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
+      <c r="I128" s="13"/>
+      <c r="J128" s="14"/>
+      <c r="K128" s="14"/>
+      <c r="L128" s="14"/>
+      <c r="M128" s="14"/>
+      <c r="N128" s="14"/>
+      <c r="O128" s="14"/>
+      <c r="P128" s="14"/>
+      <c r="Q128" s="14"/>
+      <c r="R128" s="14"/>
+      <c r="S128" s="14"/>
+      <c r="T128" s="14"/>
+      <c r="U128" s="15"/>
+      <c r="V128" s="3"/>
+      <c r="W128" s="16"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W129" s="14"/>
+      <c r="F129" s="13"/>
+      <c r="G129" s="13"/>
+      <c r="H129" s="13"/>
+      <c r="I129" s="13"/>
+      <c r="J129" s="14"/>
+      <c r="K129" s="14"/>
+      <c r="L129" s="14"/>
+      <c r="M129" s="14"/>
+      <c r="N129" s="14"/>
+      <c r="O129" s="14"/>
+      <c r="P129" s="14"/>
+      <c r="Q129" s="14"/>
+      <c r="R129" s="14"/>
+      <c r="S129" s="14"/>
+      <c r="T129" s="14"/>
+      <c r="U129" s="15"/>
+      <c r="V129" s="3"/>
+      <c r="W129" s="16"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W130" s="14"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
+      <c r="I130" s="13"/>
+      <c r="J130" s="14"/>
+      <c r="K130" s="14"/>
+      <c r="L130" s="14"/>
+      <c r="M130" s="14"/>
+      <c r="N130" s="14"/>
+      <c r="O130" s="14"/>
+      <c r="P130" s="14"/>
+      <c r="Q130" s="14"/>
+      <c r="R130" s="14"/>
+      <c r="S130" s="14"/>
+      <c r="T130" s="14"/>
+      <c r="U130" s="15"/>
+      <c r="V130" s="3"/>
+      <c r="W130" s="16"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W131" s="14"/>
+      <c r="F131" s="13"/>
+      <c r="G131" s="13"/>
+      <c r="H131" s="13"/>
+      <c r="I131" s="13"/>
+      <c r="J131" s="14"/>
+      <c r="K131" s="14"/>
+      <c r="L131" s="14"/>
+      <c r="M131" s="14"/>
+      <c r="N131" s="14"/>
+      <c r="O131" s="14"/>
+      <c r="P131" s="14"/>
+      <c r="Q131" s="14"/>
+      <c r="R131" s="14"/>
+      <c r="S131" s="14"/>
+      <c r="T131" s="14"/>
+      <c r="U131" s="15"/>
+      <c r="V131" s="3"/>
+      <c r="W131" s="16"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W132" s="14"/>
+      <c r="F132" s="13"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
+      <c r="I132" s="13"/>
+      <c r="J132" s="14"/>
+      <c r="K132" s="14"/>
+      <c r="L132" s="14"/>
+      <c r="M132" s="14"/>
+      <c r="N132" s="14"/>
+      <c r="O132" s="14"/>
+      <c r="P132" s="14"/>
+      <c r="Q132" s="14"/>
+      <c r="R132" s="14"/>
+      <c r="S132" s="14"/>
+      <c r="T132" s="14"/>
+      <c r="U132" s="15"/>
+      <c r="V132" s="3"/>
+      <c r="W132" s="16"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W133" s="14"/>
+      <c r="F133" s="13"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
+      <c r="I133" s="13"/>
+      <c r="J133" s="14"/>
+      <c r="K133" s="14"/>
+      <c r="L133" s="14"/>
+      <c r="M133" s="14"/>
+      <c r="N133" s="14"/>
+      <c r="O133" s="14"/>
+      <c r="P133" s="14"/>
+      <c r="Q133" s="14"/>
+      <c r="R133" s="14"/>
+      <c r="S133" s="14"/>
+      <c r="T133" s="14"/>
+      <c r="U133" s="15"/>
+      <c r="V133" s="3"/>
+      <c r="W133" s="16"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W134" s="14"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="I134" s="13"/>
+      <c r="J134" s="14"/>
+      <c r="K134" s="14"/>
+      <c r="L134" s="14"/>
+      <c r="M134" s="14"/>
+      <c r="N134" s="14"/>
+      <c r="O134" s="14"/>
+      <c r="P134" s="14"/>
+      <c r="Q134" s="14"/>
+      <c r="R134" s="14"/>
+      <c r="S134" s="14"/>
+      <c r="T134" s="14"/>
+      <c r="U134" s="15"/>
+      <c r="V134" s="3"/>
+      <c r="W134" s="16"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W135" s="14"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13"/>
+      <c r="I135" s="13"/>
+      <c r="J135" s="14"/>
+      <c r="K135" s="14"/>
+      <c r="L135" s="14"/>
+      <c r="M135" s="14"/>
+      <c r="N135" s="14"/>
+      <c r="O135" s="14"/>
+      <c r="P135" s="14"/>
+      <c r="Q135" s="14"/>
+      <c r="R135" s="14"/>
+      <c r="S135" s="14"/>
+      <c r="T135" s="14"/>
+      <c r="U135" s="15"/>
+      <c r="V135" s="3"/>
+      <c r="W135" s="16"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W136" s="14"/>
+      <c r="F136" s="13"/>
+      <c r="G136" s="13"/>
+      <c r="H136" s="13"/>
+      <c r="I136" s="13"/>
+      <c r="J136" s="14"/>
+      <c r="K136" s="14"/>
+      <c r="L136" s="14"/>
+      <c r="M136" s="14"/>
+      <c r="N136" s="14"/>
+      <c r="O136" s="14"/>
+      <c r="P136" s="14"/>
+      <c r="Q136" s="14"/>
+      <c r="R136" s="14"/>
+      <c r="S136" s="14"/>
+      <c r="T136" s="14"/>
+      <c r="U136" s="15"/>
+      <c r="V136" s="3"/>
+      <c r="W136" s="16"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W137" s="14"/>
+      <c r="F137" s="13"/>
+      <c r="G137" s="13"/>
+      <c r="H137" s="13"/>
+      <c r="I137" s="13"/>
+      <c r="J137" s="14"/>
+      <c r="K137" s="14"/>
+      <c r="L137" s="14"/>
+      <c r="M137" s="14"/>
+      <c r="N137" s="14"/>
+      <c r="O137" s="14"/>
+      <c r="P137" s="14"/>
+      <c r="Q137" s="14"/>
+      <c r="R137" s="14"/>
+      <c r="S137" s="14"/>
+      <c r="T137" s="14"/>
+      <c r="U137" s="15"/>
+      <c r="V137" s="3"/>
+      <c r="W137" s="16"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W138" s="14"/>
+      <c r="F138" s="13"/>
+      <c r="G138" s="13"/>
+      <c r="H138" s="13"/>
+      <c r="I138" s="13"/>
+      <c r="J138" s="14"/>
+      <c r="K138" s="14"/>
+      <c r="L138" s="14"/>
+      <c r="M138" s="14"/>
+      <c r="N138" s="14"/>
+      <c r="O138" s="14"/>
+      <c r="P138" s="14"/>
+      <c r="Q138" s="14"/>
+      <c r="R138" s="14"/>
+      <c r="S138" s="14"/>
+      <c r="T138" s="14"/>
+      <c r="U138" s="15"/>
+      <c r="V138" s="3"/>
+      <c r="W138" s="16"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W139" s="14"/>
+      <c r="F139" s="13"/>
+      <c r="G139" s="13"/>
+      <c r="H139" s="13"/>
+      <c r="I139" s="13"/>
+      <c r="J139" s="14"/>
+      <c r="K139" s="14"/>
+      <c r="L139" s="14"/>
+      <c r="M139" s="14"/>
+      <c r="N139" s="14"/>
+      <c r="O139" s="14"/>
+      <c r="P139" s="14"/>
+      <c r="Q139" s="14"/>
+      <c r="R139" s="14"/>
+      <c r="S139" s="14"/>
+      <c r="T139" s="14"/>
+      <c r="U139" s="15"/>
+      <c r="V139" s="3"/>
+      <c r="W139" s="16"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W140" s="14"/>
+      <c r="F140" s="13"/>
+      <c r="G140" s="13"/>
+      <c r="H140" s="13"/>
+      <c r="I140" s="13"/>
+      <c r="J140" s="14"/>
+      <c r="K140" s="14"/>
+      <c r="L140" s="14"/>
+      <c r="M140" s="14"/>
+      <c r="N140" s="14"/>
+      <c r="O140" s="14"/>
+      <c r="P140" s="14"/>
+      <c r="Q140" s="14"/>
+      <c r="R140" s="14"/>
+      <c r="S140" s="14"/>
+      <c r="T140" s="14"/>
+      <c r="U140" s="15"/>
+      <c r="V140" s="3"/>
+      <c r="W140" s="16"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W141" s="14"/>
+      <c r="F141" s="13"/>
+      <c r="G141" s="13"/>
+      <c r="H141" s="13"/>
+      <c r="I141" s="13"/>
+      <c r="J141" s="14"/>
+      <c r="K141" s="14"/>
+      <c r="L141" s="14"/>
+      <c r="M141" s="14"/>
+      <c r="N141" s="14"/>
+      <c r="O141" s="14"/>
+      <c r="P141" s="14"/>
+      <c r="Q141" s="14"/>
+      <c r="R141" s="14"/>
+      <c r="S141" s="14"/>
+      <c r="T141" s="14"/>
+      <c r="U141" s="15"/>
+      <c r="V141" s="3"/>
+      <c r="W141" s="16"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W142" s="14"/>
+      <c r="F142" s="13"/>
+      <c r="G142" s="13"/>
+      <c r="H142" s="13"/>
+      <c r="I142" s="13"/>
+      <c r="J142" s="14"/>
+      <c r="K142" s="14"/>
+      <c r="L142" s="14"/>
+      <c r="M142" s="14"/>
+      <c r="N142" s="14"/>
+      <c r="O142" s="14"/>
+      <c r="P142" s="14"/>
+      <c r="Q142" s="14"/>
+      <c r="R142" s="14"/>
+      <c r="S142" s="14"/>
+      <c r="T142" s="14"/>
+      <c r="U142" s="15"/>
+      <c r="V142" s="3"/>
+      <c r="W142" s="16"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W143" s="14"/>
+      <c r="F143" s="13"/>
+      <c r="G143" s="13"/>
+      <c r="H143" s="13"/>
+      <c r="I143" s="13"/>
+      <c r="J143" s="14"/>
+      <c r="K143" s="14"/>
+      <c r="L143" s="14"/>
+      <c r="M143" s="14"/>
+      <c r="N143" s="14"/>
+      <c r="O143" s="14"/>
+      <c r="P143" s="14"/>
+      <c r="Q143" s="14"/>
+      <c r="R143" s="14"/>
+      <c r="S143" s="14"/>
+      <c r="T143" s="14"/>
+      <c r="U143" s="15"/>
+      <c r="V143" s="3"/>
+      <c r="W143" s="16"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W144" s="14"/>
+      <c r="F144" s="13"/>
+      <c r="G144" s="13"/>
+      <c r="H144" s="13"/>
+      <c r="I144" s="13"/>
+      <c r="J144" s="14"/>
+      <c r="K144" s="14"/>
+      <c r="L144" s="14"/>
+      <c r="M144" s="14"/>
+      <c r="N144" s="14"/>
+      <c r="O144" s="14"/>
+      <c r="P144" s="14"/>
+      <c r="Q144" s="14"/>
+      <c r="R144" s="14"/>
+      <c r="S144" s="14"/>
+      <c r="T144" s="14"/>
+      <c r="U144" s="15"/>
+      <c r="V144" s="3"/>
+      <c r="W144" s="16"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W145" s="14"/>
+      <c r="F145" s="13"/>
+      <c r="G145" s="13"/>
+      <c r="H145" s="13"/>
+      <c r="I145" s="13"/>
+      <c r="J145" s="14"/>
+      <c r="K145" s="14"/>
+      <c r="L145" s="14"/>
+      <c r="M145" s="14"/>
+      <c r="N145" s="14"/>
+      <c r="O145" s="14"/>
+      <c r="P145" s="14"/>
+      <c r="Q145" s="14"/>
+      <c r="R145" s="14"/>
+      <c r="S145" s="14"/>
+      <c r="T145" s="14"/>
+      <c r="U145" s="15"/>
+      <c r="V145" s="3"/>
+      <c r="W145" s="16"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W146" s="14"/>
+      <c r="F146" s="13"/>
+      <c r="G146" s="13"/>
+      <c r="H146" s="13"/>
+      <c r="I146" s="13"/>
+      <c r="J146" s="14"/>
+      <c r="K146" s="14"/>
+      <c r="L146" s="14"/>
+      <c r="M146" s="14"/>
+      <c r="N146" s="14"/>
+      <c r="O146" s="14"/>
+      <c r="P146" s="14"/>
+      <c r="Q146" s="14"/>
+      <c r="R146" s="14"/>
+      <c r="S146" s="14"/>
+      <c r="T146" s="14"/>
+      <c r="U146" s="15"/>
+      <c r="V146" s="3"/>
+      <c r="W146" s="16"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W147" s="14"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
+      <c r="H147" s="13"/>
+      <c r="I147" s="13"/>
+      <c r="J147" s="14"/>
+      <c r="K147" s="14"/>
+      <c r="L147" s="14"/>
+      <c r="M147" s="14"/>
+      <c r="N147" s="14"/>
+      <c r="O147" s="14"/>
+      <c r="P147" s="14"/>
+      <c r="Q147" s="14"/>
+      <c r="R147" s="14"/>
+      <c r="S147" s="14"/>
+      <c r="T147" s="14"/>
+      <c r="U147" s="15"/>
+      <c r="V147" s="3"/>
+      <c r="W147" s="16"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W148" s="14"/>
+      <c r="F148" s="13"/>
+      <c r="G148" s="13"/>
+      <c r="H148" s="13"/>
+      <c r="I148" s="13"/>
+      <c r="J148" s="14"/>
+      <c r="K148" s="14"/>
+      <c r="L148" s="14"/>
+      <c r="M148" s="14"/>
+      <c r="N148" s="14"/>
+      <c r="O148" s="14"/>
+      <c r="P148" s="14"/>
+      <c r="Q148" s="14"/>
+      <c r="R148" s="14"/>
+      <c r="S148" s="14"/>
+      <c r="T148" s="14"/>
+      <c r="U148" s="15"/>
+      <c r="V148" s="3"/>
+      <c r="W148" s="16"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W149" s="14"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="14"/>
+      <c r="K149" s="14"/>
+      <c r="L149" s="14"/>
+      <c r="M149" s="14"/>
+      <c r="N149" s="14"/>
+      <c r="O149" s="14"/>
+      <c r="P149" s="14"/>
+      <c r="Q149" s="14"/>
+      <c r="R149" s="14"/>
+      <c r="S149" s="14"/>
+      <c r="T149" s="14"/>
+      <c r="U149" s="15"/>
+      <c r="V149" s="3"/>
+      <c r="W149" s="16"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W150" s="14"/>
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="14"/>
+      <c r="K150" s="14"/>
+      <c r="L150" s="14"/>
+      <c r="M150" s="14"/>
+      <c r="N150" s="14"/>
+      <c r="O150" s="14"/>
+      <c r="P150" s="14"/>
+      <c r="Q150" s="14"/>
+      <c r="R150" s="14"/>
+      <c r="S150" s="14"/>
+      <c r="T150" s="14"/>
+      <c r="U150" s="15"/>
+      <c r="V150" s="3"/>
+      <c r="W150" s="16"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W151" s="14"/>
+      <c r="F151" s="13"/>
+      <c r="G151" s="13"/>
+      <c r="H151" s="13"/>
+      <c r="I151" s="13"/>
+      <c r="J151" s="14"/>
+      <c r="K151" s="14"/>
+      <c r="L151" s="14"/>
+      <c r="M151" s="14"/>
+      <c r="N151" s="14"/>
+      <c r="O151" s="14"/>
+      <c r="P151" s="14"/>
+      <c r="Q151" s="14"/>
+      <c r="R151" s="14"/>
+      <c r="S151" s="14"/>
+      <c r="T151" s="14"/>
+      <c r="U151" s="15"/>
+      <c r="V151" s="3"/>
+      <c r="W151" s="16"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W152" s="14"/>
+      <c r="F152" s="13"/>
+      <c r="G152" s="13"/>
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="14"/>
+      <c r="K152" s="14"/>
+      <c r="L152" s="14"/>
+      <c r="M152" s="14"/>
+      <c r="N152" s="14"/>
+      <c r="O152" s="14"/>
+      <c r="P152" s="14"/>
+      <c r="Q152" s="14"/>
+      <c r="R152" s="14"/>
+      <c r="S152" s="14"/>
+      <c r="T152" s="14"/>
+      <c r="U152" s="15"/>
+      <c r="V152" s="3"/>
+      <c r="W152" s="16"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W153" s="14"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="14"/>
+      <c r="K153" s="14"/>
+      <c r="L153" s="14"/>
+      <c r="M153" s="14"/>
+      <c r="N153" s="14"/>
+      <c r="O153" s="14"/>
+      <c r="P153" s="14"/>
+      <c r="Q153" s="14"/>
+      <c r="R153" s="14"/>
+      <c r="S153" s="14"/>
+      <c r="T153" s="14"/>
+      <c r="U153" s="15"/>
+      <c r="V153" s="3"/>
+      <c r="W153" s="16"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W154" s="14"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+      <c r="J154" s="14"/>
+      <c r="K154" s="14"/>
+      <c r="L154" s="14"/>
+      <c r="M154" s="14"/>
+      <c r="N154" s="14"/>
+      <c r="O154" s="14"/>
+      <c r="P154" s="14"/>
+      <c r="Q154" s="14"/>
+      <c r="R154" s="14"/>
+      <c r="S154" s="14"/>
+      <c r="T154" s="14"/>
+      <c r="U154" s="15"/>
+      <c r="V154" s="3"/>
+      <c r="W154" s="16"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W155" s="14"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="I155" s="13"/>
+      <c r="J155" s="14"/>
+      <c r="K155" s="14"/>
+      <c r="L155" s="14"/>
+      <c r="M155" s="14"/>
+      <c r="N155" s="14"/>
+      <c r="O155" s="14"/>
+      <c r="P155" s="14"/>
+      <c r="Q155" s="14"/>
+      <c r="R155" s="14"/>
+      <c r="S155" s="14"/>
+      <c r="T155" s="14"/>
+      <c r="U155" s="15"/>
+      <c r="V155" s="3"/>
+      <c r="W155" s="16"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W156" s="14"/>
+      <c r="F156" s="13"/>
+      <c r="G156" s="13"/>
+      <c r="H156" s="13"/>
+      <c r="I156" s="13"/>
+      <c r="J156" s="14"/>
+      <c r="K156" s="14"/>
+      <c r="L156" s="14"/>
+      <c r="M156" s="14"/>
+      <c r="N156" s="14"/>
+      <c r="O156" s="14"/>
+      <c r="P156" s="14"/>
+      <c r="Q156" s="14"/>
+      <c r="R156" s="14"/>
+      <c r="S156" s="14"/>
+      <c r="T156" s="14"/>
+      <c r="U156" s="15"/>
+      <c r="V156" s="3"/>
+      <c r="W156" s="16"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W157" s="14"/>
+      <c r="F157" s="13"/>
+      <c r="G157" s="13"/>
+      <c r="H157" s="13"/>
+      <c r="I157" s="13"/>
+      <c r="J157" s="14"/>
+      <c r="K157" s="14"/>
+      <c r="L157" s="14"/>
+      <c r="M157" s="14"/>
+      <c r="N157" s="14"/>
+      <c r="O157" s="14"/>
+      <c r="P157" s="14"/>
+      <c r="Q157" s="14"/>
+      <c r="R157" s="14"/>
+      <c r="S157" s="14"/>
+      <c r="T157" s="14"/>
+      <c r="U157" s="15"/>
+      <c r="V157" s="3"/>
+      <c r="W157" s="16"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W158" s="14"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="13"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="13"/>
+      <c r="J158" s="14"/>
+      <c r="K158" s="14"/>
+      <c r="L158" s="14"/>
+      <c r="M158" s="14"/>
+      <c r="N158" s="14"/>
+      <c r="O158" s="14"/>
+      <c r="P158" s="14"/>
+      <c r="Q158" s="14"/>
+      <c r="R158" s="14"/>
+      <c r="S158" s="14"/>
+      <c r="T158" s="14"/>
+      <c r="U158" s="15"/>
+      <c r="V158" s="3"/>
+      <c r="W158" s="16"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W159" s="14"/>
+      <c r="F159" s="13"/>
+      <c r="G159" s="13"/>
+      <c r="H159" s="13"/>
+      <c r="I159" s="13"/>
+      <c r="J159" s="14"/>
+      <c r="K159" s="14"/>
+      <c r="L159" s="14"/>
+      <c r="M159" s="14"/>
+      <c r="N159" s="14"/>
+      <c r="O159" s="14"/>
+      <c r="P159" s="14"/>
+      <c r="Q159" s="14"/>
+      <c r="R159" s="14"/>
+      <c r="S159" s="14"/>
+      <c r="T159" s="14"/>
+      <c r="U159" s="15"/>
+      <c r="V159" s="3"/>
+      <c r="W159" s="16"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W160" s="14"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="13"/>
+      <c r="J160" s="14"/>
+      <c r="K160" s="14"/>
+      <c r="L160" s="14"/>
+      <c r="M160" s="14"/>
+      <c r="N160" s="14"/>
+      <c r="O160" s="14"/>
+      <c r="P160" s="14"/>
+      <c r="Q160" s="14"/>
+      <c r="R160" s="14"/>
+      <c r="S160" s="14"/>
+      <c r="T160" s="14"/>
+      <c r="U160" s="15"/>
+      <c r="V160" s="3"/>
+      <c r="W160" s="16"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W161" s="14"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="13"/>
+      <c r="H161" s="13"/>
+      <c r="I161" s="13"/>
+      <c r="J161" s="14"/>
+      <c r="K161" s="14"/>
+      <c r="L161" s="14"/>
+      <c r="M161" s="14"/>
+      <c r="N161" s="14"/>
+      <c r="O161" s="14"/>
+      <c r="P161" s="14"/>
+      <c r="Q161" s="14"/>
+      <c r="R161" s="14"/>
+      <c r="S161" s="14"/>
+      <c r="T161" s="14"/>
+      <c r="U161" s="15"/>
+      <c r="V161" s="3"/>
+      <c r="W161" s="16"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W162" s="14"/>
+      <c r="F162" s="13"/>
+      <c r="G162" s="13"/>
+      <c r="H162" s="13"/>
+      <c r="I162" s="13"/>
+      <c r="J162" s="14"/>
+      <c r="K162" s="14"/>
+      <c r="L162" s="14"/>
+      <c r="M162" s="14"/>
+      <c r="N162" s="14"/>
+      <c r="O162" s="14"/>
+      <c r="P162" s="14"/>
+      <c r="Q162" s="14"/>
+      <c r="R162" s="14"/>
+      <c r="S162" s="14"/>
+      <c r="T162" s="14"/>
+      <c r="U162" s="15"/>
+      <c r="V162" s="3"/>
+      <c r="W162" s="16"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W163" s="14"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="13"/>
+      <c r="H163" s="13"/>
+      <c r="I163" s="13"/>
+      <c r="J163" s="14"/>
+      <c r="K163" s="14"/>
+      <c r="L163" s="14"/>
+      <c r="M163" s="14"/>
+      <c r="N163" s="14"/>
+      <c r="O163" s="14"/>
+      <c r="P163" s="14"/>
+      <c r="Q163" s="14"/>
+      <c r="R163" s="14"/>
+      <c r="S163" s="14"/>
+      <c r="T163" s="14"/>
+      <c r="U163" s="15"/>
+      <c r="V163" s="3"/>
+      <c r="W163" s="16"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W164" s="14"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="13"/>
+      <c r="H164" s="13"/>
+      <c r="I164" s="13"/>
+      <c r="J164" s="14"/>
+      <c r="K164" s="14"/>
+      <c r="L164" s="14"/>
+      <c r="M164" s="14"/>
+      <c r="N164" s="14"/>
+      <c r="O164" s="14"/>
+      <c r="P164" s="14"/>
+      <c r="Q164" s="14"/>
+      <c r="R164" s="14"/>
+      <c r="S164" s="14"/>
+      <c r="T164" s="14"/>
+      <c r="U164" s="15"/>
+      <c r="V164" s="3"/>
+      <c r="W164" s="16"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W165" s="14"/>
+      <c r="F165" s="13"/>
+      <c r="G165" s="13"/>
+      <c r="H165" s="13"/>
+      <c r="I165" s="13"/>
+      <c r="J165" s="14"/>
+      <c r="K165" s="14"/>
+      <c r="L165" s="14"/>
+      <c r="M165" s="14"/>
+      <c r="N165" s="14"/>
+      <c r="O165" s="14"/>
+      <c r="P165" s="14"/>
+      <c r="Q165" s="14"/>
+      <c r="R165" s="14"/>
+      <c r="S165" s="14"/>
+      <c r="T165" s="14"/>
+      <c r="U165" s="15"/>
+      <c r="V165" s="3"/>
+      <c r="W165" s="16"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W166" s="14"/>
+      <c r="F166" s="13"/>
+      <c r="G166" s="13"/>
+      <c r="H166" s="13"/>
+      <c r="I166" s="13"/>
+      <c r="J166" s="14"/>
+      <c r="K166" s="14"/>
+      <c r="L166" s="14"/>
+      <c r="M166" s="14"/>
+      <c r="N166" s="14"/>
+      <c r="O166" s="14"/>
+      <c r="P166" s="14"/>
+      <c r="Q166" s="14"/>
+      <c r="R166" s="14"/>
+      <c r="S166" s="14"/>
+      <c r="T166" s="14"/>
+      <c r="U166" s="15"/>
+      <c r="V166" s="3"/>
+      <c r="W166" s="16"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W167" s="14"/>
+      <c r="F167" s="13"/>
+      <c r="G167" s="13"/>
+      <c r="H167" s="13"/>
+      <c r="I167" s="13"/>
+      <c r="J167" s="14"/>
+      <c r="K167" s="14"/>
+      <c r="L167" s="14"/>
+      <c r="M167" s="14"/>
+      <c r="N167" s="14"/>
+      <c r="O167" s="14"/>
+      <c r="P167" s="14"/>
+      <c r="Q167" s="14"/>
+      <c r="R167" s="14"/>
+      <c r="S167" s="14"/>
+      <c r="T167" s="14"/>
+      <c r="U167" s="15"/>
+      <c r="V167" s="3"/>
+      <c r="W167" s="16"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W168" s="14"/>
+      <c r="F168" s="13"/>
+      <c r="G168" s="13"/>
+      <c r="H168" s="13"/>
+      <c r="I168" s="13"/>
+      <c r="J168" s="14"/>
+      <c r="K168" s="14"/>
+      <c r="L168" s="14"/>
+      <c r="M168" s="14"/>
+      <c r="N168" s="14"/>
+      <c r="O168" s="14"/>
+      <c r="P168" s="14"/>
+      <c r="Q168" s="14"/>
+      <c r="R168" s="14"/>
+      <c r="S168" s="14"/>
+      <c r="T168" s="14"/>
+      <c r="U168" s="15"/>
+      <c r="V168" s="3"/>
+      <c r="W168" s="16"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W169" s="14"/>
+      <c r="F169" s="13"/>
+      <c r="G169" s="13"/>
+      <c r="H169" s="13"/>
+      <c r="I169" s="13"/>
+      <c r="J169" s="14"/>
+      <c r="K169" s="14"/>
+      <c r="L169" s="14"/>
+      <c r="M169" s="14"/>
+      <c r="N169" s="14"/>
+      <c r="O169" s="14"/>
+      <c r="P169" s="14"/>
+      <c r="Q169" s="14"/>
+      <c r="R169" s="14"/>
+      <c r="S169" s="14"/>
+      <c r="T169" s="14"/>
+      <c r="U169" s="15"/>
+      <c r="V169" s="3"/>
+      <c r="W169" s="16"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W170" s="14"/>
+      <c r="F170" s="13"/>
+      <c r="G170" s="13"/>
+      <c r="H170" s="13"/>
+      <c r="I170" s="13"/>
+      <c r="J170" s="14"/>
+      <c r="K170" s="14"/>
+      <c r="L170" s="14"/>
+      <c r="M170" s="14"/>
+      <c r="N170" s="14"/>
+      <c r="O170" s="14"/>
+      <c r="P170" s="14"/>
+      <c r="Q170" s="14"/>
+      <c r="R170" s="14"/>
+      <c r="S170" s="14"/>
+      <c r="T170" s="14"/>
+      <c r="U170" s="15"/>
+      <c r="V170" s="3"/>
+      <c r="W170" s="16"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W171" s="14"/>
+      <c r="F171" s="13"/>
+      <c r="G171" s="13"/>
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="14"/>
+      <c r="K171" s="14"/>
+      <c r="L171" s="14"/>
+      <c r="M171" s="14"/>
+      <c r="N171" s="14"/>
+      <c r="O171" s="14"/>
+      <c r="P171" s="14"/>
+      <c r="Q171" s="14"/>
+      <c r="R171" s="14"/>
+      <c r="S171" s="14"/>
+      <c r="T171" s="14"/>
+      <c r="U171" s="15"/>
+      <c r="V171" s="3"/>
+      <c r="W171" s="16"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W172" s="14"/>
+      <c r="F172" s="13"/>
+      <c r="G172" s="13"/>
+      <c r="H172" s="13"/>
+      <c r="I172" s="13"/>
+      <c r="J172" s="14"/>
+      <c r="K172" s="14"/>
+      <c r="L172" s="14"/>
+      <c r="M172" s="14"/>
+      <c r="N172" s="14"/>
+      <c r="O172" s="14"/>
+      <c r="P172" s="14"/>
+      <c r="Q172" s="14"/>
+      <c r="R172" s="14"/>
+      <c r="S172" s="14"/>
+      <c r="T172" s="14"/>
+      <c r="U172" s="15"/>
+      <c r="V172" s="3"/>
+      <c r="W172" s="16"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W173" s="14"/>
+      <c r="F173" s="13"/>
+      <c r="G173" s="13"/>
+      <c r="H173" s="13"/>
+      <c r="I173" s="13"/>
+      <c r="J173" s="14"/>
+      <c r="K173" s="14"/>
+      <c r="L173" s="14"/>
+      <c r="M173" s="14"/>
+      <c r="N173" s="14"/>
+      <c r="O173" s="14"/>
+      <c r="P173" s="14"/>
+      <c r="Q173" s="14"/>
+      <c r="R173" s="14"/>
+      <c r="S173" s="14"/>
+      <c r="T173" s="14"/>
+      <c r="U173" s="15"/>
+      <c r="V173" s="3"/>
+      <c r="W173" s="16"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W174" s="14"/>
@@ -6871,227 +7627,181 @@
     <row r="534" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W534" s="14"/>
     </row>
-    <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048363" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048364" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048365" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048366" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048367" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048368" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048369" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048370" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048371" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048372" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048373" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048374" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048375" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048376" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048378" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048379" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048380" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048381" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048382" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048383" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048384" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048385" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048386" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048387" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048388" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048389" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048392" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048393" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048394" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048395" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048396" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048397" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048398" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048399" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048400" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048401" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048402" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048403" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048404" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048405" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048406" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048407" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048408" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048409" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048410" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048411" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048412" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048413" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048414" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048415" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048416" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048417" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048418" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048419" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048420" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048421" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048422" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048423" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048424" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048425" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048426" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048427" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048428" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048429" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048430" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048431" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048432" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048433" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048434" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048435" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048436" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048437" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048438" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048439" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048440" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048441" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048442" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048443" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048444" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048445" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048446" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048447" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048448" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048449" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048450" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048451" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048452" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048453" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048454" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048455" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048456" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048457" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048458" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048459" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048460" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048461" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048462" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048463" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048464" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048465" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048466" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048467" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048468" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048469" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048470" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048471" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048472" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048473" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048474" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048475" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048476" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048477" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048478" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048479" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048480" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048481" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048482" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048483" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048484" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W535" s="14"/>
+    </row>
+    <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W536" s="14"/>
+    </row>
+    <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W537" s="14"/>
+    </row>
+    <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W538" s="14"/>
+    </row>
+    <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W539" s="14"/>
+    </row>
+    <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W540" s="14"/>
+    </row>
+    <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W541" s="14"/>
+    </row>
+    <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W542" s="14"/>
+    </row>
+    <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W543" s="14"/>
+    </row>
+    <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W544" s="14"/>
+    </row>
+    <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W545" s="14"/>
+    </row>
+    <row r="546" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W546" s="14"/>
+    </row>
+    <row r="547" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W547" s="14"/>
+    </row>
+    <row r="548" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W548" s="14"/>
+    </row>
+    <row r="549" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W549" s="14"/>
+    </row>
+    <row r="550" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W550" s="14"/>
+    </row>
+    <row r="551" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W551" s="14"/>
+    </row>
+    <row r="552" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W552" s="14"/>
+    </row>
+    <row r="553" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W553" s="14"/>
+    </row>
+    <row r="554" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W554" s="14"/>
+    </row>
+    <row r="555" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W555" s="14"/>
+    </row>
+    <row r="556" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W556" s="14"/>
+    </row>
+    <row r="557" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W557" s="14"/>
+    </row>
+    <row r="558" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W558" s="14"/>
+    </row>
+    <row r="559" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W559" s="14"/>
+    </row>
+    <row r="560" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W560" s="14"/>
+    </row>
+    <row r="561" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W561" s="14"/>
+    </row>
+    <row r="562" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W562" s="14"/>
+    </row>
+    <row r="563" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W563" s="14"/>
+    </row>
+    <row r="564" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W564" s="14"/>
+    </row>
+    <row r="565" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W565" s="14"/>
+    </row>
+    <row r="566" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W566" s="14"/>
+    </row>
+    <row r="567" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W567" s="14"/>
+    </row>
+    <row r="568" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W568" s="14"/>
+    </row>
+    <row r="569" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W569" s="14"/>
+    </row>
+    <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W570" s="14"/>
+    </row>
+    <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W571" s="14"/>
+    </row>
+    <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W572" s="14"/>
+    </row>
+    <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W573" s="14"/>
+    </row>
+    <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W574" s="14"/>
+    </row>
+    <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W575" s="14"/>
+    </row>
+    <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W576" s="14"/>
+    </row>
+    <row r="577" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W577" s="14"/>
+    </row>
+    <row r="578" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W578" s="14"/>
+    </row>
+    <row r="579" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W579" s="14"/>
+    </row>
+    <row r="580" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W580" s="14"/>
+    </row>
+    <row r="581" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W581" s="14"/>
+    </row>
+    <row r="582" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W582" s="14"/>
+    </row>
+    <row r="583" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W583" s="14"/>
+    </row>
+    <row r="584" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W584" s="14"/>
+    </row>
+    <row r="585" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W585" s="14"/>
+    </row>
+    <row r="586" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W586" s="14"/>
+    </row>
+    <row r="587" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W587" s="14"/>
+    </row>
+    <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W588" s="14"/>
+    </row>
+    <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W589" s="14"/>
+    </row>
+    <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="W590" s="14"/>
+    </row>
+    <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A9:W31"/>
+  <autoFilter ref="A9:W33"/>
   <mergeCells count="7">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -7102,15 +7812,15 @@
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J31 M10:N31 P10:R31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J33 M10:N33 P10:R33" type="list">
       <formula1>Sheet1!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T33" type="list">
       <formula1>Sheet1!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K33" type="list">
       <formula1>'LISTA VALORI'!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7133,46 +7843,46 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>107</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="37" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -7192,233 +7902,185 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G960"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="102"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="102"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="19" t="s">
+      <c r="B4" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D4" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="42" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="B5" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="43" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="s">
+      <c r="D5" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="44" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="B6" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="45" t="s">
+      <c r="B7" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="45" t="s">
+      <c r="B8" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D8" s="45" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="45" t="s">
+      <c r="D9" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="46" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+      <c r="B10" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="D10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="47" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+      <c r="B11" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="45" t="s">
+      <c r="D11" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="47" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>145</v>
-      </c>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="45" t="n">
-        <v>521</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>153</v>
-      </c>
-    </row>
+      <c r="D13" s="47"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8383,11 +9045,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="8.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8400,18 +9062,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9430,8 +10092,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d4db60622090a1f8a8d506ac1d64a349">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a3a9ed8bb952a3d76dd1e2fa3d624b9" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
     <xsd:import namespace="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
     <xsd:element name="properties">
@@ -9457,7 +10131,6 @@
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:UserStoryALM" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9545,11 +10218,6 @@
           <xsd:enumeration value="137048 - Stesura checklist RAP"/>
           <xsd:enumeration value="137049 - Sviluppo testcase RAP"/>
         </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -9693,7 +10361,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -9702,20 +10370,25 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE213DB-5082-48B0-B2A5-099EBF944035}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -9733,33 +10406,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Sheet1" sheetId="6" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Summary!$A$1:$G$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$33</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Summary!$A$1:$G$17</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">TestCases!$A$9:$W$31</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -286,113 +286,83 @@
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT4</t>
   </si>
   <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L’applicativo effettua controlli preventivi sul dato inserito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 1" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-20T10:49:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f17cfcdc21dd44a0f6b102d0921ef63b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.3f47aed86b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation", al fine di una futura pubblicazione, con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
-Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 2" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-20T11:50:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87202318605b410218263c6a459226ae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.c7955e2469^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 </t>
   </si>
   <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’applicativo effettua controlli preventivi sul dato inserito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-03-09T13:42:58Z</t>
   </si>
   <si>
@@ -441,7 +411,7 @@
     <t xml:space="preserve">Versione:</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.5</t>
+    <t xml:space="preserve">9.0.0</t>
   </si>
   <si>
     <t xml:space="preserve">LAB</t>
@@ -453,7 +423,7 @@
     <t xml:space="preserve">4, 452</t>
   </si>
   <si>
-    <t xml:space="preserve">28,36,44,53,55,56,57,58,59,60,61,62, 466</t>
+    <t xml:space="preserve">28,36,44,53,55,56,57,59,60,61,62, 466, 473</t>
   </si>
   <si>
     <t xml:space="preserve">LDO</t>
@@ -471,7 +441,7 @@
     <t xml:space="preserve">471, 472</t>
   </si>
   <si>
-    <t xml:space="preserve">31,39,47,76,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93, 462</t>
+    <t xml:space="preserve">31,39,47,76,78,79,80,81,83,84,85,86,87,88,89,90,91,92,93, 462, 474</t>
   </si>
   <si>
     <t xml:space="preserve">CERT_VAC</t>
@@ -507,10 +477,10 @@
     <t xml:space="preserve">448, 449</t>
   </si>
   <si>
-    <t xml:space="preserve">32,40,48,152,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169, 461, 468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">444, 445</t>
+    <t xml:space="preserve">32,40,48,152,154,155,156,157,159,160,161,162,163,164,165,166,167,168,169, 461, 468, 475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">476,477,478</t>
   </si>
   <si>
     <t xml:space="preserve">30,38,46,175,177,178,179,180,181,182,183,184,185,186,187,188,189,190, 469</t>
@@ -532,6 +502,57 @@
   </si>
   <si>
     <t xml:space="preserve">423,424,425,427,428,429,430,431,432,433,434,435,436,437,438,439,440,441,442,443,448,449, 470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">479, 480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481,482,483,484,485,486,487,488,489,490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETT_SCREEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">491, 492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493,494,495,496,497,498,499,500,501,502,503,504,505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETT_VACC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">506, 507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508,509,510,511,512,513,514,515,516,517,518,519,520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">522,523,524,525,526,527,528,529,530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531, 532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533,534,535,536,537,538,539,540,541,542,543,544,545,546,547,548,549,550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REL_CTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">551, 552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">553,554,555,556,557,558,559,560,561,562,563,564,565,566,567,568,569,570</t>
   </si>
   <si>
     <t xml:space="preserve">PASS</t>
@@ -544,10 +565,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -675,7 +697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -791,10 +813,31 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right/>
       <top style="medium"/>
       <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -827,7 +870,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -948,7 +991,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -976,48 +1019,72 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2481,7 +2548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W595"/>
+  <dimension ref="A1:W1048576"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.16"/>
@@ -2695,7 +2762,7 @@
       <c r="V8" s="3"/>
       <c r="W8" s="16"/>
     </row>
-    <row r="9" s="27" customFormat="true" ht="73.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="27" customFormat="true" ht="72.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
         <v>24</v>
       </c>
@@ -2779,16 +2846,18 @@
       <c r="D10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="30"/>
+      <c r="E10" s="30" t="s">
+        <v>50</v>
+      </c>
       <c r="F10" s="31"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
       <c r="I10" s="33"/>
       <c r="J10" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
@@ -2802,7 +2871,7 @@
       <c r="U10" s="35"/>
       <c r="V10" s="36"/>
       <c r="W10" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2816,18 +2885,18 @@
         <v>48</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="30"/>
+        <v>54</v>
+      </c>
+      <c r="E11" s="37"/>
       <c r="F11" s="31"/>
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
       <c r="I11" s="33"/>
       <c r="J11" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="34"/>
@@ -2841,7 +2910,7 @@
       <c r="U11" s="35"/>
       <c r="V11" s="36"/>
       <c r="W11" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2855,44 +2924,44 @@
         <v>48</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="30"/>
+        <v>55</v>
+      </c>
+      <c r="E12" s="37"/>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
       <c r="I12" s="33"/>
       <c r="J12" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O12" s="34"/>
       <c r="P12" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q12" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R12" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S12" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T12" s="34"/>
       <c r="U12" s="35"/>
       <c r="V12" s="36"/>
       <c r="W12" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2906,18 +2975,18 @@
         <v>48</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="E13" s="37"/>
       <c r="F13" s="31"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="33"/>
       <c r="J13" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="34"/>
@@ -2931,7 +3000,7 @@
       <c r="U13" s="35"/>
       <c r="V13" s="36"/>
       <c r="W13" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2945,18 +3014,18 @@
         <v>48</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="30"/>
+        <v>58</v>
+      </c>
+      <c r="E14" s="37"/>
       <c r="F14" s="31"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="33"/>
       <c r="J14" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
@@ -2970,7 +3039,7 @@
       <c r="U14" s="35"/>
       <c r="V14" s="36"/>
       <c r="W14" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2984,18 +3053,18 @@
         <v>48</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="30"/>
+        <v>59</v>
+      </c>
+      <c r="E15" s="37"/>
       <c r="F15" s="31"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
       <c r="J15" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
@@ -3009,7 +3078,7 @@
       <c r="U15" s="35"/>
       <c r="V15" s="36"/>
       <c r="W15" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3023,18 +3092,18 @@
         <v>48</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="30"/>
+        <v>60</v>
+      </c>
+      <c r="E16" s="37"/>
       <c r="F16" s="31"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
       <c r="I16" s="33"/>
       <c r="J16" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="34"/>
@@ -3048,7 +3117,7 @@
       <c r="U16" s="35"/>
       <c r="V16" s="36"/>
       <c r="W16" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3062,18 +3131,18 @@
         <v>48</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="30"/>
+        <v>61</v>
+      </c>
+      <c r="E17" s="37"/>
       <c r="F17" s="31"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
       <c r="I17" s="33"/>
       <c r="J17" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K17" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
@@ -3087,7 +3156,7 @@
       <c r="U17" s="35"/>
       <c r="V17" s="36"/>
       <c r="W17" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3101,18 +3170,18 @@
         <v>48</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="30"/>
+        <v>62</v>
+      </c>
+      <c r="E18" s="37"/>
       <c r="F18" s="31"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="33"/>
       <c r="J18" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K18" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="34"/>
@@ -3126,7 +3195,7 @@
       <c r="U18" s="35"/>
       <c r="V18" s="36"/>
       <c r="W18" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3140,18 +3209,18 @@
         <v>48</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="30"/>
+        <v>63</v>
+      </c>
+      <c r="E19" s="37"/>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
       <c r="I19" s="33"/>
       <c r="J19" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="34"/>
@@ -3165,7 +3234,7 @@
       <c r="U19" s="35"/>
       <c r="V19" s="36"/>
       <c r="W19" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3179,18 +3248,18 @@
         <v>48</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="30"/>
+        <v>64</v>
+      </c>
+      <c r="E20" s="37"/>
       <c r="F20" s="31"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="33"/>
       <c r="J20" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K20" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="34"/>
@@ -3204,7 +3273,7 @@
       <c r="U20" s="35"/>
       <c r="V20" s="36"/>
       <c r="W20" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3218,18 +3287,18 @@
         <v>48</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="30"/>
+        <v>65</v>
+      </c>
+      <c r="E21" s="37"/>
       <c r="F21" s="31"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="33"/>
       <c r="J21" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
@@ -3243,7 +3312,7 @@
       <c r="U21" s="35"/>
       <c r="V21" s="36"/>
       <c r="W21" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3257,18 +3326,18 @@
         <v>48</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="30"/>
+        <v>66</v>
+      </c>
+      <c r="E22" s="37"/>
       <c r="F22" s="31"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="33"/>
       <c r="J22" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K22" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
@@ -3282,7 +3351,7 @@
       <c r="U22" s="35"/>
       <c r="V22" s="36"/>
       <c r="W22" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3296,18 +3365,18 @@
         <v>48</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="30"/>
+        <v>67</v>
+      </c>
+      <c r="E23" s="37"/>
       <c r="F23" s="31"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
       <c r="I23" s="33"/>
       <c r="J23" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K23" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
@@ -3321,7 +3390,7 @@
       <c r="U23" s="35"/>
       <c r="V23" s="36"/>
       <c r="W23" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3335,18 +3404,18 @@
         <v>48</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="E24" s="37"/>
       <c r="F24" s="31"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="33"/>
       <c r="J24" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K24" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
@@ -3360,7 +3429,7 @@
       <c r="U24" s="35"/>
       <c r="V24" s="36"/>
       <c r="W24" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3374,18 +3443,18 @@
         <v>48</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="30"/>
+        <v>69</v>
+      </c>
+      <c r="E25" s="37"/>
       <c r="F25" s="31"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="33"/>
       <c r="J25" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="34"/>
@@ -3399,7 +3468,7 @@
       <c r="U25" s="35"/>
       <c r="V25" s="36"/>
       <c r="W25" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3413,18 +3482,18 @@
         <v>48</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="30"/>
+        <v>70</v>
+      </c>
+      <c r="E26" s="37"/>
       <c r="F26" s="31"/>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="33"/>
       <c r="J26" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K26" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="34"/>
@@ -3438,7 +3507,7 @@
       <c r="U26" s="35"/>
       <c r="V26" s="36"/>
       <c r="W26" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3452,18 +3521,18 @@
         <v>48</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="30"/>
+        <v>71</v>
+      </c>
+      <c r="E27" s="37"/>
       <c r="F27" s="31"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
       <c r="I27" s="33"/>
       <c r="J27" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K27" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
@@ -3477,12 +3546,12 @@
       <c r="U27" s="35"/>
       <c r="V27" s="36"/>
       <c r="W27" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="n">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>47</v>
@@ -3491,28 +3560,18 @@
         <v>48</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="31" t="n">
-        <v>46073</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="I28" s="33" t="s">
-        <v>75</v>
-      </c>
+      <c r="E28" s="37"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="34" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K28" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="34"/>
@@ -3526,12 +3585,12 @@
       <c r="U28" s="35"/>
       <c r="V28" s="36"/>
       <c r="W28" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="n">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>47</v>
@@ -3540,28 +3599,28 @@
         <v>48</v>
       </c>
       <c r="D29" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="I29" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="F29" s="31" t="n">
-        <v>46073</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>80</v>
-      </c>
       <c r="J29" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K29" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L29" s="34"/>
       <c r="M29" s="34"/>
@@ -3575,12 +3634,12 @@
       <c r="U29" s="35"/>
       <c r="V29" s="36"/>
       <c r="W29" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>47</v>
@@ -3589,18 +3648,18 @@
         <v>48</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="30"/>
+        <v>78</v>
+      </c>
+      <c r="E30" s="37"/>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
       <c r="I30" s="33"/>
       <c r="J30" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K30" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="34"/>
@@ -3614,12 +3673,12 @@
       <c r="U30" s="35"/>
       <c r="V30" s="36"/>
       <c r="W30" s="34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B31" s="28" t="s">
         <v>47</v>
@@ -3628,28 +3687,18 @@
         <v>48</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="F31" s="31" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G31" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>86</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E31" s="37"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="33"/>
       <c r="J31" s="34" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="34"/>
@@ -3663,86 +3712,48 @@
       <c r="U31" s="35"/>
       <c r="V31" s="36"/>
       <c r="W31" s="34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="n">
-        <v>477</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="K32" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="35"/>
-      <c r="V32" s="36"/>
-      <c r="W32" s="34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="n">
-        <v>478</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="35"/>
-      <c r="V33" s="36"/>
-      <c r="W33" s="34" t="s">
-        <v>52</v>
-      </c>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="16"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F34" s="13"/>
@@ -6505,44 +6516,10 @@
       <c r="W171" s="16"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F172" s="13"/>
-      <c r="G172" s="13"/>
-      <c r="H172" s="13"/>
-      <c r="I172" s="13"/>
-      <c r="J172" s="14"/>
-      <c r="K172" s="14"/>
-      <c r="L172" s="14"/>
-      <c r="M172" s="14"/>
-      <c r="N172" s="14"/>
-      <c r="O172" s="14"/>
-      <c r="P172" s="14"/>
-      <c r="Q172" s="14"/>
-      <c r="R172" s="14"/>
-      <c r="S172" s="14"/>
-      <c r="T172" s="14"/>
-      <c r="U172" s="15"/>
-      <c r="V172" s="3"/>
-      <c r="W172" s="16"/>
+      <c r="W172" s="14"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F173" s="13"/>
-      <c r="G173" s="13"/>
-      <c r="H173" s="13"/>
-      <c r="I173" s="13"/>
-      <c r="J173" s="14"/>
-      <c r="K173" s="14"/>
-      <c r="L173" s="14"/>
-      <c r="M173" s="14"/>
-      <c r="N173" s="14"/>
-      <c r="O173" s="14"/>
-      <c r="P173" s="14"/>
-      <c r="Q173" s="14"/>
-      <c r="R173" s="14"/>
-      <c r="S173" s="14"/>
-      <c r="T173" s="14"/>
-      <c r="U173" s="15"/>
-      <c r="V173" s="3"/>
-      <c r="W173" s="16"/>
+      <c r="W173" s="14"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W174" s="14"/>
@@ -7789,19 +7766,15 @@
     <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="W588" s="14"/>
     </row>
-    <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W589" s="14"/>
-    </row>
-    <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="W590" s="14"/>
-    </row>
+    <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A9:W33"/>
+  <autoFilter ref="A9:W31"/>
   <mergeCells count="7">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -7812,15 +7785,15 @@
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J33 M10:N33 P10:R33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J10:J31 M10:N31 P10:R31" type="list">
       <formula1>Sheet1!$B$2:$B$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T10:T31" type="list">
       <formula1>Sheet1!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K10:K31" type="list">
       <formula1>'LISTA VALORI'!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7846,43 +7819,43 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
-        <v>89</v>
+      <c r="A1" s="38" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
-        <v>90</v>
+      <c r="A2" s="38" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
-        <v>91</v>
+      <c r="A3" s="38" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
-        <v>92</v>
+      <c r="A4" s="38" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
-        <v>93</v>
+      <c r="A5" s="38" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
-        <v>94</v>
+      <c r="A6" s="38" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
-        <v>51</v>
+      <c r="A7" s="38" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>95</v>
+      <c r="A8" s="38" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -7906,183 +7879,306 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="102"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="102.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="52.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="0"/>
+      <c r="F1" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="39" t="s">
+      <c r="B3" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D3" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="B4" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="45" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
+      <c r="D4" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="B5" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D5" s="46" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="42" t="s">
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="43" t="s">
+      <c r="B6" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D6" s="47" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="s">
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="43" t="s">
+      <c r="B7" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D7" s="47" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="43" t="s">
+      <c r="B8" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D8" s="47" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="43" t="s">
+      <c r="D9" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="44" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
+      <c r="B10" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="43" t="s">
+      <c r="D10" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="44" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
+      <c r="B11" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="43" t="s">
+      <c r="D11" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="44" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="43" t="s">
+      <c r="B12" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D12" s="47" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="46" t="s">
+      <c r="B13" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D13" s="47" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="43" t="s">
+      <c r="B14" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D14" s="47" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="47"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="47"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>521</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+    </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -9027,7 +9123,7 @@
     <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G17"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9062,18 +9158,18 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="141">
   <si>
     <t xml:space="preserve">COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -870,7 +870,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -991,7 +991,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1019,71 +1019,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2887,7 +2879,7 @@
       <c r="D11" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="37"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="31"/>
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
@@ -2926,7 +2918,7 @@
       <c r="D12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="37"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
@@ -2977,7 +2969,7 @@
       <c r="D13" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="37"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="31"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
@@ -3016,7 +3008,7 @@
       <c r="D14" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="37"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="31"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
@@ -3055,7 +3047,7 @@
       <c r="D15" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="31"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
@@ -3094,7 +3086,7 @@
       <c r="D16" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="37"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="31"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
@@ -3133,7 +3125,7 @@
       <c r="D17" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="37"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="31"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
@@ -3172,7 +3164,7 @@
       <c r="D18" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="37"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="31"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
@@ -3211,7 +3203,7 @@
       <c r="D19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="37"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
@@ -3250,7 +3242,7 @@
       <c r="D20" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="37"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="31"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
@@ -3289,7 +3281,7 @@
       <c r="D21" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="37"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="31"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
@@ -3328,7 +3320,7 @@
       <c r="D22" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="37"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="31"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
@@ -3367,7 +3359,7 @@
       <c r="D23" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="37"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="31"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
@@ -3406,7 +3398,7 @@
       <c r="D24" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="37"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="31"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
@@ -3445,7 +3437,7 @@
       <c r="D25" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="37"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="31"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
@@ -3484,7 +3476,7 @@
       <c r="D26" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="37"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="31"/>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
@@ -3523,7 +3515,7 @@
       <c r="D27" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="37"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="31"/>
       <c r="G27" s="32"/>
       <c r="H27" s="32"/>
@@ -3562,7 +3554,7 @@
       <c r="D28" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="37"/>
+      <c r="E28" s="30"/>
       <c r="F28" s="31"/>
       <c r="G28" s="32"/>
       <c r="H28" s="32"/>
@@ -3601,7 +3593,7 @@
       <c r="D29" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="30" t="s">
         <v>74</v>
       </c>
       <c r="F29" s="31" t="n">
@@ -3619,9 +3611,7 @@
       <c r="J29" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="K29" s="34" t="s">
-        <v>52</v>
-      </c>
+      <c r="K29" s="34"/>
       <c r="L29" s="34"/>
       <c r="M29" s="34"/>
       <c r="N29" s="34"/>
@@ -3650,7 +3640,7 @@
       <c r="D30" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="37"/>
+      <c r="E30" s="30"/>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
       <c r="H30" s="32"/>
@@ -3689,7 +3679,7 @@
       <c r="D31" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="37"/>
+      <c r="E31" s="30"/>
       <c r="F31" s="31"/>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
@@ -7819,42 +7809,42 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="37" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="37" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="37" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="37" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7887,297 +7877,248 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="0"/>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="0"/>
-      <c r="F2" s="0"/>
-      <c r="G2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="0"/>
-      <c r="F4" s="0"/>
-      <c r="G4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
-    </row>
-    <row r="7" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0"/>
-      <c r="G7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="0"/>
-      <c r="F8" s="0"/>
-      <c r="G8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
-      <c r="G9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
-      <c r="G10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="D14" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="45" t="n">
+      <c r="C15" s="44" t="n">
         <v>521</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -363,13 +363,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-09T13:42:58Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92a0d9fa1ee781154fd41ff9bc8018a8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.abe0342557^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-04-11T10:48:45Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352798b3b54381aa6df1ce1ad3a72bfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.bda8782e7d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_PSS_CT23</t>
@@ -571,7 +571,7 @@
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,6 +667,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -870,7 +876,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1019,6 +1025,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1035,7 +1049,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3597,15 +3611,15 @@
         <v>74</v>
       </c>
       <c r="F29" s="31" t="n">
-        <v>46090</v>
+        <v>46123</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="32" t="s">
+      <c r="H29" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="I29" s="33" t="s">
+      <c r="I29" s="38" t="s">
         <v>77</v>
       </c>
       <c r="J29" s="34" t="s">
@@ -7809,42 +7823,42 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="39" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="39" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="39" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="39" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="39" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="39" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7877,246 +7891,246 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="44" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="47" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="47" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="48" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="47" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="48" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="48" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="48" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="48" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="47" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="48" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="48" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="48" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="48" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="46" t="n">
         <v>521</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="48" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="48" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="48" t="s">
         <v>138</v>
       </c>
     </row>

--- a/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#YOOMULTIMEDIAX1/YOO-Multimedia-SRL/YOOMULTIMEDIA-FSE-GATEWAY/1.1.0/report-checklist.xlsx
@@ -571,7 +571,7 @@
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,12 +667,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -876,7 +870,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1025,14 +1019,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1049,7 +1035,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3616,10 +3602,10 @@
       <c r="G29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="37" t="s">
+      <c r="H29" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="I29" s="38" t="s">
+      <c r="I29" s="33" t="s">
         <v>77</v>
       </c>
       <c r="J29" s="34" t="s">
@@ -7823,42 +7809,42 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="37" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="37" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="37" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="37" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="37" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="37" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="37" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="37" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7891,246 +7877,246 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="42" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="45" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="45" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="46" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="45" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="46" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="46" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="46" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="46" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="45" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="46" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="46" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="46" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="46" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="46" t="n">
+      <c r="C15" s="44" t="n">
         <v>521</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="46" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="46" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D17" s="46" t="s">
         <v>138</v>
       </c>
     </row>
